--- a/tame_output/ON/bt/strategyON_20240917.xlsx
+++ b/tame_output/ON/bt/strategyON_20240917.xlsx
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-102.0%</t>
+          <t>-102.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-328.4%</t>
+          <t>-328.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-80.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>118.0%</t>
+          <t>117.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319539</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397788</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316243</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284876</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636281</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.81322282095762</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830323</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.75004401586814</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332685</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231801</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818516</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051782</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.81263594067962</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700472</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077634</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833451</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077623</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735275</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108851</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.80735616812146</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912979</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539888</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811003</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013421</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.730570473395084</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74127833279115</v>
+        <v>3.741278332791146</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285648</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.74058140139947</v>
+        <v>3.740581401399466</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256371</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701001</v>
+        <v>3.689942600700997</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.711852429687008</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.714879051790798</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437326</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298392</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960217994</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
@@ -48994,7 +48994,7 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.73608941335353</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113273</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113682</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016435</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307667</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863548</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394108</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715607446456724</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883671</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236294</v>
+        <v>3.71715069923629</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
@@ -49224,7 +49224,7 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427678</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610377</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
@@ -49270,7 +49270,7 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667449</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889185</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
@@ -49316,7 +49316,7 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.68247609940956</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
@@ -49339,7 +49339,7 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452567</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
@@ -49362,7 +49362,7 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762281</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988012</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
@@ -49408,7 +49408,7 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740918</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
@@ -49431,7 +49431,7 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
@@ -49454,7 +49454,7 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
@@ -49477,7 +49477,7 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
@@ -49500,7 +49500,7 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383087</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
@@ -49523,7 +49523,7 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
@@ -49546,7 +49546,7 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455267</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
@@ -49569,7 +49569,7 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.749078058963129</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.909463130501221</v>
+        <v>3.909463130501218</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.434922433821491</v>
+        <v>-4.435772915184947</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.742044901265693</v>
+        <v>2.74170470872031</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.440496942646562</v>
+        <v>1.439347646977557</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.380668464695974</v>
+        <v>5.379978887294572</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240917.xlsx
+++ b/tame_output/ON/bt/strategyON_20240917.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>69.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-70.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.0%</t>
+          <t>422.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-605.1%</t>
+          <t>-580.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-102.1%</t>
+          <t>-92.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-58.2%</t>
+          <t>-60.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-328.5%</t>
+          <t>-331.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-66.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>117.9%</t>
+          <t>121.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>111.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>100.1%</t>
         </is>
       </c>
     </row>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.781410331006696</v>
+        <v>-3.540091935801637</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9698111444346214</v>
+        <v>1.066338502516645</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4946492433056819</v>
+        <v>0.6258424675419635</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.779521247134457</v>
+        <v>2.858237181676226</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.882608112443869</v>
+        <v>-3.64128971723881</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9285359537562536</v>
+        <v>1.025063311838277</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4262404297603627</v>
+        <v>0.5574336539966442</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.737679880903767</v>
+        <v>2.816395815445536</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.876097145829556</v>
+        <v>-3.634778750624498</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9287403019562954</v>
+        <v>1.025267660038319</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4262404297603627</v>
+        <v>0.5574336539966442</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.735279842458084</v>
+        <v>2.813995776999853</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.857059018122259</v>
+        <v>-3.6157406229172</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9328802722474592</v>
+        <v>1.029407630329483</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3680568184291682</v>
+        <v>0.4992500426654497</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.696894394867612</v>
+        <v>2.775610329409381</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.909574820397079</v>
+        <v>-3.66825642519202</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.031168352971722</v>
+        <v>1.127695711053745</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3680568184291682</v>
+        <v>0.4992500426654497</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.816188796501802</v>
+        <v>2.894904731043571</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.912983131831659</v>
+        <v>-3.6716647366266</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.030638357384023</v>
+        <v>1.127165715466047</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4005733874385456</v>
+        <v>0.5317666116748271</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.836532066893562</v>
+        <v>2.915248001435331</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.893626995937812</v>
+        <v>-3.652308600732753</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.044389342138488</v>
+        <v>1.140916700220511</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4005733874385456</v>
+        <v>0.5317666116748271</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.842540597290488</v>
+        <v>2.921256531832257</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.745884025702809</v>
+        <v>-3.504565630497751</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.001436751509688</v>
+        <v>1.097964109591712</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5683807446734288</v>
+        <v>0.6995739689097102</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.841175232908618</v>
+        <v>2.919891167450387</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.829705246977507</v>
+        <v>-3.588386851772449</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.97070188453129</v>
+        <v>1.067229242613314</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5683807446734288</v>
+        <v>0.6995739689097102</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.843968854440099</v>
+        <v>2.922684788981868</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.823552540924723</v>
+        <v>-3.582234145719664</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9738253153440621</v>
+        <v>1.070352673426086</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5745334507262131</v>
+        <v>0.7057266749624945</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.848322826463427</v>
+        <v>2.927038761005196</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.840361839075225</v>
+        <v>-3.599043443870166</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9661820728239718</v>
+        <v>1.062709430905995</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5577241525757115</v>
+        <v>0.6889173768119929</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.837317724313237</v>
+        <v>2.916033658855006</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.778063840299103</v>
+        <v>-3.536745445094044</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.057436826131241</v>
+        <v>1.153964184213265</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6030184168501536</v>
+        <v>0.734211641086435</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.930829836674723</v>
+        <v>3.009545771216492</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.576273642633945</v>
+        <v>-3.334955247428886</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9404449069114318</v>
+        <v>1.036972264993455</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.801036609019308</v>
+        <v>0.9322298332555894</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.851932753690343</v>
+        <v>2.930648688232111</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.627160355320139</v>
+        <v>-3.385841960115081</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.990380454159129</v>
+        <v>1.086907812241153</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7501498963331135</v>
+        <v>0.8813431205693949</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.891690958400801</v>
+        <v>2.97040689294257</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319539</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.540549612670332</v>
+        <v>-3.299231217465274</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.039652487335096</v>
+        <v>1.136179845417119</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8287756275382717</v>
+        <v>0.9599688517745532</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.95349413323994</v>
+        <v>3.032210067781709</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.600758910675617</v>
+        <v>-3.359440515470558</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.014104748957654</v>
+        <v>1.110632107039677</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7685663295329872</v>
+        <v>0.8997595537692686</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.915904535261441</v>
+        <v>2.99462046980321</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397788</v>
+        <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.551572261991265</v>
+        <v>-3.310253866786207</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.032271026471323</v>
+        <v>1.128798384553346</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7685663295329872</v>
+        <v>0.8997595537692686</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.914396153301369</v>
+        <v>2.993112087843138</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316243</v>
+        <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.507199130352697</v>
+        <v>-3.265880735147638</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.049883146562186</v>
+        <v>1.14641050464421</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8129394611715558</v>
+        <v>0.9441326854078372</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.940882899719947</v>
+        <v>3.019598834261715</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.529679481211581</v>
+        <v>-3.288361086006523</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.035284800357223</v>
+        <v>1.131812158439246</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8129394611715558</v>
+        <v>0.9441326854078372</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.935276693858537</v>
+        <v>3.013992628400306</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.482023750650526</v>
+        <v>-3.240705355445467</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.06072884960945</v>
+        <v>1.157256207691473</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8605951917326115</v>
+        <v>0.9917884159688928</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.970251889222975</v>
+        <v>3.048967823764744</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569612</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.381505592151771</v>
+        <v>-3.140187196946712</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.105828486383676</v>
+        <v>1.2023558444657</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.961113350231366</v>
+        <v>1.092306574467647</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.035455157696953</v>
+        <v>3.114171092238721</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.365600262719418</v>
+        <v>-3.12428186751436</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.09894529063249</v>
+        <v>1.195472648714513</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8820006895221271</v>
+        <v>1.013193913758409</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.974742233747282</v>
+        <v>3.05345816828905</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.32076186111102</v>
+        <v>-3.079443465905962</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.120978353886477</v>
+        <v>1.217505711968501</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8865441224669965</v>
+        <v>1.017737346703278</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.981565996124832</v>
+        <v>3.0602819306666</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.340260317353029</v>
+        <v>-3.09894192214797</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.117339911020752</v>
+        <v>1.213867269102776</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8384594811870922</v>
+        <v>0.9696527054233737</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.956876150987967</v>
+        <v>3.035592085529736</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.296057480267128</v>
+        <v>-3.054739085062069</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.14090064838295</v>
+        <v>1.237428006464973</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8826623182729927</v>
+        <v>1.013855542509274</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.989277455767345</v>
+        <v>3.067993390309113</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.303617146104175</v>
+        <v>-3.062298750899116</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.136286782517378</v>
+        <v>1.232814140599402</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.937465722282812</v>
+        <v>1.068658946519093</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.020569498642484</v>
+        <v>3.099285433184253</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284876</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.145325728564903</v>
+        <v>-2.904007333359844</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.250851114716127</v>
+        <v>1.34737847279815</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.937465722282812</v>
+        <v>1.068658946519093</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.071817263825523</v>
+        <v>3.150533198367292</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.937683724930427</v>
+        <v>-2.696365329725368</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.332348620764171</v>
+        <v>1.428875978846194</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.145107725917288</v>
+        <v>1.27630095015357</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.194843170600462</v>
+        <v>3.273559105142231</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.886651632207899</v>
+        <v>-2.64533323700284</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.347709686091452</v>
+        <v>1.444237044173475</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.196139818639816</v>
+        <v>1.327333042876098</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.220410654472249</v>
+        <v>3.299126589014018</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.821427451080693</v>
+        <v>-2.580109055875634</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.390986762635039</v>
+        <v>1.487514120717063</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.261363999767022</v>
+        <v>1.392557224003303</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.276732567241277</v>
+        <v>3.355448501783046</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.784000431009559</v>
+        <v>-2.5426820358045</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.401918542962773</v>
+        <v>1.498445901044796</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.266615537796203</v>
+        <v>1.397808762032485</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.275844462358067</v>
+        <v>3.354560396899836</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.782642446036014</v>
+        <v>-2.541324050830955</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.403718529283432</v>
+        <v>1.500245887365455</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.340953663334022</v>
+        <v>1.472146887570304</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.321704130011998</v>
+        <v>3.400420064553767</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636281</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.75422918293613</v>
+        <v>-2.512910787731071</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.575641605544596</v>
+        <v>1.672168963626619</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.281978100587593</v>
+        <v>1.413171324823875</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.446876563385352</v>
+        <v>3.52559249792712</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095762</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.679446921911117</v>
+        <v>-2.438128526706059</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.725667419172418</v>
+        <v>1.822194777254441</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.356760361612606</v>
+        <v>1.487953585848887</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.611858829218177</v>
+        <v>3.690574763759946</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.653362837647309</v>
+        <v>-2.412044442442251</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.7278090288918</v>
+        <v>1.824336386973823</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.356760361612606</v>
+        <v>1.487953585848887</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.603566805232036</v>
+        <v>3.682282739773805</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.565484924538189</v>
+        <v>-2.32416652933313</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.761153389719228</v>
+        <v>1.857680747801251</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.472686004035957</v>
+        <v>1.603879228272238</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.671315386269826</v>
+        <v>3.750031320811595</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.556592463144906</v>
+        <v>-2.315274067939847</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.782264780003332</v>
+        <v>1.878792138085356</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.472686004035957</v>
+        <v>1.603879228272238</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.688869791996617</v>
+        <v>3.767585726538386</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.725068580114784</v>
+        <v>-2.483750184909725</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.706729380619965</v>
+        <v>1.803256738701989</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.444738168319376</v>
+        <v>1.575931392555658</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.663956137971252</v>
+        <v>3.742672072513021</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.278812387485344</v>
+        <v>-2.037493992280285</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.866501554859603</v>
+        <v>1.963028912941626</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.350019498649743</v>
+        <v>1.481212722886025</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.588394633357335</v>
+        <v>3.667110567899104</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.256091283802191</v>
+        <v>-2.014772888597133</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.866254018829768</v>
+        <v>1.962781376911792</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.350019498649743</v>
+        <v>1.481212722886025</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.579058655854239</v>
+        <v>3.657774590396008</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.385293097096234</v>
+        <v>-2.143974701891175</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.973479419363321</v>
+        <v>2.070006777445344</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.220817685355701</v>
+        <v>1.352010909591983</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.660443693728983</v>
+        <v>3.739159628270752</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.411167495570259</v>
+        <v>-2.169849100365201</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.000207482467357</v>
+        <v>2.09673484054938</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.265729294067442</v>
+        <v>1.396922518303724</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.724468481449674</v>
+        <v>3.803184415991443</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.404112805355086</v>
+        <v>-2.162794410150027</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.999704714542971</v>
+        <v>2.096232072624995</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.272783984282616</v>
+        <v>1.403977208518898</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.725376651568324</v>
+        <v>3.804092586110093</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.377161581028598</v>
+        <v>-2.135843185823539</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.020491357918308</v>
+        <v>2.117018716000332</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.287664330310335</v>
+        <v>1.418857554546617</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.744311012829697</v>
+        <v>3.823026947371466</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.398705808859385</v>
+        <v>-2.157387413654326</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.195976798930953</v>
+        <v>2.292504157012976</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.287664330310335</v>
+        <v>1.418857554546617</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.928414144974656</v>
+        <v>4.007130079516426</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.421113926664257</v>
+        <v>-2.179795531459198</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.179130246711997</v>
+        <v>2.275657604794021</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.287664330310335</v>
+        <v>1.418857554546617</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.920530839877649</v>
+        <v>3.999246774419419</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.449338162241857</v>
+        <v>-2.208019767036799</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.169894552030595</v>
+        <v>2.266421910112618</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.305641082761644</v>
+        <v>1.436834306997925</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.933370890898072</v>
+        <v>4.012086825439841</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.458779088130387</v>
+        <v>-2.217460692925329</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.22237189939703</v>
+        <v>2.318899257479053</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.428068200305035</v>
+        <v>1.559261424541317</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.063080879145955</v>
+        <v>4.141796813687723</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.547655719298861</v>
+        <v>-2.306337324093803</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.189712341474941</v>
+        <v>2.286239699556964</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.339191569136561</v>
+        <v>1.470384793372843</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.012645994990171</v>
+        <v>4.091361929531939</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.623985696899767</v>
+        <v>-2.382667301694708</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.157292163328354</v>
+        <v>2.253819521410378</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.339191569136561</v>
+        <v>1.470384793372843</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.010757807883946</v>
+        <v>4.089473742425715</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.717649641577308</v>
+        <v>-2.47633124637225</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.1146468150602</v>
+        <v>2.211174173142223</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.24552762445902</v>
+        <v>1.376720848695302</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.949379670680283</v>
+        <v>4.028095605222052</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.879218067104564</v>
+        <v>-2.637899671899505</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.04845345505945</v>
+        <v>2.144980813141474</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.118744700661141</v>
+        <v>1.249937924897422</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.871743926611708</v>
+        <v>3.950459861153477</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.987518728974683</v>
+        <v>-2.746200333769624</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.018206597177321</v>
+        <v>2.114733955259344</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.118744700661141</v>
+        <v>1.249937924897422</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.884817333477627</v>
+        <v>3.963533268019396</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.005322700695427</v>
+        <v>-2.764004305490368</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.003090205271963</v>
+        <v>2.099617563353987</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.04821007775594</v>
+        <v>1.179403301992221</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.834501756517446</v>
+        <v>3.913217691059215</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.0332234878049</v>
+        <v>-2.791905092599841</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.990453931555176</v>
+        <v>2.086981289637199</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.013613153613005</v>
+        <v>1.144806377849287</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.812267643158687</v>
+        <v>3.890983577700456</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.155749590507794</v>
+        <v>-2.914431195302735</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.938207934451217</v>
+        <v>2.034735292533241</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.891087050910111</v>
+        <v>1.022280275146393</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.73551642551415</v>
+        <v>3.814232360055918</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.386264086693383</v>
+        <v>-3.144945691488324</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.912708095567485</v>
+        <v>2.009235453649509</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6605725547245223</v>
+        <v>0.7917657789608039</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.6639136873933</v>
+        <v>3.742629621935069</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.735009171917826</v>
+        <v>-3.493690776712768</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.913521780479555</v>
+        <v>2.010049138561579</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5518246008056245</v>
+        <v>0.6830178250419061</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.738976634043809</v>
+        <v>3.817692568585577</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.888995589693967</v>
+        <v>-3.647677194488908</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.920907482514739</v>
+        <v>2.017434840596762</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5518246008056245</v>
+        <v>0.6830178250419061</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.807956903189448</v>
+        <v>3.886672837731217</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.093595024556976</v>
+        <v>-3.852276629351917</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.825118910689656</v>
+        <v>1.92164626877168</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5518246008056245</v>
+        <v>0.6830178250419061</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.794008105309569</v>
+        <v>3.872724039851338</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.3460701785647</v>
+        <v>-4.104751783359641</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.73599933814198</v>
+        <v>1.832526696224004</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5518246008056245</v>
+        <v>0.6830178250419061</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.805878594364983</v>
+        <v>3.884594528906752</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.638965935044112</v>
+        <v>-4.397647539839054</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.620051570069159</v>
+        <v>1.716578928151183</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5518246008056245</v>
+        <v>0.6830178250419061</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.807089128883927</v>
+        <v>3.885805063425696</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.82563006317892</v>
+        <v>-4.584311667973862</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.549507661042557</v>
+        <v>1.646035019124581</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5250856299810646</v>
+        <v>0.6562788542173462</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.795167488616512</v>
+        <v>3.873883423158281</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.971650750092882</v>
+        <v>-4.730332354887824</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.486177239013162</v>
+        <v>1.582704597095185</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5160025381872075</v>
+        <v>0.6471957624234892</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.784795486276388</v>
+        <v>3.863511420818157</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830323</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.063364759202468</v>
+        <v>-4.822046363997408</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.611695692068372</v>
+        <v>1.708223050150395</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5160025381872075</v>
+        <v>0.6471957624234892</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.946999542975432</v>
+        <v>4.025715477517201</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.095016418262437</v>
+        <v>-4.853698023057378</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.593881666408198</v>
+        <v>1.690409024490222</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5108340809427674</v>
+        <v>0.642027305179049</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.938745106592582</v>
+        <v>4.017461041134351</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.75004401586814</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.176951236531321</v>
+        <v>-4.935632841326261</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.571337156669136</v>
+        <v>1.66786451475116</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5008993353556872</v>
+        <v>0.6320925595919689</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.943013676808825</v>
+        <v>4.021729611350594</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332685</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.278927358779728</v>
+        <v>-5.037608963574669</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.539472346225675</v>
+        <v>1.635999704307699</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3989232131072796</v>
+        <v>0.5301164373435613</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.890753641915683</v>
+        <v>3.969469576457452</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231801</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.168921075302507</v>
+        <v>-4.927602680097447</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.575627746860739</v>
+        <v>1.672155104942763</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4221277850245548</v>
+        <v>0.5533210092608365</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.896829272310223</v>
+        <v>3.975545206851992</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818516</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.02586149956158</v>
+        <v>-4.784543104356521</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.637101587879084</v>
+        <v>1.733628945961108</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4301412116145341</v>
+        <v>0.5613344358508158</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.905887338986185</v>
+        <v>3.984603273527954</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051782</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.724414774089743</v>
+        <v>-4.483096378884683</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.764941160950355</v>
+        <v>1.861468519032379</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7315879370863714</v>
+        <v>0.862781161322653</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.094016257151823</v>
+        <v>4.172732191693592</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.81263594067962</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.749005018324927</v>
+        <v>-4.507686623119867</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.756076241008992</v>
+        <v>1.852603599091016</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7315879370863714</v>
+        <v>0.862781161322653</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.094987434904534</v>
+        <v>4.173703369446303</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.697966642318407</v>
+        <v>-4.456648247113347</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.777334495791356</v>
+        <v>1.87386185387338</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7315879370863714</v>
+        <v>0.862781161322653</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.09583033928429</v>
+        <v>4.174546273826058</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969538</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.656827347451776</v>
+        <v>-4.415508952246716</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.812828312612154</v>
+        <v>1.909355670694177</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7727272319530022</v>
+        <v>0.9039204561892838</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.139552015078413</v>
+        <v>4.218267949620182</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700472</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.560192435433136</v>
+        <v>-4.318874040228076</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.667666273543544</v>
+        <v>1.764193631625568</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8693621439716421</v>
+        <v>1.000555368207924</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.013716958413532</v>
+        <v>4.092432892955301</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077634</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.690773169963978</v>
+        <v>-4.449454774758919</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.618936023805171</v>
+        <v>1.715463381887195</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7387814094407996</v>
+        <v>0.8699746336770813</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.93887056176899</v>
+        <v>4.017586496310759</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833451</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.526276835773016</v>
+        <v>-4.284958440567957</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.669161376557639</v>
+        <v>1.765688734639662</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9032777436317615</v>
+        <v>1.034470967868043</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.02199518135965</v>
+        <v>4.10071111590142</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077623</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.449178234231144</v>
+        <v>-4.207859839026084</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.699188527610817</v>
+        <v>1.795715885692841</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9032777436317615</v>
+        <v>1.034470967868043</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.02118289179608</v>
+        <v>4.099898826337849</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147905</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.459563429121033</v>
+        <v>-4.218245033915974</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.704903228779934</v>
+        <v>1.801430586861958</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8928925487418722</v>
+        <v>1.024085772978154</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.024820553987219</v>
+        <v>4.103536488528988</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735275</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.478151587843258</v>
+        <v>-4.236833192638199</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.768304971067469</v>
+        <v>1.864832329149493</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8743043900196468</v>
+        <v>1.005497614255928</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.084504664530309</v>
+        <v>4.163220599072078</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.478450134539294</v>
+        <v>-4.237131739334234</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.765054563207353</v>
+        <v>1.861581921289377</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8740058433236109</v>
+        <v>1.005199067559893</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.081194547330986</v>
+        <v>4.159910481872755</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108851</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.377627000848866</v>
+        <v>-4.136308605643807</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.809914711622916</v>
+        <v>1.90644206970494</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8864700588079647</v>
+        <v>1.017663283044246</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.093203971560989</v>
+        <v>4.171919906102758</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.80735616812146</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.186845640096459</v>
+        <v>-3.945527244891399</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.886356509402422</v>
+        <v>1.982883867484446</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.077251419560372</v>
+        <v>1.208444643796654</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.207802041490977</v>
+        <v>4.286517976032746</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.079882282247038</v>
+        <v>-3.838563887041977</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.908978698279787</v>
+        <v>2.005506056361811</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.135716027520174</v>
+        <v>1.266909251756455</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.222717652004454</v>
+        <v>4.301433586546223</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912979</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.024551694345275</v>
+        <v>-3.783233299140215</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.96607787005255</v>
+        <v>2.062605228134574</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.191046615421936</v>
+        <v>1.322239839658217</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.29088294135757</v>
+        <v>4.36959887589934</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539888</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.012497567432312</v>
+        <v>-3.771179172227253</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.964586088719173</v>
+        <v>2.061113446801198</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.203100742334898</v>
+        <v>1.33429396657118</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.291801985406786</v>
+        <v>4.370517919948554</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811003</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.053652687000533</v>
+        <v>-3.812334291795473</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.950004671076021</v>
+        <v>2.046532029158045</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.161945622766678</v>
+        <v>1.293138847002959</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.268989543849989</v>
+        <v>4.347705478391758</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382913</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.985604124309003</v>
+        <v>-3.744285729103944</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.990075122030516</v>
+        <v>2.086602480112539</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.229994185458207</v>
+        <v>1.361187409694489</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.322669707342789</v>
+        <v>4.401385641884558</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013421</v>
+        <v>3.645256780013424</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.217204517478504</v>
+        <v>-3.975886122273445</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.917637634936309</v>
+        <v>2.014164993018333</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.229994185458207</v>
+        <v>1.361187409694489</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.342872377516383</v>
+        <v>4.421588312058153</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.267256063007723</v>
+        <v>-4.025937667802664</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.881223252791504</v>
+        <v>1.977750610873527</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.229994185458207</v>
+        <v>1.361187409694489</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.326478613583266</v>
+        <v>4.405194548125035</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800095</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.442362895584168</v>
+        <v>-4.201044500379108</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.771432433354392</v>
+        <v>1.867959791436416</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.229994185458207</v>
+        <v>1.361187409694489</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.286730527176732</v>
+        <v>4.365446461718501</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660847</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.246262742153645</v>
+        <v>-4.004944346948585</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.856895113723541</v>
+        <v>1.953422471805565</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.42609433888873</v>
+        <v>1.557287563125012</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.411413238231986</v>
+        <v>4.490129172773755</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395084</v>
+        <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.09323735004036</v>
+        <v>-3.851918954835301</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.017276270141759</v>
+        <v>2.113803628223783</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.579119731002014</v>
+        <v>1.710312955238296</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.602399473072861</v>
+        <v>4.68111540761463</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791146</v>
+        <v>3.74127833279115</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.121544663913631</v>
+        <v>-3.880226268708571</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.193419569500744</v>
+        <v>2.289946927582768</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.579119731002014</v>
+        <v>1.710312955238296</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.789865697981154</v>
+        <v>4.868581632522922</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620432</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.288137889027153</v>
+        <v>-4.046819493822094</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.096185230809418</v>
+        <v>2.192712588891442</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.412526505888492</v>
+        <v>1.543719730124774</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.659312714267123</v>
+        <v>4.738028648808892</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285648</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.265102095665587</v>
+        <v>-4.023783700460528</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.109075950815762</v>
+        <v>2.205603308897786</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.412526505888492</v>
+        <v>1.543719730124774</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.66298911692884</v>
+        <v>4.74170505147061</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399466</v>
+        <v>3.74058140139947</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.235856115209891</v>
+        <v>-3.994537720004832</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.118392398121536</v>
+        <v>2.214919756203559</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.412526505888492</v>
+        <v>1.543719730124774</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.660607172052336</v>
+        <v>4.739323106594105</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.699404642256371</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.342781663087742</v>
+        <v>-4.101463267882683</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.07291541812803</v>
+        <v>2.169442776210054</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.305600958010641</v>
+        <v>1.436794182246922</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.59374508248326</v>
+        <v>4.672461017025029</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700997</v>
+        <v>3.689942600701001</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.48780022159499</v>
+        <v>-4.246481826389932</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.016336796868365</v>
+        <v>2.112864154950389</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.160582399503392</v>
+        <v>1.291775623739674</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.508162749522145</v>
+        <v>4.586878684063914</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687008</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.606141987379708</v>
+        <v>-4.364823592174649</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.068931329812231</v>
+        <v>2.165458687894255</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.171268438066282</v>
+        <v>1.302461662302564</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.614505611917632</v>
+        <v>4.693221546459401</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790798</v>
+        <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.657552409700416</v>
+        <v>-4.416234014495357</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.046152858009887</v>
+        <v>2.142680216091911</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.171268438066282</v>
+        <v>1.302461662302564</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.612291309043571</v>
+        <v>4.69100724358534</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437326</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.736971860908167</v>
+        <v>-4.495653465703109</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.014288205601076</v>
+        <v>2.110815563683099</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.171268438066282</v>
+        <v>1.302461662302564</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.612194437117861</v>
+        <v>4.690910371659629</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298392</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.832434858825385</v>
+        <v>-4.591116463620327</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.976096899992232</v>
+        <v>2.072624258074255</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.171268438066282</v>
+        <v>1.302461662302564</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.612188330675903</v>
+        <v>4.690904265217672</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217994</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.76805894797467</v>
+        <v>-4.526740552769612</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.999943660895128</v>
+        <v>2.096471018977152</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.235644348916997</v>
+        <v>1.366837573153279</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.648910273748943</v>
+        <v>4.727626208290712</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73608941335353</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.823428110106864</v>
+        <v>-4.582109714901805</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.983529813789978</v>
+        <v>2.080057171872001</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.235644348916997</v>
+        <v>1.366837573153279</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.65464409149667</v>
+        <v>4.733360026038438</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113273</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.868865889937691</v>
+        <v>-4.627547494732632</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.964893065200579</v>
+        <v>2.061420423282602</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.192799358238838</v>
+        <v>1.32399258247512</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.628475460432706</v>
+        <v>4.707191394974475</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113682</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.780659055790113</v>
+        <v>-4.539340660585054</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.020050191709929</v>
+        <v>2.116577549791952</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.192799358238838</v>
+        <v>1.32399258247512</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.648349853283025</v>
+        <v>4.727065787824794</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016435</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.674624060584804</v>
+        <v>-4.433305665379745</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.04616489031678</v>
+        <v>2.142692248398804</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.192799358238838</v>
+        <v>1.32399258247512</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.632050553807753</v>
+        <v>4.710766488349522</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307667</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.491412397451708</v>
+        <v>-4.25009400224665</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.121880505034064</v>
+        <v>2.218407863116088</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.192799358238838</v>
+        <v>1.32399258247512</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.634481503271799</v>
+        <v>4.713197437813568</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863548</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.419690950437857</v>
+        <v>-4.178372555232799</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.116360269687494</v>
+        <v>2.212887627769518</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.264520805252689</v>
+        <v>1.39571402948897</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.643305557327999</v>
+        <v>4.722021491869768</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394108</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.397317924830151</v>
+        <v>-4.155999529625093</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.072225225851748</v>
+        <v>2.168752583933772</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.27577655636559</v>
+        <v>1.406969780601872</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.596974753916911</v>
+        <v>4.67569068845868</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456724</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.430334220740896</v>
+        <v>-4.189015825535837</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.244216912372806</v>
+        <v>2.340744270454829</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.206339179698839</v>
+        <v>1.33753240393512</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.740510532802215</v>
+        <v>4.819226467343984</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883671</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.418806585091287</v>
+        <v>-4.177488189886229</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.240749192460898</v>
+        <v>2.337276550542922</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.265339837900201</v>
+        <v>1.396533062136483</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.767832153551282</v>
+        <v>4.84654808809305</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.71715069923629</v>
+        <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.516148086433656</v>
+        <v>-4.274829691228597</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.205480704445739</v>
+        <v>2.302008062527762</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.220919655734713</v>
+        <v>1.352112879970994</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.744848156773777</v>
+        <v>4.823564091315546</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427678</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.602004115773623</v>
+        <v>-4.360685720568564</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.172389374902591</v>
+        <v>2.268916732984614</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.178543586508578</v>
+        <v>1.309736810744859</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.720673597430935</v>
+        <v>4.799389531972704</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610377</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.610840913189742</v>
+        <v>-4.369522517984683</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.151273857756645</v>
+        <v>2.247801215838668</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.171101413867227</v>
+        <v>1.302294638103509</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.698627495666626</v>
+        <v>4.777343430208395</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667449</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.702223475755201</v>
+        <v>-4.460905080550142</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.124885343775511</v>
+        <v>2.221412701857534</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.134536529147882</v>
+        <v>1.265729753384164</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.686853075880069</v>
+        <v>4.765569010421838</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889185</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.690516757768195</v>
+        <v>-4.449198362563136</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.231696288794581</v>
+        <v>2.328223646876604</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.146243247134889</v>
+        <v>1.27743647137117</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.79600536449654</v>
+        <v>4.874721299038309</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.68247609940956</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.590853253684532</v>
+        <v>-4.349534858479474</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.27459402915945</v>
+        <v>2.371121387241474</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.209430330338575</v>
+        <v>1.340623554574857</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.836949953150157</v>
+        <v>4.915665887691926</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452567</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.601169351850884</v>
+        <v>-4.359850956645825</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.483372423170968</v>
+        <v>2.579899781252991</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.209430330338575</v>
+        <v>1.340623554574857</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.049854786428215</v>
+        <v>5.128570720969984</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762281</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.601075383833511</v>
+        <v>-4.359756988628453</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.482588677290006</v>
+        <v>2.57911603537203</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.209800191685893</v>
+        <v>1.340993415922175</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.049255370148695</v>
+        <v>5.127971304690464</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988012</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.608294208033356</v>
+        <v>-4.366975812828297</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.473933133554422</v>
+        <v>2.570460491636446</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.209800191685893</v>
+        <v>1.340993415922175</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.043487356093049</v>
+        <v>5.122203290634818</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740918</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.607345784915317</v>
+        <v>-4.366027389710259</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.474312502801638</v>
+        <v>2.570839860883662</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.209800191685893</v>
+        <v>1.340993415922175</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.043487356093049</v>
+        <v>5.122203290634818</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663622</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.764414243170942</v>
+        <v>-4.523095847965882</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.42421272748048</v>
+        <v>2.520740085562504</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.209800191685893</v>
+        <v>1.340993415922175</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.056214964074141</v>
+        <v>5.134930898615909</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424766</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.75842199638213</v>
+        <v>-4.51710360117707</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.428555624620393</v>
+        <v>2.525082982702417</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.209800191685893</v>
+        <v>1.340993415922175</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.058160962498529</v>
+        <v>5.136876897040297</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149214</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.669864035251362</v>
+        <v>-4.428545640046303</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.457632945090468</v>
+        <v>2.554160303172492</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.209800191685893</v>
+        <v>1.340993415922175</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.051815098516298</v>
+        <v>5.130531033058066</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383087</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.652104957748288</v>
+        <v>-4.410786562543229</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.464045253530694</v>
+        <v>2.560572611612717</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.209800191685893</v>
+        <v>1.340993415922175</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.051123775955293</v>
+        <v>5.129839710497063</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.55247480669922</v>
+        <v>-4.311156411494161</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.516679499858908</v>
+        <v>2.613206857940932</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.309430342734961</v>
+        <v>1.440623566971242</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.123684052493321</v>
+        <v>5.20239998703509</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455267</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.601874315388232</v>
+        <v>-4.360555920183172</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.68607396188203</v>
+        <v>2.782601319964053</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.319689176166706</v>
+        <v>1.450882400402987</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.318993618051094</v>
+        <v>5.397709552592863</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963129</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.395189841745855</v>
+        <v>-4.153871446540796</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.755936424441842</v>
+        <v>2.852463782523866</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.526373649809081</v>
+        <v>1.657566874045363</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.430192975339381</v>
+        <v>5.50890890988115</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.909463130501218</v>
+        <v>3.979602843474773</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.435772915184947</v>
+        <v>-4.188028341538322</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.74170470872031</v>
+        <v>2.84080253817896</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.439347646977557</v>
+        <v>1.57398310450455</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.379978887294572</v>
+        <v>5.460760161810768</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240917.xlsx
+++ b/tame_output/ON/bt/strategyON_20240917.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.6%</t>
+          <t>422.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-580.4%</t>
+          <t>-593.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-92.1%</t>
+          <t>-97.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-60.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-331.1%</t>
+          <t>-343.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-66.6%</t>
+          <t>-68.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>121.3%</t>
+          <t>120.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>111.4%</t>
+          <t>110.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.1%</t>
+          <t>98.9%</t>
         </is>
       </c>
     </row>
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.338778816372826</v>
+        <v>-7.226054034658109</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2155920232403763</v>
+        <v>0.2606819359262631</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.060402676835486</v>
+        <v>-0.9476778951207698</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.515218368001963</v>
+        <v>2.582853237030793</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.175378945433463</v>
+        <v>-7.062654163718746</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2803187928368782</v>
+        <v>0.325408705522765</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8970028058961237</v>
+        <v>-0.7842780241814074</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.612625111786337</v>
+        <v>2.680259980815167</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.941897723203865</v>
+        <v>-6.829172941489148</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3816357105665698</v>
+        <v>0.4267256232524566</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6635215836665251</v>
+        <v>-0.5507968019518088</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.760638273961949</v>
+        <v>2.828273142990779</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.79223133219635</v>
+        <v>-6.679506550481633</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4386100566566169</v>
+        <v>0.4836999693425037</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5706180924239892</v>
+        <v>-0.4578933107092729</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.813488158394511</v>
+        <v>2.881123027423341</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.659955858565463</v>
+        <v>-6.547231076850746</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.392781032116126</v>
+        <v>0.4378709448020128</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4383426187931025</v>
+        <v>-0.3256178370783862</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.794114228580198</v>
+        <v>2.861749097609028</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.488094643000561</v>
+        <v>-6.375369861285844</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4643405790297237</v>
+        <v>0.5094304917156105</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.2664814032281997</v>
+        <v>-0.1537566215134833</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.900046018606776</v>
+        <v>2.967680887635606</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.403129976271241</v>
+        <v>-6.290405194556524</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5112327869451101</v>
+        <v>0.5563226996309973</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1815167364988801</v>
+        <v>-0.06879195478416378</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.963931159868027</v>
+        <v>3.031566028896857</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.508719966044346</v>
+        <v>-6.395995184329628</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3410208614366494</v>
+        <v>0.3861107741225367</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2871067262719845</v>
+        <v>-0.1743819445572681</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.772601236404946</v>
+        <v>2.840236105433775</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.440485381418918</v>
+        <v>-6.327760599704201</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4168590371639072</v>
+        <v>0.461948949849794</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2686914033994485</v>
+        <v>-0.1559666216847321</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.832194772005554</v>
+        <v>2.899829641034383</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.292545340011319</v>
+        <v>-6.179820558296601</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3594142450885398</v>
+        <v>0.4045041577744266</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2483704874908909</v>
+        <v>-0.1356457057761746</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.727766512912281</v>
+        <v>2.795401381941111</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.239575817757331</v>
+        <v>-6.126851036042613</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3718880677366569</v>
+        <v>0.4169779804225442</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.0826761835221857</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.750834240011196</v>
+        <v>2.818469109040026</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.07378762179704</v>
+        <v>-5.961062840082322</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4312427340256799</v>
+        <v>0.4763326467115672</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.0826761835221857</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.743873627916103</v>
+        <v>2.811508496944933</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.040424415318271</v>
+        <v>-5.927699633603553</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4590503709983307</v>
+        <v>0.5041402836842179</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.0826761835221857</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.758335982297246</v>
+        <v>2.825970851326076</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.932165278195749</v>
+        <v>-5.819440496481032</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4968861463065344</v>
+        <v>0.5419760589924216</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.0826761835221857</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.752868102756441</v>
+        <v>2.820502971785271</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.808874143378619</v>
+        <v>-5.696149361663901</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5437006942439635</v>
+        <v>0.5887906069298507</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.07210983041977154</v>
+        <v>0.0406149512949448</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.824340877657296</v>
+        <v>2.891975746686126</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.756177276247327</v>
+        <v>-5.643452494532609</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5724804193338051</v>
+        <v>0.6175703320196924</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.01941296328848036</v>
+        <v>0.09331181842623598</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.863659976173396</v>
+        <v>2.931294845202226</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.512411834263883</v>
+        <v>-5.399687052549165</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6657673044742336</v>
+        <v>0.7108572171601208</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.01941296328848036</v>
+        <v>0.09331181842623598</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.859440684520447</v>
+        <v>2.927075553549277</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.422636161887411</v>
+        <v>-5.309911380172693</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7038018873448384</v>
+        <v>0.7488918000307256</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.04218648162582966</v>
+        <v>0.154911263340546</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.898524665389049</v>
+        <v>2.966159534417879</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.172785767938336</v>
+        <v>-5.060060986223618</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7964841199081705</v>
+        <v>0.8415740325940577</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.04218648162582966</v>
+        <v>0.154911263340546</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.891266740372751</v>
+        <v>2.958901609401581</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.996893675470904</v>
+        <v>-4.884168893756186</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8704400804157921</v>
+        <v>0.9155299931016794</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.04218648162582966</v>
+        <v>0.154911263340546</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.8948658638934</v>
+        <v>2.962500732922229</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.825447212448441</v>
+        <v>-4.712722430733723</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9523461716793311</v>
+        <v>0.9974360843652184</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2136329446482928</v>
+        <v>0.3263577263630091</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.011061247761432</v>
+        <v>3.078696116790261</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.74542492533932</v>
+        <v>-4.632700143624602</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9833755641392765</v>
+        <v>1.028465476825164</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2936552317574138</v>
+        <v>0.4063800134721301</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.058095097643201</v>
+        <v>3.125729966672031</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.681789183105385</v>
+        <v>-4.569064401390667</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.013524662087168</v>
+        <v>1.058614574773055</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3572909739913483</v>
+        <v>0.4700157557060646</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.100971344037879</v>
+        <v>3.168606213066709</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.58809186488899</v>
+        <v>-4.475367083174272</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.032197848157521</v>
+        <v>1.077287760843408</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3572909739913483</v>
+        <v>0.4700157557060646</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.082165602821675</v>
+        <v>3.149800471850504</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.598594487954279</v>
+        <v>-4.485869706239561</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.029739875556283</v>
+        <v>1.07482978824217</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3467883509260594</v>
+        <v>0.4595131326407758</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.077607105607379</v>
+        <v>3.145241974636209</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.486108227285404</v>
+        <v>-4.373383445570687</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.078663693658653</v>
+        <v>1.12375360634454</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3467883509260594</v>
+        <v>0.4595131326407758</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.081536419442199</v>
+        <v>3.149171288471029</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.468394540407539</v>
+        <v>-4.355669758692821</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.086427752327139</v>
+        <v>1.131517665013027</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3499696798229762</v>
+        <v>0.4626944615376926</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.084123800697689</v>
+        <v>3.151758669726519</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.344920269094521</v>
+        <v>-4.232195487379803</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.13281553207234</v>
+        <v>1.177905444758227</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3499696798229762</v>
+        <v>0.4626944615376926</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.081121871917682</v>
+        <v>3.148756740946512</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.12489947105751</v>
+        <v>-4.012174689342793</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.222402888297758</v>
+        <v>1.267492800983645</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4911895248909565</v>
+        <v>0.6039143066056728</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.167432815969085</v>
+        <v>3.235067684997914</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.992031781994232</v>
+        <v>-3.879307000279514</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.291444146724893</v>
+        <v>1.33653405941078</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4911895248909565</v>
+        <v>0.6039143066056728</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.183326998770908</v>
+        <v>3.250961867799738</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.871858698629733</v>
+        <v>-3.759133916915015</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.340659224510995</v>
+        <v>1.385749137196882</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6113626082554554</v>
+        <v>0.7240873899701717</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.256576693229909</v>
+        <v>3.324211562258739</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.736605337299756</v>
+        <v>-3.623880555585038</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.404848671604425</v>
+        <v>1.449938584290312</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7466159695854325</v>
+        <v>0.8593407513001489</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.347816812589335</v>
+        <v>3.415451681618165</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.796480164657448</v>
+        <v>-3.683755382942731</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.366936232062774</v>
+        <v>1.412026144748661</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6867411422277404</v>
+        <v>0.7994659239424567</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.297929407576146</v>
+        <v>3.365564276604976</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.676659933746611</v>
+        <v>-3.563935152031893</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.430153493661318</v>
+        <v>1.475243406347205</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6867411422277404</v>
+        <v>0.7994659239424567</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.313218576810355</v>
+        <v>3.380853445839184</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.679129640208417</v>
+        <v>-3.566404858493699</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.336809810399037</v>
+        <v>1.381899723084924</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6842714357659343</v>
+        <v>0.7969962174806506</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.219380952255712</v>
+        <v>3.287015821284542</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.747499826532427</v>
+        <v>-3.634775044817709</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.228723597354734</v>
+        <v>1.273813510040621</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.8062719165168656</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.144208233162743</v>
+        <v>3.211843102191573</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.859372106158578</v>
+        <v>-3.74664732444386</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.174411394136165</v>
+        <v>1.219501306822052</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.8062719165168656</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.134644941794634</v>
+        <v>3.202279810823464</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.84339744067231</v>
+        <v>-3.730672658957592</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.1473757852547</v>
+        <v>1.192465697940587</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.8062719165168656</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.101219466718661</v>
+        <v>3.168854335747491</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.66792318087984</v>
+        <v>-3.555198399165123</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.222132721163475</v>
+        <v>1.267222633849362</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.8062719165168656</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.105786698710449</v>
+        <v>3.173421567739279</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.659998806294926</v>
+        <v>-3.547274024580208</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.201044499758648</v>
+        <v>1.246134412444535</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.8062719165168656</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.081528727471656</v>
+        <v>3.149163596500486</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.653720603725077</v>
+        <v>-3.540995822010359</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.132094094188037</v>
+        <v>1.177184006873925</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6998253373719983</v>
+        <v>0.8125501190867146</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.013833962415015</v>
+        <v>3.081468831443845</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.593867984521354</v>
+        <v>-3.481143202806636</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.166207528301659</v>
+        <v>1.211297440987546</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6998253373719983</v>
+        <v>0.8125501190867146</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.024006348847148</v>
+        <v>3.091641217875978</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.507624521494977</v>
+        <v>-3.394899739780259</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.19565118408607</v>
+        <v>1.240741096771957</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6998253373719983</v>
+        <v>0.8125501190867146</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.018952619421008</v>
+        <v>3.086587488449838</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.552931340893957</v>
+        <v>-3.440206559179239</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.169304231771004</v>
+        <v>1.214394144456891</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6590151743627675</v>
+        <v>0.7717399560774838</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.986242297059995</v>
+        <v>3.053877166088825</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.581964445596258</v>
+        <v>-3.46923966388154</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.158242862923185</v>
+        <v>1.203332775609072</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6590151743627675</v>
+        <v>0.7717399560774838</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.986794170093097</v>
+        <v>3.054429039121926</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.489153964145399</v>
+        <v>-3.376429182430681</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.124639747394894</v>
+        <v>1.169729660080781</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7518256558136268</v>
+        <v>0.8645504375283432</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.971753150854978</v>
+        <v>3.039388019883808</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.533543433474827</v>
+        <v>-3.420818651760109</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.108757435587724</v>
+        <v>1.153847348273611</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7074361864841991</v>
+        <v>0.8201609681989155</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.946992945181922</v>
+        <v>3.014627814210752</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.513039739589329</v>
+        <v>-3.400314957874611</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.112034621653646</v>
+        <v>1.157124534339533</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7279398803696965</v>
+        <v>0.8406646620844128</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.954370870024944</v>
+        <v>3.022005739053773</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.552963834171901</v>
+        <v>-3.440239052457184</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.101556279651284</v>
+        <v>1.146646192337171</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7279398803696965</v>
+        <v>0.8406646620844128</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.959862165855611</v>
+        <v>3.027497034884441</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.580744232073255</v>
+        <v>-3.468019450358537</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.101941322259282</v>
+        <v>1.147031234945169</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7001594824683435</v>
+        <v>0.8128842641830598</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.954691128883338</v>
+        <v>3.022325997912168</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.699124904803393</v>
+        <v>-3.586400123088675</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8929447731678799</v>
+        <v>0.9380346858537671</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6329416303173673</v>
+        <v>0.7456664120320836</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.752716137593405</v>
+        <v>2.820351006622236</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.807738983246724</v>
+        <v>-3.695014201532006</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9696488025097532</v>
+        <v>1.01473871519564</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6329416303173673</v>
+        <v>0.7456664120320836</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.872865798312611</v>
+        <v>2.940500667341441</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.772329944998581</v>
+        <v>-3.659605163283863</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9983254439113332</v>
+        <v>1.04341535659722</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6329416303173673</v>
+        <v>0.7456664120320836</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.887378824414934</v>
+        <v>2.955013693443764</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.780791113654042</v>
+        <v>-3.668066331939325</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9923604177915175</v>
+        <v>1.037450330477405</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6244804616619062</v>
+        <v>0.7372052433766225</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.879721564564026</v>
+        <v>2.947356433592856</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.603674783618876</v>
+        <v>-3.490950001904158</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.059935978650886</v>
+        <v>1.105025891336773</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6244804616619062</v>
+        <v>0.7372052433766225</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.876450593409329</v>
+        <v>2.944085462438158</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.648767028452422</v>
+        <v>-3.536042246737704</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.042582472479381</v>
+        <v>1.087672385165268</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5625844184925164</v>
+        <v>0.6753092002072327</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.839996359269608</v>
+        <v>2.907631228298438</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.469391607213654</v>
+        <v>-3.356666825498936</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.108119616281303</v>
+        <v>1.15320952896719</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7193611766632351</v>
+        <v>0.8320859583779514</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.927849389478454</v>
+        <v>2.995484258507283</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.514405820734261</v>
+        <v>-3.401681039019543</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.07092138620465</v>
+        <v>1.116011298890537</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6890122813486305</v>
+        <v>0.8017370630633468</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.890447507621281</v>
+        <v>2.95808237665011</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.540091935801637</v>
+        <v>-3.668685549291978</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.066338502516645</v>
+        <v>1.014901057120508</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6258424675419635</v>
+        <v>0.6073740250203983</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.858237181676226</v>
+        <v>2.847156116163287</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.64128971723881</v>
+        <v>-3.769883330729151</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.025063311838277</v>
+        <v>0.9736258664421409</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5574336539966442</v>
+        <v>0.5389652114750791</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.816395815445536</v>
+        <v>2.805314749932597</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.634778750624498</v>
+        <v>-3.763372364114838</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.025267660038319</v>
+        <v>0.9738302146421827</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5574336539966442</v>
+        <v>0.5389652114750791</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.813995776999853</v>
+        <v>2.802914711486914</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.6157406229172</v>
+        <v>-3.744334236407541</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.029407630329483</v>
+        <v>0.9779701849333464</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4992500426654497</v>
+        <v>0.4807816001438846</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.775610329409381</v>
+        <v>2.764529263896442</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.66825642519202</v>
+        <v>-3.796850038682361</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.127695711053745</v>
+        <v>1.076258265657609</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4992500426654497</v>
+        <v>0.4807816001438846</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.894904731043571</v>
+        <v>2.883823665530632</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.6716647366266</v>
+        <v>-3.800258350116941</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.127165715466047</v>
+        <v>1.07572827006991</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5317666116748271</v>
+        <v>0.513298169153262</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.915248001435331</v>
+        <v>2.904166935922392</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.652308600732753</v>
+        <v>-3.780902214223094</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.140916700220511</v>
+        <v>1.089479254824375</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5317666116748271</v>
+        <v>0.513298169153262</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.921256531832257</v>
+        <v>2.910175466319318</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.504565630497751</v>
+        <v>-3.633159243988092</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.097964109591712</v>
+        <v>1.046526664195575</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6995739689097102</v>
+        <v>0.6811055263881451</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.919891167450387</v>
+        <v>2.908810101937447</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.588386851772449</v>
+        <v>-3.71698046526279</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.067229242613314</v>
+        <v>1.015791797217177</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6995739689097102</v>
+        <v>0.6811055263881451</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.922684788981868</v>
+        <v>2.911603723468928</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.582234145719664</v>
+        <v>-3.710827759210005</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.070352673426086</v>
+        <v>1.018915228029949</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.7057266749624945</v>
+        <v>0.6872582324409294</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.927038761005196</v>
+        <v>2.915957695492257</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.599043443870166</v>
+        <v>-3.727637057360507</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.062709430905995</v>
+        <v>1.011271985509859</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.6889173768119929</v>
+        <v>0.6704489342904278</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.916033658855006</v>
+        <v>2.904952593342067</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.536745445094044</v>
+        <v>-3.665339058584385</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.153964184213265</v>
+        <v>1.102526738817129</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.734211641086435</v>
+        <v>0.7157431985648699</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.009545771216492</v>
+        <v>2.998464705703553</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.334955247428886</v>
+        <v>-3.463548860919227</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.036972264993455</v>
+        <v>0.9855348195973188</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.9322298332555894</v>
+        <v>0.9137613907340243</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.930648688232111</v>
+        <v>2.919567622719172</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.385841960115081</v>
+        <v>-3.514435573605422</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.086907812241153</v>
+        <v>1.035470366845016</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8813431205693949</v>
+        <v>0.8628746780478298</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.97040689294257</v>
+        <v>2.959325827429631</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.299231217465274</v>
+        <v>-3.427824830955614</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.136179845417119</v>
+        <v>1.084742400020983</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9599688517745532</v>
+        <v>0.9415004092529881</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.032210067781709</v>
+        <v>3.021129002268769</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.359440515470558</v>
+        <v>-3.488034128960899</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.110632107039677</v>
+        <v>1.059194661643541</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8997595537692686</v>
+        <v>0.8812911112477035</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.99462046980321</v>
+        <v>2.983539404290271</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.310253866786207</v>
+        <v>-3.438847480276547</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.128798384553346</v>
+        <v>1.07736093915721</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8997595537692686</v>
+        <v>0.8812911112477035</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.993112087843138</v>
+        <v>2.982031022330199</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.265880735147638</v>
+        <v>-3.394474348637979</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.14641050464421</v>
+        <v>1.094973059248074</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9441326854078372</v>
+        <v>0.9256642428862721</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.019598834261715</v>
+        <v>3.008517768748777</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.288361086006523</v>
+        <v>-3.416954699496864</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.131812158439246</v>
+        <v>1.08037471304311</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9441326854078372</v>
+        <v>0.9256642428862721</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.013992628400306</v>
+        <v>3.002911562887367</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.240705355445467</v>
+        <v>-3.369298968935808</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.157256207691473</v>
+        <v>1.105818762295337</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.9917884159688928</v>
+        <v>0.9733199734473278</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.048967823764744</v>
+        <v>3.037886758251805</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.140187196946712</v>
+        <v>-3.268780810437053</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.2023558444657</v>
+        <v>1.150918399069564</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.092306574467647</v>
+        <v>1.073838131946082</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.114171092238721</v>
+        <v>3.103090026725782</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.12428186751436</v>
+        <v>-3.2528754810047</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.195472648714513</v>
+        <v>1.144035203318377</v>
       </c>
       <c r="F1980" t="n">
-        <v>1.013193913758409</v>
+        <v>0.9947254712368434</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.05345816828905</v>
+        <v>3.042377102776111</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.079443465905962</v>
+        <v>-3.208037079396302</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.217505711968501</v>
+        <v>1.166068266572365</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.017737346703278</v>
+        <v>0.9992689041817129</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.0602819306666</v>
+        <v>3.049200865153662</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.09894192214797</v>
+        <v>-3.227535535638311</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.213867269102776</v>
+        <v>1.162429823706639</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9696527054233737</v>
+        <v>0.9511842629018086</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.035592085529736</v>
+        <v>3.024511020016797</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.054739085062069</v>
+        <v>-3.18333269855241</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.237428006464973</v>
+        <v>1.185990561068837</v>
       </c>
       <c r="F1983" t="n">
-        <v>1.013855542509274</v>
+        <v>0.995387099987709</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.067993390309113</v>
+        <v>3.056912324796174</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.062298750899116</v>
+        <v>-3.190892364389457</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.232814140599402</v>
+        <v>1.181376695203266</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.068658946519093</v>
+        <v>1.050190503997528</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.099285433184253</v>
+        <v>3.088204367671314</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.904007333359844</v>
+        <v>-3.032600946850185</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.34737847279815</v>
+        <v>1.295941027402014</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.068658946519093</v>
+        <v>1.050190503997528</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.150533198367292</v>
+        <v>3.139452132854353</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.696365329725368</v>
+        <v>-2.824958943215709</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.428875978846194</v>
+        <v>1.377438533450058</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.27630095015357</v>
+        <v>1.257832507632004</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.273559105142231</v>
+        <v>3.262478039629292</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.64533323700284</v>
+        <v>-2.773926850493181</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.444237044173475</v>
+        <v>1.392799598777339</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.327333042876098</v>
+        <v>1.308864600354533</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.299126589014018</v>
+        <v>3.288045523501079</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.580109055875634</v>
+        <v>-2.708702669365975</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.487514120717063</v>
+        <v>1.436076675320926</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.392557224003303</v>
+        <v>1.374088781481738</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.355448501783046</v>
+        <v>3.344367436270107</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.5426820358045</v>
+        <v>-2.671275649294841</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.498445901044796</v>
+        <v>1.44700845564866</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.397808762032485</v>
+        <v>1.37934031951092</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.354560396899836</v>
+        <v>3.343479331386897</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.541324050830955</v>
+        <v>-2.669917664321296</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.500245887365455</v>
+        <v>1.448808441969319</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.472146887570304</v>
+        <v>1.453678445048739</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.400420064553767</v>
+        <v>3.389338999040828</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.512910787731071</v>
+        <v>-2.641504401221412</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.672168963626619</v>
+        <v>1.620731518230483</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.413171324823875</v>
+        <v>1.39470288230231</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.52559249792712</v>
+        <v>3.514511432414182</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.438128526706059</v>
+        <v>-2.566722140196399</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.822194777254441</v>
+        <v>1.770757331858305</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.487953585848887</v>
+        <v>1.469485143327322</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.690574763759946</v>
+        <v>3.679493698247006</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.412044442442251</v>
+        <v>-2.540638055932591</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.824336386973823</v>
+        <v>1.772898941577687</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.487953585848887</v>
+        <v>1.469485143327322</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.682282739773805</v>
+        <v>3.671201674260865</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.32416652933313</v>
+        <v>-2.452760142823471</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.857680747801251</v>
+        <v>1.806243302405115</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.603879228272238</v>
+        <v>1.585410785750673</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.750031320811595</v>
+        <v>3.738950255298656</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.315274067939847</v>
+        <v>-2.443867681430188</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.878792138085356</v>
+        <v>1.827354692689219</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.603879228272238</v>
+        <v>1.585410785750673</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.767585726538386</v>
+        <v>3.756504661025447</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.483750184909725</v>
+        <v>-2.612343798400066</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.803256738701989</v>
+        <v>1.751819293305852</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.575931392555658</v>
+        <v>1.557462950034093</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.742672072513021</v>
+        <v>3.731591007000082</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.037493992280285</v>
+        <v>-2.166087605770626</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.963028912941626</v>
+        <v>1.91159146754549</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.481212722886025</v>
+        <v>1.46274428036446</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.667110567899104</v>
+        <v>3.656029502386164</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.014772888597133</v>
+        <v>-2.143366502087473</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.962781376911792</v>
+        <v>1.911343931515656</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.481212722886025</v>
+        <v>1.46274428036446</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.657774590396008</v>
+        <v>3.646693524883069</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.143974701891175</v>
+        <v>-2.272568315381516</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.070006777445344</v>
+        <v>2.018569332049208</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.352010909591983</v>
+        <v>1.333542467070418</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.739159628270752</v>
+        <v>3.728078562757813</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.169849100365201</v>
+        <v>-2.298442713855541</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.09673484054938</v>
+        <v>2.045297395153244</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.396922518303724</v>
+        <v>1.378454075782159</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.803184415991443</v>
+        <v>3.792103350478504</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.162794410150027</v>
+        <v>-2.291388023640368</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.096232072624995</v>
+        <v>2.044794627228859</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.403977208518898</v>
+        <v>1.385508765997333</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.804092586110093</v>
+        <v>3.793011520597154</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.135843185823539</v>
+        <v>-2.26443679931388</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.117018716000332</v>
+        <v>2.065581270604195</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.418857554546617</v>
+        <v>1.400389112025052</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.823026947371466</v>
+        <v>3.811945881858526</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.157387413654326</v>
+        <v>-2.285981027144667</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.292504157012976</v>
+        <v>2.24106671161684</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.418857554546617</v>
+        <v>1.400389112025052</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.007130079516426</v>
+        <v>3.996049014003487</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.179795531459198</v>
+        <v>-2.308389144949539</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.275657604794021</v>
+        <v>2.224220159397885</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.418857554546617</v>
+        <v>1.400389112025052</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.999246774419419</v>
+        <v>3.98816570890648</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.208019767036799</v>
+        <v>-2.336613380527139</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.266421910112618</v>
+        <v>2.214984464716482</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.436834306997925</v>
+        <v>1.41836586447636</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.012086825439841</v>
+        <v>4.001005759926902</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.217460692925329</v>
+        <v>-2.346054306415669</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.318899257479053</v>
+        <v>2.267461812082917</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.559261424541317</v>
+        <v>1.540792982019752</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.141796813687723</v>
+        <v>4.130715748174784</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.306337324093803</v>
+        <v>-2.434930937584143</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.286239699556964</v>
+        <v>2.234802254160829</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.470384793372843</v>
+        <v>1.451916350851278</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.091361929531939</v>
+        <v>4.080280864019</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.382667301694708</v>
+        <v>-2.511260915185049</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.253819521410378</v>
+        <v>2.202382076014241</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.470384793372843</v>
+        <v>1.451916350851278</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.089473742425715</v>
+        <v>4.078392676912776</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.47633124637225</v>
+        <v>-2.60492485986259</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.211174173142223</v>
+        <v>2.159736727746087</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.376720848695302</v>
+        <v>1.358252406173737</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.028095605222052</v>
+        <v>4.017014539709113</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.637899671899505</v>
+        <v>-2.766493285389846</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.144980813141474</v>
+        <v>2.093543367745337</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.249937924897422</v>
+        <v>1.231469482375857</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.950459861153477</v>
+        <v>3.939378795640538</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.746200333769624</v>
+        <v>-2.874793947259965</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.114733955259344</v>
+        <v>2.063296509863208</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.249937924897422</v>
+        <v>1.231469482375857</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.963533268019396</v>
+        <v>3.952452202506457</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.764004305490368</v>
+        <v>-2.892597918980709</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.099617563353987</v>
+        <v>2.04818011795785</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.179403301992221</v>
+        <v>1.160934859470656</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.913217691059215</v>
+        <v>3.902136625546276</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.791905092599841</v>
+        <v>-2.920498706090182</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.086981289637199</v>
+        <v>2.035543844241063</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.144806377849287</v>
+        <v>1.126337935327721</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.890983577700456</v>
+        <v>3.879902512187517</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.914431195302735</v>
+        <v>-3.043024808793076</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.034735292533241</v>
+        <v>1.983297847137104</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.022280275146393</v>
+        <v>1.003811832624828</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.814232360055918</v>
+        <v>3.80315129454298</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.144945691488324</v>
+        <v>-3.273539304978665</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.009235453649509</v>
+        <v>1.957798008253373</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7917657789608039</v>
+        <v>0.7732973364392388</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.742629621935069</v>
+        <v>3.73154855642213</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.493690776712768</v>
+        <v>-3.622284390203109</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.010049138561579</v>
+        <v>1.958611693165442</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6830178250419061</v>
+        <v>0.664549382520341</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.817692568585577</v>
+        <v>3.806611503072638</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.647677194488908</v>
+        <v>-3.776270807979249</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.017434840596762</v>
+        <v>1.965997395200626</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6830178250419061</v>
+        <v>0.664549382520341</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.886672837731217</v>
+        <v>3.875591772218278</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.852276629351917</v>
+        <v>-3.980870242842258</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.92164626877168</v>
+        <v>1.870208823375543</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6830178250419061</v>
+        <v>0.664549382520341</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.872724039851338</v>
+        <v>3.861642974338399</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.104751783359641</v>
+        <v>-4.233345396849982</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.832526696224004</v>
+        <v>1.781089250827867</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6830178250419061</v>
+        <v>0.664549382520341</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.884594528906752</v>
+        <v>3.873513463393813</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.397647539839054</v>
+        <v>-4.526241153329394</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.716578928151183</v>
+        <v>1.665141482755046</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6830178250419061</v>
+        <v>0.664549382520341</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.885805063425696</v>
+        <v>3.874723997912757</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.584311667973862</v>
+        <v>-4.712905281464202</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.646035019124581</v>
+        <v>1.594597573728444</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6562788542173462</v>
+        <v>0.6378104116957811</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.873883423158281</v>
+        <v>3.862802357645342</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.730332354887824</v>
+        <v>-4.858925968378164</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.582704597095185</v>
+        <v>1.531267151699049</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.6471957624234892</v>
+        <v>0.6287273199019241</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.863511420818157</v>
+        <v>3.852430355305217</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.822046363997408</v>
+        <v>-4.95063997748775</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.708223050150395</v>
+        <v>1.656785604754259</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.6471957624234892</v>
+        <v>0.6287273199019241</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.025715477517201</v>
+        <v>4.014634412004262</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.853698023057378</v>
+        <v>-4.982291636547719</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.690409024490222</v>
+        <v>1.638971579094085</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.642027305179049</v>
+        <v>0.6235588626574839</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.017461041134351</v>
+        <v>4.006379975621412</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.935632841326261</v>
+        <v>-5.064226454816603</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.66786451475116</v>
+        <v>1.616427069355023</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6320925595919689</v>
+        <v>0.6136241170704038</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.021729611350594</v>
+        <v>4.010648545837655</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.037608963574669</v>
+        <v>-5.16620257706501</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.635999704307699</v>
+        <v>1.584562258911562</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.5301164373435613</v>
+        <v>0.5116479948219962</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.969469576457452</v>
+        <v>3.958388510944513</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.927602680097447</v>
+        <v>-5.056196293587789</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.672155104942763</v>
+        <v>1.620717659546627</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.5533210092608365</v>
+        <v>0.5348525667392714</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.975545206851992</v>
+        <v>3.964464141339053</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.784543104356521</v>
+        <v>-4.913136717846863</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.733628945961108</v>
+        <v>1.682191500564971</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.5613344358508158</v>
+        <v>0.5428659933292507</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.984603273527954</v>
+        <v>3.973522208015015</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.483096378884683</v>
+        <v>-4.611689992375025</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.861468519032379</v>
+        <v>1.810031073636242</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.862781161322653</v>
+        <v>0.8443127188010879</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.172732191693592</v>
+        <v>4.161651126180653</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.507686623119867</v>
+        <v>-4.636280236610209</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.852603599091016</v>
+        <v>1.801166153694879</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.862781161322653</v>
+        <v>0.8443127188010879</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.173703369446303</v>
+        <v>4.162622303933364</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.456648247113347</v>
+        <v>-4.585241860603689</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.87386185387338</v>
+        <v>1.822424408477243</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.862781161322653</v>
+        <v>0.8443127188010879</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.174546273826058</v>
+        <v>4.163465208313119</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.415508952246716</v>
+        <v>-4.544102565737058</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.909355670694177</v>
+        <v>1.857918225298041</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.9039204561892838</v>
+        <v>0.8854520136677188</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.218267949620182</v>
+        <v>4.207186884107244</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.318874040228076</v>
+        <v>-4.447467653718418</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.764193631625568</v>
+        <v>1.712756186229431</v>
       </c>
       <c r="F2033" t="n">
-        <v>1.000555368207924</v>
+        <v>0.9820869256863587</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.092432892955301</v>
+        <v>4.081351827442361</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.449454774758919</v>
+        <v>-4.57804838824926</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.715463381887195</v>
+        <v>1.664025936491059</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.8699746336770813</v>
+        <v>0.8515061911555162</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.017586496310759</v>
+        <v>4.00650543079782</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.284958440567957</v>
+        <v>-4.413552054058298</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.765688734639662</v>
+        <v>1.714251289243526</v>
       </c>
       <c r="F2035" t="n">
-        <v>1.034470967868043</v>
+        <v>1.016002525346478</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.10071111590142</v>
+        <v>4.089630050388481</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.207859839026084</v>
+        <v>-4.336453452516426</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.795715885692841</v>
+        <v>1.744278440296704</v>
       </c>
       <c r="F2036" t="n">
-        <v>1.034470967868043</v>
+        <v>1.016002525346478</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.099898826337849</v>
+        <v>4.08881776082491</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.218245033915974</v>
+        <v>-4.346838647406315</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.801430586861958</v>
+        <v>1.749993141465821</v>
       </c>
       <c r="F2037" t="n">
-        <v>1.024085772978154</v>
+        <v>1.005617330456589</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.103536488528988</v>
+        <v>4.092455423016049</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.236833192638199</v>
+        <v>-4.36542680612854</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.864832329149493</v>
+        <v>1.813394883753356</v>
       </c>
       <c r="F2038" t="n">
-        <v>1.005497614255928</v>
+        <v>0.9870291717343633</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.163220599072078</v>
+        <v>4.152139533559138</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.237131739334234</v>
+        <v>-4.365725352824576</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.861581921289377</v>
+        <v>1.810144475893241</v>
       </c>
       <c r="F2039" t="n">
-        <v>1.005199067559893</v>
+        <v>0.9867306250383274</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.159910481872755</v>
+        <v>4.148829416359815</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.136308605643807</v>
+        <v>-4.264902219134148</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.90644206970494</v>
+        <v>1.855004624308803</v>
       </c>
       <c r="F2040" t="n">
-        <v>1.017663283044246</v>
+        <v>0.9991948405226814</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.171919906102758</v>
+        <v>4.160838840589819</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-3.945527244891399</v>
+        <v>-4.074120858381741</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.982883867484446</v>
+        <v>1.931446422088309</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.208444643796654</v>
+        <v>1.189976201275089</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.286517976032746</v>
+        <v>4.275436910519807</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.838563887041977</v>
+        <v>-3.96715750053232</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.005506056361811</v>
+        <v>1.954068610965674</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.266909251756455</v>
+        <v>1.24844080923489</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.301433586546223</v>
+        <v>4.290352521033284</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.783233299140215</v>
+        <v>-3.911826912630558</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.062605228134574</v>
+        <v>2.011167782738438</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.322239839658217</v>
+        <v>1.303771397136652</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.36959887589934</v>
+        <v>4.358517810386401</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.771179172227253</v>
+        <v>-3.899772785717595</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.061113446801198</v>
+        <v>2.00967600140506</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.33429396657118</v>
+        <v>1.315825524049615</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.370517919948554</v>
+        <v>4.359436854435615</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.812334291795473</v>
+        <v>-3.940927905285816</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.046532029158045</v>
+        <v>1.995094583761908</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.293138847002959</v>
+        <v>1.274670404481394</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.347705478391758</v>
+        <v>4.336624412878819</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.744285729103944</v>
+        <v>-3.872879342594286</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.086602480112539</v>
+        <v>2.035165034716402</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.361187409694489</v>
+        <v>1.342718967172924</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.401385641884558</v>
+        <v>4.390304576371619</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-3.975886122273445</v>
+        <v>-4.104479735763787</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.014164993018333</v>
+        <v>1.962727547622196</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.361187409694489</v>
+        <v>1.342718967172924</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.421588312058153</v>
+        <v>4.410507246545214</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.025937667802664</v>
+        <v>-4.154531281293007</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.977750610873527</v>
+        <v>1.92631316547739</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.361187409694489</v>
+        <v>1.342718967172924</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.405194548125035</v>
+        <v>4.394113482612095</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.201044500379108</v>
+        <v>-4.329638113869452</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.867959791436416</v>
+        <v>1.816522346040279</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.361187409694489</v>
+        <v>1.342718967172924</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.365446461718501</v>
+        <v>4.354365396205562</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.004944346948585</v>
+        <v>-4.133537960438929</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.953422471805565</v>
+        <v>1.901985026409428</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.557287563125012</v>
+        <v>1.538819120603447</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.490129172773755</v>
+        <v>4.479048107260816</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.851918954835301</v>
+        <v>-3.980512568325645</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.113803628223783</v>
+        <v>2.062366182827646</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.710312955238296</v>
+        <v>1.691844512716731</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.68111540761463</v>
+        <v>4.67003434210169</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.880226268708571</v>
+        <v>-4.008819882198915</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.289946927582768</v>
+        <v>2.238509482186631</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.710312955238296</v>
+        <v>1.691844512716731</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.868581632522922</v>
+        <v>4.857500567009984</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.046819493822094</v>
+        <v>-4.175413107312437</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.192712588891442</v>
+        <v>2.141275143495304</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.543719730124774</v>
+        <v>1.525251287603208</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.738028648808892</v>
+        <v>4.726947583295953</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.023783700460528</v>
+        <v>-4.152377313950871</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.205603308897786</v>
+        <v>2.154165863501649</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.543719730124774</v>
+        <v>1.525251287603208</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.74170505147061</v>
+        <v>4.730623985957671</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-3.994537720004832</v>
+        <v>-4.123131333495174</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.214919756203559</v>
+        <v>2.163482310807423</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.543719730124774</v>
+        <v>1.525251287603208</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.739323106594105</v>
+        <v>4.728242041081166</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.101463267882683</v>
+        <v>-4.230056881373025</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.169442776210054</v>
+        <v>2.118005330813917</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.436794182246922</v>
+        <v>1.418325739725357</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.672461017025029</v>
+        <v>4.66137995151209</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.246481826389932</v>
+        <v>-4.375075439880274</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.112864154950389</v>
+        <v>2.061426709554252</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.291775623739674</v>
+        <v>1.273307181218109</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.586878684063914</v>
+        <v>4.575797618550975</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.364823592174649</v>
+        <v>-4.493417205664992</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.165458687894255</v>
+        <v>2.114021242498118</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.302461662302564</v>
+        <v>1.283993219780999</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.693221546459401</v>
+        <v>4.682140480946462</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.416234014495357</v>
+        <v>-4.5448276279857</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.142680216091911</v>
+        <v>2.091242770695774</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.302461662302564</v>
+        <v>1.283993219780999</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.69100724358534</v>
+        <v>4.679926178072401</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.495653465703109</v>
+        <v>-4.624247079193451</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.110815563683099</v>
+        <v>2.059378118286962</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.302461662302564</v>
+        <v>1.283993219780999</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.690910371659629</v>
+        <v>4.67982930614669</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.591116463620327</v>
+        <v>-4.719710077110669</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.072624258074255</v>
+        <v>2.021186812678118</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.302461662302564</v>
+        <v>1.283993219780999</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.690904265217672</v>
+        <v>4.679823199704733</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.526740552769612</v>
+        <v>-4.655334166259954</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.096471018977152</v>
+        <v>2.045033573581015</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.366837573153279</v>
+        <v>1.348369130631714</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.727626208290712</v>
+        <v>4.716545142777773</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.582109714901805</v>
+        <v>-4.710703328392148</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.080057171872001</v>
+        <v>2.028619726475864</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.366837573153279</v>
+        <v>1.348369130631714</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.733360026038438</v>
+        <v>4.722278960525499</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.627547494732632</v>
+        <v>-4.756141108222975</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.061420423282602</v>
+        <v>2.009982977886466</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.32399258247512</v>
+        <v>1.305524139953554</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.707191394974475</v>
+        <v>4.696110329461536</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.539340660585054</v>
+        <v>-4.667934274075397</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.116577549791952</v>
+        <v>2.065140104395815</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.32399258247512</v>
+        <v>1.305524139953554</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.727065787824794</v>
+        <v>4.715984722311855</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.433305665379745</v>
+        <v>-4.561899278870087</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.142692248398804</v>
+        <v>2.091254803002667</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.32399258247512</v>
+        <v>1.305524139953554</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.710766488349522</v>
+        <v>4.699685422836582</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.25009400224665</v>
+        <v>-4.378687615736992</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.218407863116088</v>
+        <v>2.16697041771995</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.32399258247512</v>
+        <v>1.305524139953554</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.713197437813568</v>
+        <v>4.702116372300628</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.178372555232799</v>
+        <v>-4.306966168723141</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.212887627769518</v>
+        <v>2.161450182373381</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.39571402948897</v>
+        <v>1.377245586967405</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.722021491869768</v>
+        <v>4.710940426356829</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.155999529625093</v>
+        <v>-4.284593143115435</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.168752583933772</v>
+        <v>2.117315138537635</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.406969780601872</v>
+        <v>1.388501338080307</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.67569068845868</v>
+        <v>4.664609622945741</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.189015825535837</v>
+        <v>-4.31760943902618</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.340744270454829</v>
+        <v>2.289306825058692</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.33753240393512</v>
+        <v>1.319063961413555</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.819226467343984</v>
+        <v>4.808145401831045</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.177488189886229</v>
+        <v>-4.306081803376571</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.337276550542922</v>
+        <v>2.285839105146785</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.396533062136483</v>
+        <v>1.378064619614918</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.84654808809305</v>
+        <v>4.835467022580112</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.274829691228597</v>
+        <v>-4.40342330471894</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.302008062527762</v>
+        <v>2.250570617131626</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.352112879970994</v>
+        <v>1.333644437449429</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.823564091315546</v>
+        <v>4.812483025802607</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.360685720568564</v>
+        <v>-4.489279334058907</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.268916732984614</v>
+        <v>2.217479287588477</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.309736810744859</v>
+        <v>1.291268368223294</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.799389531972704</v>
+        <v>4.788308466459765</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.369522517984683</v>
+        <v>-4.498116131475026</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.247801215838668</v>
+        <v>2.196363770442531</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.302294638103509</v>
+        <v>1.283826195581943</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.777343430208395</v>
+        <v>4.766262364695456</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.460905080550142</v>
+        <v>-4.589498694040484</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.221412701857534</v>
+        <v>2.169975256461397</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.265729753384164</v>
+        <v>1.247261310862599</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.765569010421838</v>
+        <v>4.754487944908899</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.449198362563136</v>
+        <v>-4.577791976053478</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.328223646876604</v>
+        <v>2.276786201480467</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.27743647137117</v>
+        <v>1.258968028849605</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.874721299038309</v>
+        <v>4.86364023352537</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.349534858479474</v>
+        <v>-4.478128471969816</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.371121387241474</v>
+        <v>2.319683941845337</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.340623554574857</v>
+        <v>1.322155112053292</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.915665887691926</v>
+        <v>4.904584822178986</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.359850956645825</v>
+        <v>-4.488444570136168</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.579899781252991</v>
+        <v>2.528462335856854</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.340623554574857</v>
+        <v>1.322155112053292</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.128570720969984</v>
+        <v>5.117489655457044</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.359756988628453</v>
+        <v>-4.488350602118795</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.57911603537203</v>
+        <v>2.527678589975893</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.340993415922175</v>
+        <v>1.32252497340061</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.127971304690464</v>
+        <v>5.116890239177525</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.366975812828297</v>
+        <v>-4.49556942631864</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.570460491636446</v>
+        <v>2.519023046240309</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.340993415922175</v>
+        <v>1.32252497340061</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.122203290634818</v>
+        <v>5.111122225121878</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.366027389710259</v>
+        <v>-4.494621003200601</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.570839860883662</v>
+        <v>2.519402415487524</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.340993415922175</v>
+        <v>1.32252497340061</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.122203290634818</v>
+        <v>5.111122225121878</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.523095847965882</v>
+        <v>-4.651689461456225</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.520740085562504</v>
+        <v>2.469302640166367</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.340993415922175</v>
+        <v>1.32252497340061</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.134930898615909</v>
+        <v>5.12384983310297</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.51710360117707</v>
+        <v>-4.645697214667414</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.525082982702417</v>
+        <v>2.473645537306279</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.340993415922175</v>
+        <v>1.32252497340061</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.136876897040297</v>
+        <v>5.125795831527358</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.428545640046303</v>
+        <v>-4.557139253536646</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.554160303172492</v>
+        <v>2.502722857776355</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.340993415922175</v>
+        <v>1.32252497340061</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.130531033058066</v>
+        <v>5.119449967545127</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.410786562543229</v>
+        <v>-4.539380176033572</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.560572611612717</v>
+        <v>2.50913516621658</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.340993415922175</v>
+        <v>1.32252497340061</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.129839710497063</v>
+        <v>5.118758644984123</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.311156411494161</v>
+        <v>-4.439750024984504</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.613206857940932</v>
+        <v>2.561769412544794</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.440623566971242</v>
+        <v>1.422155124449677</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.20239998703509</v>
+        <v>5.19131892152215</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.360555920183172</v>
+        <v>-4.489149533673515</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.782601319964053</v>
+        <v>2.731163874567916</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.450882400402987</v>
+        <v>1.432413957881422</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.397709552592863</v>
+        <v>5.386628487079924</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.153871446540796</v>
+        <v>-4.282465060031139</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.852463782523866</v>
+        <v>2.801026337127729</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.657566874045363</v>
+        <v>1.639098431523798</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.50890890988115</v>
+        <v>5.497827844368211</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.979602843474773</v>
+        <v>3.971782112853617</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.188028341538322</v>
+        <v>-4.316621955028666</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.84080253817896</v>
+        <v>2.789365092782823</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.57398310450455</v>
+        <v>1.555514661982985</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.460760161810768</v>
+        <v>5.449679096297829</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240917.xlsx
+++ b/tame_output/ON/bt/strategyON_20240917.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>70.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>113.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>140.0%</t>
+          <t>177.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.2%</t>
+          <t>-70.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.2%</t>
+          <t>422.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-593.2%</t>
+          <t>-577.2%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-97.3%</t>
+          <t>-90.9%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>-60.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-343.2%</t>
+          <t>-330.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-68.4%</t>
+          <t>-58.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>120.5%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,27 +1476,27 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>42.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2089"/>
+  <dimension ref="A1:G2090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.226054034658109</v>
+        <v>-7.338778816372826</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2606819359262631</v>
+        <v>0.2155920232403763</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9476778951207698</v>
+        <v>-1.060402676835486</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.582853237030793</v>
+        <v>2.515218368001963</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.062654163718746</v>
+        <v>-7.175378945433463</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.325408705522765</v>
+        <v>0.2803187928368782</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7842780241814074</v>
+        <v>-0.8970028058961237</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.680259980815167</v>
+        <v>2.612625111786337</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.829172941489148</v>
+        <v>-6.941897723203865</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4267256232524566</v>
+        <v>0.3816357105665698</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5507968019518088</v>
+        <v>-0.6635215836665251</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.828273142990779</v>
+        <v>2.760638273961949</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.679506550481633</v>
+        <v>-6.79223133219635</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4836999693425037</v>
+        <v>0.4386100566566169</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4578933107092729</v>
+        <v>-0.5706180924239892</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.881123027423341</v>
+        <v>2.813488158394511</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.547231076850746</v>
+        <v>-6.659955858565463</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4378709448020128</v>
+        <v>0.392781032116126</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3256178370783862</v>
+        <v>-0.4383426187931025</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.861749097609028</v>
+        <v>2.794114228580198</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.375369861285844</v>
+        <v>-6.488094643000561</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5094304917156105</v>
+        <v>0.4643405790297237</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1537566215134833</v>
+        <v>-0.2664814032281997</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.967680887635606</v>
+        <v>2.900046018606776</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.290405194556524</v>
+        <v>-6.403129976271241</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5563226996309973</v>
+        <v>0.5112327869451101</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06879195478416378</v>
+        <v>-0.1815167364988801</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.031566028896857</v>
+        <v>2.963931159868027</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.395995184329628</v>
+        <v>-6.508719966044346</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3861107741225367</v>
+        <v>0.3410208614366494</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1743819445572681</v>
+        <v>-0.2871067262719845</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.840236105433775</v>
+        <v>2.772601236404946</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.327760599704201</v>
+        <v>-6.440485381418918</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.461948949849794</v>
+        <v>0.4168590371639072</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1559666216847321</v>
+        <v>-0.2686914033994485</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.899829641034383</v>
+        <v>2.832194772005554</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.179820558296601</v>
+        <v>-6.292545340011319</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4045041577744266</v>
+        <v>0.3594142450885398</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1356457057761746</v>
+        <v>-0.2483704874908909</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.795401381941111</v>
+        <v>2.727766512912281</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.126851036042613</v>
+        <v>-6.239575817757331</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4169779804225442</v>
+        <v>0.3718880677366569</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.0826761835221857</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.818469109040026</v>
+        <v>2.750834240011196</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.961062840082322</v>
+        <v>-6.07378762179704</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4763326467115672</v>
+        <v>0.4312427340256799</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.0826761835221857</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.811508496944933</v>
+        <v>2.743873627916103</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.927699633603553</v>
+        <v>-6.040424415318271</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5041402836842179</v>
+        <v>0.4590503709983307</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.0826761835221857</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.825970851326076</v>
+        <v>2.758335982297246</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.819440496481032</v>
+        <v>-5.932165278195749</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5419760589924216</v>
+        <v>0.4968861463065344</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.0826761835221857</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.820502971785271</v>
+        <v>2.752868102756441</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.696149361663901</v>
+        <v>-5.808874143378619</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5887906069298507</v>
+        <v>0.5437006942439635</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.0406149512949448</v>
+        <v>-0.07210983041977154</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.891975746686126</v>
+        <v>2.824340877657296</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.643452494532609</v>
+        <v>-5.756177276247327</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6175703320196924</v>
+        <v>0.5724804193338051</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.09331181842623598</v>
+        <v>-0.01941296328848036</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.931294845202226</v>
+        <v>2.863659976173396</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.399687052549165</v>
+        <v>-5.512411834263883</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7108572171601208</v>
+        <v>0.6657673044742336</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.09331181842623598</v>
+        <v>-0.01941296328848036</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.927075553549277</v>
+        <v>2.859440684520447</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.309911380172693</v>
+        <v>-5.422636161887411</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7488918000307256</v>
+        <v>0.7038018873448384</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.154911263340546</v>
+        <v>0.04218648162582966</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.966159534417879</v>
+        <v>2.898524665389049</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.060060986223618</v>
+        <v>-5.172785767938336</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8415740325940577</v>
+        <v>0.7964841199081705</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.154911263340546</v>
+        <v>0.04218648162582966</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.958901609401581</v>
+        <v>2.891266740372751</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.884168893756186</v>
+        <v>-4.996893675470904</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9155299931016794</v>
+        <v>0.8704400804157921</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.154911263340546</v>
+        <v>0.04218648162582966</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.962500732922229</v>
+        <v>2.8948658638934</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.712722430733723</v>
+        <v>-4.825447212448441</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9974360843652184</v>
+        <v>0.9523461716793311</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3263577263630091</v>
+        <v>0.2136329446482928</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.078696116790261</v>
+        <v>3.011061247761432</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.632700143624602</v>
+        <v>-4.74542492533932</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.028465476825164</v>
+        <v>0.9833755641392765</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.4063800134721301</v>
+        <v>0.2936552317574138</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.125729966672031</v>
+        <v>3.058095097643201</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.569064401390667</v>
+        <v>-4.681789183105385</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.058614574773055</v>
+        <v>1.013524662087168</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4700157557060646</v>
+        <v>0.3572909739913483</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.168606213066709</v>
+        <v>3.100971344037879</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.475367083174272</v>
+        <v>-4.58809186488899</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.077287760843408</v>
+        <v>1.032197848157521</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4700157557060646</v>
+        <v>0.3572909739913483</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.149800471850504</v>
+        <v>3.082165602821675</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.485869706239561</v>
+        <v>-4.598594487954279</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.07482978824217</v>
+        <v>1.029739875556283</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4595131326407758</v>
+        <v>0.3467883509260594</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.145241974636209</v>
+        <v>3.077607105607379</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.373383445570687</v>
+        <v>-4.486108227285404</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.12375360634454</v>
+        <v>1.078663693658653</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4595131326407758</v>
+        <v>0.3467883509260594</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.149171288471029</v>
+        <v>3.081536419442199</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.355669758692821</v>
+        <v>-4.468394540407539</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.131517665013027</v>
+        <v>1.086427752327139</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4626944615376926</v>
+        <v>0.3499696798229762</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.151758669726519</v>
+        <v>3.084123800697689</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.232195487379803</v>
+        <v>-4.344920269094521</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.177905444758227</v>
+        <v>1.13281553207234</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4626944615376926</v>
+        <v>0.3499696798229762</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.148756740946512</v>
+        <v>3.081121871917682</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.012174689342793</v>
+        <v>-4.12489947105751</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.267492800983645</v>
+        <v>1.222402888297758</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6039143066056728</v>
+        <v>0.4911895248909565</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.235067684997914</v>
+        <v>3.167432815969085</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.879307000279514</v>
+        <v>-3.992031781994232</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.33653405941078</v>
+        <v>1.291444146724893</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6039143066056728</v>
+        <v>0.4911895248909565</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.250961867799738</v>
+        <v>3.183326998770908</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.759133916915015</v>
+        <v>-3.871858698629733</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.385749137196882</v>
+        <v>1.340659224510995</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7240873899701717</v>
+        <v>0.6113626082554554</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.324211562258739</v>
+        <v>3.256576693229909</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.623880555585038</v>
+        <v>-3.736605337299756</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.449938584290312</v>
+        <v>1.404848671604425</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8593407513001489</v>
+        <v>0.7466159695854325</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.415451681618165</v>
+        <v>3.347816812589335</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.683755382942731</v>
+        <v>-3.796480164657448</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.412026144748661</v>
+        <v>1.366936232062774</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7994659239424567</v>
+        <v>0.6867411422277404</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.365564276604976</v>
+        <v>3.297929407576146</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.563935152031893</v>
+        <v>-3.676659933746611</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.475243406347205</v>
+        <v>1.430153493661318</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7994659239424567</v>
+        <v>0.6867411422277404</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.380853445839184</v>
+        <v>3.313218576810355</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.566404858493699</v>
+        <v>-3.679129640208417</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.381899723084924</v>
+        <v>1.336809810399037</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7969962174806506</v>
+        <v>0.6842714357659343</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.287015821284542</v>
+        <v>3.219380952255712</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.634775044817709</v>
+        <v>-3.747499826532427</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.273813510040621</v>
+        <v>1.228723597354734</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8062719165168656</v>
+        <v>0.6935471348021492</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.211843102191573</v>
+        <v>3.144208233162743</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.74664732444386</v>
+        <v>-3.859372106158578</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.219501306822052</v>
+        <v>1.174411394136165</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8062719165168656</v>
+        <v>0.6935471348021492</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.202279810823464</v>
+        <v>3.134644941794634</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.730672658957592</v>
+        <v>-3.84339744067231</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.192465697940587</v>
+        <v>1.1473757852547</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8062719165168656</v>
+        <v>0.6935471348021492</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.168854335747491</v>
+        <v>3.101219466718661</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.555198399165123</v>
+        <v>-3.66792318087984</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.267222633849362</v>
+        <v>1.222132721163475</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8062719165168656</v>
+        <v>0.6935471348021492</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.173421567739279</v>
+        <v>3.105786698710449</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.547274024580208</v>
+        <v>-3.659998806294926</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.246134412444535</v>
+        <v>1.201044499758648</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8062719165168656</v>
+        <v>0.6935471348021492</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.149163596500486</v>
+        <v>3.081528727471656</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.540995822010359</v>
+        <v>-3.653720603725077</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.177184006873925</v>
+        <v>1.132094094188037</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8125501190867146</v>
+        <v>0.6998253373719983</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.081468831443845</v>
+        <v>3.013833962415015</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.481143202806636</v>
+        <v>-3.593867984521354</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.211297440987546</v>
+        <v>1.166207528301659</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8125501190867146</v>
+        <v>0.6998253373719983</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.091641217875978</v>
+        <v>3.024006348847148</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.394899739780259</v>
+        <v>-3.507624521494977</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.240741096771957</v>
+        <v>1.19565118408607</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8125501190867146</v>
+        <v>0.6998253373719983</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.086587488449838</v>
+        <v>3.018952619421008</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.440206559179239</v>
+        <v>-3.552931340893957</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.214394144456891</v>
+        <v>1.169304231771004</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7717399560774838</v>
+        <v>0.6590151743627675</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.053877166088825</v>
+        <v>2.986242297059995</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.46923966388154</v>
+        <v>-3.581964445596258</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.203332775609072</v>
+        <v>1.158242862923185</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7717399560774838</v>
+        <v>0.6590151743627675</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.054429039121926</v>
+        <v>2.986794170093097</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.376429182430681</v>
+        <v>-3.489153964145399</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.169729660080781</v>
+        <v>1.124639747394894</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8645504375283432</v>
+        <v>0.7518256558136268</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.039388019883808</v>
+        <v>2.971753150854978</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.420818651760109</v>
+        <v>-3.533543433474827</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.153847348273611</v>
+        <v>1.108757435587724</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8201609681989155</v>
+        <v>0.7074361864841991</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.014627814210752</v>
+        <v>2.946992945181922</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.400314957874611</v>
+        <v>-3.513039739589329</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.157124534339533</v>
+        <v>1.112034621653646</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.8406646620844128</v>
+        <v>0.7279398803696965</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.022005739053773</v>
+        <v>2.954370870024944</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.440239052457184</v>
+        <v>-3.552963834171901</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.146646192337171</v>
+        <v>1.101556279651284</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.8406646620844128</v>
+        <v>0.7279398803696965</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.027497034884441</v>
+        <v>2.959862165855611</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.468019450358537</v>
+        <v>-3.580744232073255</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.147031234945169</v>
+        <v>1.101941322259282</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.8128842641830598</v>
+        <v>0.7001594824683435</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.022325997912168</v>
+        <v>2.954691128883338</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.586400123088675</v>
+        <v>-3.699124904803393</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9380346858537671</v>
+        <v>0.8929447731678799</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7456664120320836</v>
+        <v>0.6329416303173673</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.820351006622236</v>
+        <v>2.752716137593405</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.695014201532006</v>
+        <v>-3.807738983246724</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.01473871519564</v>
+        <v>0.9696488025097532</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7456664120320836</v>
+        <v>0.6329416303173673</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.940500667341441</v>
+        <v>2.872865798312611</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.659605163283863</v>
+        <v>-3.772329944998581</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.04341535659722</v>
+        <v>0.9983254439113332</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7456664120320836</v>
+        <v>0.6329416303173673</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.955013693443764</v>
+        <v>2.887378824414934</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.668066331939325</v>
+        <v>-3.780791113654042</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.037450330477405</v>
+        <v>0.9923604177915175</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7372052433766225</v>
+        <v>0.6244804616619062</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.947356433592856</v>
+        <v>2.879721564564026</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.490950001904158</v>
+        <v>-3.603674783618876</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.105025891336773</v>
+        <v>1.059935978650886</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7372052433766225</v>
+        <v>0.6244804616619062</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.944085462438158</v>
+        <v>2.876450593409329</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.536042246737704</v>
+        <v>-3.648767028452422</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.087672385165268</v>
+        <v>1.042582472479381</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6753092002072327</v>
+        <v>0.5625844184925164</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.907631228298438</v>
+        <v>2.839996359269608</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.356666825498936</v>
+        <v>-3.469391607213654</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.15320952896719</v>
+        <v>1.108119616281303</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8320859583779514</v>
+        <v>0.7193611766632351</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.995484258507283</v>
+        <v>2.927849389478454</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.401681039019543</v>
+        <v>-3.514405820734261</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.116011298890537</v>
+        <v>1.07092138620465</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.8017370630633468</v>
+        <v>0.6890122813486305</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.95808237665011</v>
+        <v>2.890447507621281</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.668685549291978</v>
+        <v>-3.542570212848694</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.014901057120508</v>
+        <v>1.065347191697822</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6073740250203983</v>
+        <v>0.6271880390725921</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.847156116163287</v>
+        <v>2.859044524594603</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.769883330729151</v>
+        <v>-3.643767994285867</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9736258664421409</v>
+        <v>1.024072001019455</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5389652114750791</v>
+        <v>0.558779225527273</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.805314749932597</v>
+        <v>2.817203158363913</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.763372364114838</v>
+        <v>-3.637257027671554</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9738302146421827</v>
+        <v>1.024276349219496</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5389652114750791</v>
+        <v>0.558779225527273</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.802914711486914</v>
+        <v>2.81480311991823</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.744334236407541</v>
+        <v>-3.618218899964257</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9779701849333464</v>
+        <v>1.02841631951066</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4807816001438846</v>
+        <v>0.5005956141960785</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.764529263896442</v>
+        <v>2.776417672327758</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.796850038682361</v>
+        <v>-3.670734702239077</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.076258265657609</v>
+        <v>1.126704400234922</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4807816001438846</v>
+        <v>0.5005956141960785</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.883823665530632</v>
+        <v>2.895712073961949</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.800258350116941</v>
+        <v>-3.674143013673656</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.07572827006991</v>
+        <v>1.126174404647224</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.513298169153262</v>
+        <v>0.5331121832054558</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.904166935922392</v>
+        <v>2.916055344353708</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.780902214223094</v>
+        <v>-3.654786877779809</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.089479254824375</v>
+        <v>1.139925389401689</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.513298169153262</v>
+        <v>0.5331121832054558</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.910175466319318</v>
+        <v>2.922063874750634</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.633159243988092</v>
+        <v>-3.507043907544807</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.046526664195575</v>
+        <v>1.096972798772889</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6811055263881451</v>
+        <v>0.700919540440339</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.908810101937447</v>
+        <v>2.920698510368764</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.71698046526279</v>
+        <v>-3.590865128819505</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.015791797217177</v>
+        <v>1.066237931794491</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6811055263881451</v>
+        <v>0.700919540440339</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.911603723468928</v>
+        <v>2.923492131900245</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.710827759210005</v>
+        <v>-3.584712422766721</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.018915228029949</v>
+        <v>1.069361362607263</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6872582324409294</v>
+        <v>0.7070722464931233</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.915957695492257</v>
+        <v>2.927846103923573</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.727637057360507</v>
+        <v>-3.601521720917222</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.011271985509859</v>
+        <v>1.061718120087173</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.6704489342904278</v>
+        <v>0.6902629483426217</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.904952593342067</v>
+        <v>2.916841001773383</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.665339058584385</v>
+        <v>-3.5392237221411</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.102526738817129</v>
+        <v>1.152972873394442</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7157431985648699</v>
+        <v>0.7355572126170637</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.998464705703553</v>
+        <v>3.010353114134869</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.463548860919227</v>
+        <v>-3.337433524475943</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9855348195973188</v>
+        <v>1.035980954174633</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.9137613907340243</v>
+        <v>0.9335754047862181</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.919567622719172</v>
+        <v>2.931456031150489</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.514435573605422</v>
+        <v>-3.388320237162137</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.035470366845016</v>
+        <v>1.08591650142233</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8628746780478298</v>
+        <v>0.8826886921000237</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.959325827429631</v>
+        <v>2.971214235860947</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.427824830955614</v>
+        <v>-3.30170949451233</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.084742400020983</v>
+        <v>1.135188534598297</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9415004092529881</v>
+        <v>0.9613144233051819</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.021129002268769</v>
+        <v>3.033017410700086</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.488034128960899</v>
+        <v>-3.361918792517614</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.059194661643541</v>
+        <v>1.109640796220854</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8812911112477035</v>
+        <v>0.9011051252998974</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.983539404290271</v>
+        <v>2.995427812721587</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.438847480276547</v>
+        <v>-3.312732143833263</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.07736093915721</v>
+        <v>1.127807073734524</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8812911112477035</v>
+        <v>0.9011051252998974</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.982031022330199</v>
+        <v>2.993919430761515</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.394474348637979</v>
+        <v>-3.268359012194694</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.094973059248074</v>
+        <v>1.145419193825387</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9256642428862721</v>
+        <v>0.945478256938466</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.008517768748777</v>
+        <v>3.020406177180093</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.416954699496864</v>
+        <v>-3.290839363053579</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.08037471304311</v>
+        <v>1.130820847620424</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9256642428862721</v>
+        <v>0.945478256938466</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.002911562887367</v>
+        <v>3.014799971318683</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.369298968935808</v>
+        <v>-3.243183632492523</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.105818762295337</v>
+        <v>1.156264896872651</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.9733199734473278</v>
+        <v>0.9931339874995215</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.037886758251805</v>
+        <v>3.049775166683121</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.268780810437053</v>
+        <v>-3.142665473993769</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.150918399069564</v>
+        <v>1.201364533646877</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.073838131946082</v>
+        <v>1.093652145998276</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.103090026725782</v>
+        <v>3.114978435157099</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.2528754810047</v>
+        <v>-3.126760144561416</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.144035203318377</v>
+        <v>1.194481337895691</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9947254712368434</v>
+        <v>1.014539485289037</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.042377102776111</v>
+        <v>3.054265511207428</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.208037079396302</v>
+        <v>-3.081921742953018</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.166068266572365</v>
+        <v>1.216514401149678</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9992689041817129</v>
+        <v>1.019082918233907</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.049200865153662</v>
+        <v>3.061089273584978</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.227535535638311</v>
+        <v>-3.101420199195026</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.162429823706639</v>
+        <v>1.212875958283953</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9511842629018086</v>
+        <v>0.9709982769540024</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.024511020016797</v>
+        <v>3.036399428448113</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.18333269855241</v>
+        <v>-3.057217362109126</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.185990561068837</v>
+        <v>1.236436695646151</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.995387099987709</v>
+        <v>1.015201114039903</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.056912324796174</v>
+        <v>3.068800733227491</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.190892364389457</v>
+        <v>-3.064777027946173</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.181376695203266</v>
+        <v>1.231822829780579</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.050190503997528</v>
+        <v>1.070004518049722</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.088204367671314</v>
+        <v>3.10009277610263</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.032600946850185</v>
+        <v>-2.906485610406901</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.295941027402014</v>
+        <v>1.346387161979328</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.050190503997528</v>
+        <v>1.070004518049722</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.139452132854353</v>
+        <v>3.151340541285669</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.824958943215709</v>
+        <v>-2.698843606772424</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.377438533450058</v>
+        <v>1.427884668027372</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.257832507632004</v>
+        <v>1.277646521684198</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.262478039629292</v>
+        <v>3.274366448060608</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.773926850493181</v>
+        <v>-2.647811514049896</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.392799598777339</v>
+        <v>1.443245733354653</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.308864600354533</v>
+        <v>1.328678614406726</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.288045523501079</v>
+        <v>3.299933931932395</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.708702669365975</v>
+        <v>-2.58258733292269</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.436076675320926</v>
+        <v>1.48652280989824</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.374088781481738</v>
+        <v>1.393902795533932</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.344367436270107</v>
+        <v>3.356255844701423</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.671275649294841</v>
+        <v>-2.545160312851557</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.44700845564866</v>
+        <v>1.497454590225974</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.37934031951092</v>
+        <v>1.399154333563114</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.343479331386897</v>
+        <v>3.355367739818213</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.669917664321296</v>
+        <v>-2.543802327878011</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.448808441969319</v>
+        <v>1.499254576546632</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.453678445048739</v>
+        <v>1.473492459100932</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.389338999040828</v>
+        <v>3.401227407472144</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.641504401221412</v>
+        <v>-2.515389064778128</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.620731518230483</v>
+        <v>1.671177652807797</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.39470288230231</v>
+        <v>1.414516896354504</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.514511432414182</v>
+        <v>3.526399840845498</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.566722140196399</v>
+        <v>-2.440606803753115</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.770757331858305</v>
+        <v>1.821203466435619</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.469485143327322</v>
+        <v>1.489299157379516</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.679493698247006</v>
+        <v>3.691382106678323</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.540638055932591</v>
+        <v>-2.414522719489307</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.772898941577687</v>
+        <v>1.823345076155001</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.469485143327322</v>
+        <v>1.489299157379516</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.671201674260865</v>
+        <v>3.683090082692182</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.452760142823471</v>
+        <v>-2.326644806380187</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.806243302405115</v>
+        <v>1.856689436982429</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.585410785750673</v>
+        <v>1.605224799802867</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.738950255298656</v>
+        <v>3.750838663729972</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.443867681430188</v>
+        <v>-2.317752344986904</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.827354692689219</v>
+        <v>1.877800827266533</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.585410785750673</v>
+        <v>1.605224799802867</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.756504661025447</v>
+        <v>3.768393069456763</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.612343798400066</v>
+        <v>-2.486228461956781</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.751819293305852</v>
+        <v>1.802265427883166</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.557462950034093</v>
+        <v>1.577276964086286</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.731591007000082</v>
+        <v>3.743479415431398</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.166087605770626</v>
+        <v>-2.039972269327341</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.91159146754549</v>
+        <v>1.962037602122804</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.46274428036446</v>
+        <v>1.482558294416654</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.656029502386164</v>
+        <v>3.667917910817481</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.143366502087473</v>
+        <v>-2.017251165644189</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.911343931515656</v>
+        <v>1.961790066092969</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.46274428036446</v>
+        <v>1.482558294416654</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.646693524883069</v>
+        <v>3.658581933314386</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.272568315381516</v>
+        <v>-2.146452978938231</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.018569332049208</v>
+        <v>2.069015466626522</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.333542467070418</v>
+        <v>1.353356481122612</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.728078562757813</v>
+        <v>3.739966971189129</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.298442713855541</v>
+        <v>-2.172327377412257</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.045297395153244</v>
+        <v>2.095743529730558</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.378454075782159</v>
+        <v>1.398268089834353</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.792103350478504</v>
+        <v>3.80399175890982</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.291388023640368</v>
+        <v>-2.165272687197084</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.044794627228859</v>
+        <v>2.095240761806172</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.385508765997333</v>
+        <v>1.405322780049526</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.793011520597154</v>
+        <v>3.80489992902847</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.26443679931388</v>
+        <v>-2.138321462870596</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.065581270604195</v>
+        <v>2.116027405181509</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.400389112025052</v>
+        <v>1.420203126077246</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.811945881858526</v>
+        <v>3.823834290289843</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.285981027144667</v>
+        <v>-2.159865690701383</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.24106671161684</v>
+        <v>2.291512846194154</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.400389112025052</v>
+        <v>1.420203126077246</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.996049014003487</v>
+        <v>4.007937422434803</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.308389144949539</v>
+        <v>-2.182273808506255</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.224220159397885</v>
+        <v>2.274666293975198</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.400389112025052</v>
+        <v>1.420203126077246</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.98816570890648</v>
+        <v>4.000054117337796</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.336613380527139</v>
+        <v>-2.210498044083855</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.214984464716482</v>
+        <v>2.265430599293795</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.41836586447636</v>
+        <v>1.438179878528554</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.001005759926902</v>
+        <v>4.012894168358218</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.346054306415669</v>
+        <v>-2.219938969972385</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.267461812082917</v>
+        <v>2.317907946660231</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.540792982019752</v>
+        <v>1.560606996071946</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.130715748174784</v>
+        <v>4.1426041566061</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.434930937584143</v>
+        <v>-2.308815601140859</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.234802254160829</v>
+        <v>2.285248388738142</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.451916350851278</v>
+        <v>1.471730364903472</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.080280864019</v>
+        <v>4.092169272450317</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.511260915185049</v>
+        <v>-2.385145578741765</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.202382076014241</v>
+        <v>2.252828210591555</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.451916350851278</v>
+        <v>1.471730364903472</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.078392676912776</v>
+        <v>4.090281085344092</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.60492485986259</v>
+        <v>-2.478809523419306</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.159736727746087</v>
+        <v>2.210182862323401</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.358252406173737</v>
+        <v>1.378066420225931</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.017014539709113</v>
+        <v>4.02890294814043</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.766493285389846</v>
+        <v>-2.640377948946561</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.093543367745337</v>
+        <v>2.143989502322651</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.231469482375857</v>
+        <v>1.251283496428051</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.939378795640538</v>
+        <v>3.951267204071854</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.874793947259965</v>
+        <v>-2.748678610816681</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.063296509863208</v>
+        <v>2.113742644440522</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.231469482375857</v>
+        <v>1.251283496428051</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.952452202506457</v>
+        <v>3.964340610937773</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.892597918980709</v>
+        <v>-2.766482582537425</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.04818011795785</v>
+        <v>2.098626252535164</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.160934859470656</v>
+        <v>1.18074887352285</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.902136625546276</v>
+        <v>3.914025033977592</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.920498706090182</v>
+        <v>-2.794383369646898</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.035543844241063</v>
+        <v>2.085989978818377</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.126337935327721</v>
+        <v>1.146151949379915</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.879902512187517</v>
+        <v>3.891790920618833</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.043024808793076</v>
+        <v>-2.916909472349792</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.983297847137104</v>
+        <v>2.033743981714418</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.003811832624828</v>
+        <v>1.023625846677021</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.80315129454298</v>
+        <v>3.815039702974296</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.273539304978665</v>
+        <v>-3.147423968535381</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.957798008253373</v>
+        <v>2.008244142830686</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7732973364392388</v>
+        <v>0.7931113504914327</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.73154855642213</v>
+        <v>3.743436964853446</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.622284390203109</v>
+        <v>-3.496169053759824</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.958611693165442</v>
+        <v>2.009057827742756</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.664549382520341</v>
+        <v>0.6843633965725349</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.806611503072638</v>
+        <v>3.818499911503955</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.776270807979249</v>
+        <v>-3.650155471535965</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.965997395200626</v>
+        <v>2.01644352977794</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.664549382520341</v>
+        <v>0.6843633965725349</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.875591772218278</v>
+        <v>3.887480180649594</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.980870242842258</v>
+        <v>-3.854754906398973</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.870208823375543</v>
+        <v>1.920654957952857</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.664549382520341</v>
+        <v>0.6843633965725349</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.861642974338399</v>
+        <v>3.873531382769715</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.233345396849982</v>
+        <v>-4.107230060406698</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.781089250827867</v>
+        <v>1.831535385405181</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.664549382520341</v>
+        <v>0.6843633965725349</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.873513463393813</v>
+        <v>3.885401871825129</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.526241153329394</v>
+        <v>-4.40012581688611</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.665141482755046</v>
+        <v>1.71558761733236</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.664549382520341</v>
+        <v>0.6843633965725349</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.874723997912757</v>
+        <v>3.886612406344073</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.712905281464202</v>
+        <v>-4.586789945020918</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.594597573728444</v>
+        <v>1.645043708305758</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6378104116957811</v>
+        <v>0.657624425747975</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.862802357645342</v>
+        <v>3.874690766076658</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.858925968378164</v>
+        <v>-4.73281063193488</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.531267151699049</v>
+        <v>1.581713286276363</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.6287273199019241</v>
+        <v>0.6485413339541179</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.852430355305217</v>
+        <v>3.864318763736534</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.95063997748775</v>
+        <v>-4.824524641044466</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.656785604754259</v>
+        <v>1.707231739331573</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.6287273199019241</v>
+        <v>0.6485413339541179</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.014634412004262</v>
+        <v>4.026522820435578</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.982291636547719</v>
+        <v>-4.856176300104435</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.638971579094085</v>
+        <v>1.689417713671399</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6235588626574839</v>
+        <v>0.6433728767096778</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.006379975621412</v>
+        <v>4.018268384052728</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.064226454816603</v>
+        <v>-4.938111118373318</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.616427069355023</v>
+        <v>1.666873203932337</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6136241170704038</v>
+        <v>0.6334381311225976</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.010648545837655</v>
+        <v>4.022536954268971</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.16620257706501</v>
+        <v>-5.040087240621726</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.584562258911562</v>
+        <v>1.635008393488876</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.5116479948219962</v>
+        <v>0.53146200887419</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.958388510944513</v>
+        <v>3.970276919375829</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.056196293587789</v>
+        <v>-4.930080957144504</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.620717659546627</v>
+        <v>1.67116379412394</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.5348525667392714</v>
+        <v>0.5546665807914652</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.964464141339053</v>
+        <v>3.976352549770369</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.913136717846863</v>
+        <v>-4.787021381403578</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.682191500564971</v>
+        <v>1.732637635142285</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.5428659933292507</v>
+        <v>0.5626800073814445</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.973522208015015</v>
+        <v>3.985410616446331</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.611689992375025</v>
+        <v>-4.485574655931741</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.810031073636242</v>
+        <v>1.860477208213556</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.8443127188010879</v>
+        <v>0.8641267328532818</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.161651126180653</v>
+        <v>4.17353953461197</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.636280236610209</v>
+        <v>-4.510164900166925</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.801166153694879</v>
+        <v>1.851612288272193</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.8443127188010879</v>
+        <v>0.8641267328532818</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.162622303933364</v>
+        <v>4.17451071236468</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.585241860603689</v>
+        <v>-4.459126524160404</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.822424408477243</v>
+        <v>1.872870543054557</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.8443127188010879</v>
+        <v>0.8641267328532818</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.163465208313119</v>
+        <v>4.175353616744435</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.544102565737058</v>
+        <v>-4.417987229293773</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.857918225298041</v>
+        <v>1.908364359875355</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8854520136677188</v>
+        <v>0.9052660277199126</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.207186884107244</v>
+        <v>4.21907529253856</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.447467653718418</v>
+        <v>-4.321352317275133</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.712756186229431</v>
+        <v>1.763202320806745</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.9820869256863587</v>
+        <v>1.001900939738553</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.081351827442361</v>
+        <v>4.093240235873678</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.57804838824926</v>
+        <v>-4.451933051805976</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.664025936491059</v>
+        <v>1.714472071068372</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.8515061911555162</v>
+        <v>0.87132020520771</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.00650543079782</v>
+        <v>4.018393839229137</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.413552054058298</v>
+        <v>-4.287436717615014</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.714251289243526</v>
+        <v>1.764697423820839</v>
       </c>
       <c r="F2035" t="n">
-        <v>1.016002525346478</v>
+        <v>1.035816539398672</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.089630050388481</v>
+        <v>4.101518458819797</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.336453452516426</v>
+        <v>-4.210338116073141</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.744278440296704</v>
+        <v>1.794724574874018</v>
       </c>
       <c r="F2036" t="n">
-        <v>1.016002525346478</v>
+        <v>1.035816539398672</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.08881776082491</v>
+        <v>4.100706169256227</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.346838647406315</v>
+        <v>-4.220723310963031</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.749993141465821</v>
+        <v>1.800439276043135</v>
       </c>
       <c r="F2037" t="n">
-        <v>1.005617330456589</v>
+        <v>1.025431344508783</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.092455423016049</v>
+        <v>4.104343831447365</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.36542680612854</v>
+        <v>-4.239311469685256</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.813394883753356</v>
+        <v>1.86384101833067</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9870291717343633</v>
+        <v>1.006843185786557</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.152139533559138</v>
+        <v>4.164027941990455</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.365725352824576</v>
+        <v>-4.239610016381292</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.810144475893241</v>
+        <v>1.860590610470554</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9867306250383274</v>
+        <v>1.006544639090521</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.148829416359815</v>
+        <v>4.160717824791132</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.264902219134148</v>
+        <v>-4.138786882690864</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.855004624308803</v>
+        <v>1.905450758886117</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9991948405226814</v>
+        <v>1.019008854574875</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.160838840589819</v>
+        <v>4.172727249021135</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.074120858381741</v>
+        <v>-3.948005521938457</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.931446422088309</v>
+        <v>1.981892556665623</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.189976201275089</v>
+        <v>1.209790215327283</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.275436910519807</v>
+        <v>4.287325318951123</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.96715750053232</v>
+        <v>-3.841042164089035</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.954068610965674</v>
+        <v>2.004514745542989</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.24844080923489</v>
+        <v>1.268254823287084</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.290352521033284</v>
+        <v>4.302240929464601</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.911826912630558</v>
+        <v>-3.785711576187273</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.011167782738438</v>
+        <v>2.061613917315752</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.303771397136652</v>
+        <v>1.323585411188846</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.358517810386401</v>
+        <v>4.370406218817717</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.899772785717595</v>
+        <v>-3.77365744927431</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.00967600140506</v>
+        <v>2.060122135982374</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.315825524049615</v>
+        <v>1.335639538101809</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.359436854435615</v>
+        <v>4.371325262866932</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.940927905285816</v>
+        <v>-3.814812568842531</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.995094583761908</v>
+        <v>2.045540718339222</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.274670404481394</v>
+        <v>1.294484418533588</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.336624412878819</v>
+        <v>4.348512821310135</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.872879342594286</v>
+        <v>-3.746764006151001</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.035165034716402</v>
+        <v>2.085611169293716</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.342718967172924</v>
+        <v>1.362532981225118</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.390304576371619</v>
+        <v>4.402192984802936</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.104479735763787</v>
+        <v>-3.978364399320502</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.962727547622196</v>
+        <v>2.01317368219951</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.342718967172924</v>
+        <v>1.362532981225118</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.410507246545214</v>
+        <v>4.42239565497653</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.154531281293007</v>
+        <v>-4.028415944849721</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.92631316547739</v>
+        <v>1.976759300054705</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.342718967172924</v>
+        <v>1.362532981225118</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.394113482612095</v>
+        <v>4.406001891043412</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.329638113869452</v>
+        <v>-4.203522777426166</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.816522346040279</v>
+        <v>1.866968480617593</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.342718967172924</v>
+        <v>1.362532981225118</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.354365396205562</v>
+        <v>4.366253804636878</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.133537960438929</v>
+        <v>-4.007422623995643</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.901985026409428</v>
+        <v>1.952431160986742</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.538819120603447</v>
+        <v>1.558633134655641</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.479048107260816</v>
+        <v>4.490936515692132</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.980512568325645</v>
+        <v>-3.854397231882359</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.062366182827646</v>
+        <v>2.11281231740496</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.691844512716731</v>
+        <v>1.711658526768925</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.67003434210169</v>
+        <v>4.681922750533007</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.008819882198915</v>
+        <v>-3.882704545755629</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.238509482186631</v>
+        <v>2.288955616763945</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.691844512716731</v>
+        <v>1.711658526768925</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.857500567009984</v>
+        <v>4.8693889754413</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.175413107312437</v>
+        <v>-4.049297770869151</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.141275143495304</v>
+        <v>2.191721278072619</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.525251287603208</v>
+        <v>1.545065301655402</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.726947583295953</v>
+        <v>4.738835991727269</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.152377313950871</v>
+        <v>-4.026261977507585</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.154165863501649</v>
+        <v>2.204611998078963</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.525251287603208</v>
+        <v>1.545065301655402</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.730623985957671</v>
+        <v>4.742512394388987</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.123131333495174</v>
+        <v>-3.997015997051889</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.163482310807423</v>
+        <v>2.213928445384737</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.525251287603208</v>
+        <v>1.545065301655402</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.728242041081166</v>
+        <v>4.740130449512482</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.230056881373025</v>
+        <v>-4.10394154492974</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.118005330813917</v>
+        <v>2.168451465391231</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.418325739725357</v>
+        <v>1.438139753777551</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.66137995151209</v>
+        <v>4.673268359943406</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.375075439880274</v>
+        <v>-4.248960103436989</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.061426709554252</v>
+        <v>2.111872844131566</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.273307181218109</v>
+        <v>1.293121195270303</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.575797618550975</v>
+        <v>4.587686026982292</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.493417205664992</v>
+        <v>-4.367301869221706</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.114021242498118</v>
+        <v>2.164467377075432</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.283993219780999</v>
+        <v>1.303807233833193</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.682140480946462</v>
+        <v>4.694028889377778</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.5448276279857</v>
+        <v>-4.418712291542414</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.091242770695774</v>
+        <v>2.141688905273088</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.283993219780999</v>
+        <v>1.303807233833193</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.679926178072401</v>
+        <v>4.691814586503718</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.624247079193451</v>
+        <v>-4.498131742750166</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.059378118286962</v>
+        <v>2.109824252864276</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.283993219780999</v>
+        <v>1.303807233833193</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.67982930614669</v>
+        <v>4.691717714578006</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.719710077110669</v>
+        <v>-4.593594740667384</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.021186812678118</v>
+        <v>2.071632947255432</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.283993219780999</v>
+        <v>1.303807233833193</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.679823199704733</v>
+        <v>4.69171160813605</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.655334166259954</v>
+        <v>-4.529218829816669</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.045033573581015</v>
+        <v>2.095479708158329</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.348369130631714</v>
+        <v>1.368183144683908</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.716545142777773</v>
+        <v>4.728433551209089</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.710703328392148</v>
+        <v>-4.584587991948863</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.028619726475864</v>
+        <v>2.079065861053178</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.348369130631714</v>
+        <v>1.368183144683908</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.722278960525499</v>
+        <v>4.734167368956816</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.756141108222975</v>
+        <v>-4.63002577177969</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.009982977886466</v>
+        <v>2.06042911246378</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.305524139953554</v>
+        <v>1.325338154005748</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.696110329461536</v>
+        <v>4.707998737892853</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.667934274075397</v>
+        <v>-4.541818937632112</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.065140104395815</v>
+        <v>2.11558623897313</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.305524139953554</v>
+        <v>1.325338154005748</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.715984722311855</v>
+        <v>4.727873130743172</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.561899278870087</v>
+        <v>-4.435783942426802</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.091254803002667</v>
+        <v>2.141700937579981</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.305524139953554</v>
+        <v>1.325338154005748</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.699685422836582</v>
+        <v>4.711573831267899</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.378687615736992</v>
+        <v>-4.252572279293707</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.16697041771995</v>
+        <v>2.217416552297265</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.305524139953554</v>
+        <v>1.325338154005748</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.702116372300628</v>
+        <v>4.714004780731945</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.306966168723141</v>
+        <v>-4.180850832279856</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.161450182373381</v>
+        <v>2.211896316950695</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.377245586967405</v>
+        <v>1.397059601019599</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.710940426356829</v>
+        <v>4.722828834788145</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.284593143115435</v>
+        <v>-4.15847780667215</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.117315138537635</v>
+        <v>2.167761273114949</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.388501338080307</v>
+        <v>1.4083153521325</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.664609622945741</v>
+        <v>4.676498031377058</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.31760943902618</v>
+        <v>-4.191494102582895</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.289306825058692</v>
+        <v>2.339752959636006</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.319063961413555</v>
+        <v>1.338877975465749</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.808145401831045</v>
+        <v>4.820033810262362</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.306081803376571</v>
+        <v>-4.179966466933286</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.285839105146785</v>
+        <v>2.336285239724099</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.378064619614918</v>
+        <v>1.397878633667111</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.835467022580112</v>
+        <v>4.847355431011428</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236294</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.40342330471894</v>
+        <v>-4.277307968275655</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.250570617131626</v>
+        <v>2.30101675170894</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.333644437449429</v>
+        <v>1.353458451501623</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.812483025802607</v>
+        <v>4.824371434233924</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.489279334058907</v>
+        <v>-4.363163997615621</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.217479287588477</v>
+        <v>2.267925422165791</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.291268368223294</v>
+        <v>1.311082382275488</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.788308466459765</v>
+        <v>4.800196874891081</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.498116131475026</v>
+        <v>-4.372000795031741</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.196363770442531</v>
+        <v>2.246809905019846</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.283826195581943</v>
+        <v>1.303640209634137</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.766262364695456</v>
+        <v>4.778150773126772</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.589498694040484</v>
+        <v>-4.463383357597199</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.169975256461397</v>
+        <v>2.220421391038712</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.247261310862599</v>
+        <v>1.267075324914793</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.754487944908899</v>
+        <v>4.766376353340215</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.577791976053478</v>
+        <v>-4.451676639610193</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.276786201480467</v>
+        <v>2.327232336057781</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.258968028849605</v>
+        <v>1.278782042901799</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.86364023352537</v>
+        <v>4.875528641956686</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.478128471969816</v>
+        <v>-4.352013135526531</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.319683941845337</v>
+        <v>2.370130076422651</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.322155112053292</v>
+        <v>1.341969126105486</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.904584822178986</v>
+        <v>4.916473230610302</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.488444570136168</v>
+        <v>-4.362329233692883</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.528462335856854</v>
+        <v>2.578908470434168</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.322155112053292</v>
+        <v>1.341969126105486</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.117489655457044</v>
+        <v>5.12937806388836</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.488350602118795</v>
+        <v>-4.36223526567551</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.527678589975893</v>
+        <v>2.578124724553207</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.32252497340061</v>
+        <v>1.342338987452804</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.116890239177525</v>
+        <v>5.128778647608842</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.49556942631864</v>
+        <v>-4.369454089875354</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.519023046240309</v>
+        <v>2.569469180817623</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.32252497340061</v>
+        <v>1.342338987452804</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.111122225121878</v>
+        <v>5.123010633553195</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.494621003200601</v>
+        <v>-4.368505666757316</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.519402415487524</v>
+        <v>2.569848550064838</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.32252497340061</v>
+        <v>1.342338987452804</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.111122225121878</v>
+        <v>5.123010633553195</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.651689461456225</v>
+        <v>-4.525574125012939</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.469302640166367</v>
+        <v>2.519748774743681</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.32252497340061</v>
+        <v>1.342338987452804</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.12384983310297</v>
+        <v>5.135738241534288</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.645697214667414</v>
+        <v>-4.519581878224128</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.473645537306279</v>
+        <v>2.524091671883594</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.32252497340061</v>
+        <v>1.342338987452804</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.125795831527358</v>
+        <v>5.137684239958675</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.557139253536646</v>
+        <v>-4.43102391709336</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.502722857776355</v>
+        <v>2.553168992353669</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.32252497340061</v>
+        <v>1.342338987452804</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.119449967545127</v>
+        <v>5.131338375976444</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.539380176033572</v>
+        <v>-4.413264839590286</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.50913516621658</v>
+        <v>2.559581300793894</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.32252497340061</v>
+        <v>1.342338987452804</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.118758644984123</v>
+        <v>5.130647053415439</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.439750024984504</v>
+        <v>-4.313634688541218</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.561769412544794</v>
+        <v>2.612215547122108</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.422155124449677</v>
+        <v>1.441969138501871</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.19131892152215</v>
+        <v>5.203207329953467</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.489149533673515</v>
+        <v>-4.363034197230229</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.731163874567916</v>
+        <v>2.78161000914523</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.432413957881422</v>
+        <v>1.452227971933616</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.386628487079924</v>
+        <v>5.39851689551124</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.282465060031139</v>
+        <v>-4.156349723587853</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.801026337127729</v>
+        <v>2.851472471705043</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.639098431523798</v>
+        <v>1.658912445575992</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.497827844368211</v>
+        <v>5.509716252799527</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,45 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.971782112853617</v>
+        <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.316621955028666</v>
+        <v>-4.156156687804433</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.789365092782823</v>
+        <v>2.853551199672516</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.555514661982985</v>
+        <v>1.659089346624647</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.449679096297829</v>
+        <v>5.511823907082825</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" s="2" t="n">
+        <v>45552</v>
+      </c>
+      <c r="B2090" t="n">
+        <v>3.981726001287928</v>
+      </c>
+      <c r="C2090" t="n">
+        <v>4.892051269809499</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>-4.156156687804433</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>2.853551199672516</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>1.659089346624647</v>
+      </c>
+      <c r="G2090" t="n">
+        <v>4.885115066795866</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240917.xlsx
+++ b/tame_output/ON/bt/strategyON_20240917.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>31.9%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>100.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>177.6%</t>
+          <t>134.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.2%</t>
+          <t>-72.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.6%</t>
+          <t>420.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-577.2%</t>
+          <t>-606.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-90.9%</t>
+          <t>-102.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>75.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-60.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.7%</t>
+          <t>-342.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-58.1%</t>
+          <t>-76.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,31 +1423,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>85.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,57 +1456,57 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>-0.3%</t>
         </is>
       </c>
     </row>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.338778816372826</v>
+        <v>-7.226054034658109</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2155920232403763</v>
+        <v>0.2606819359262631</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.060402676835486</v>
+        <v>-0.9476778951207698</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.515218368001963</v>
+        <v>2.582853237030793</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.175378945433463</v>
+        <v>-7.062654163718746</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2803187928368782</v>
+        <v>0.325408705522765</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8970028058961237</v>
+        <v>-0.7842780241814074</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.612625111786337</v>
+        <v>2.680259980815167</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.941897723203865</v>
+        <v>-6.829172941489148</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3816357105665698</v>
+        <v>0.4267256232524566</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6635215836665251</v>
+        <v>-0.5507968019518088</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.760638273961949</v>
+        <v>2.828273142990779</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.79223133219635</v>
+        <v>-6.679506550481633</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4386100566566169</v>
+        <v>0.4836999693425037</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5706180924239892</v>
+        <v>-0.4578933107092729</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.813488158394511</v>
+        <v>2.881123027423341</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.659955858565463</v>
+        <v>-6.547231076850746</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.392781032116126</v>
+        <v>0.4378709448020128</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4383426187931025</v>
+        <v>-0.3256178370783862</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.794114228580198</v>
+        <v>2.861749097609028</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.488094643000561</v>
+        <v>-6.375369861285844</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4643405790297237</v>
+        <v>0.5094304917156105</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.2664814032281997</v>
+        <v>-0.1537566215134833</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.900046018606776</v>
+        <v>2.967680887635606</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.403129976271241</v>
+        <v>-6.290405194556524</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5112327869451101</v>
+        <v>0.5563226996309973</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1815167364988801</v>
+        <v>-0.06879195478416378</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.963931159868027</v>
+        <v>3.031566028896857</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.508719966044346</v>
+        <v>-6.395995184329628</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3410208614366494</v>
+        <v>0.3861107741225367</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2871067262719845</v>
+        <v>-0.1743819445572681</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.772601236404946</v>
+        <v>2.840236105433775</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.440485381418918</v>
+        <v>-6.327760599704201</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4168590371639072</v>
+        <v>0.461948949849794</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2686914033994485</v>
+        <v>-0.1559666216847321</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.832194772005554</v>
+        <v>2.899829641034383</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.292545340011319</v>
+        <v>-6.179820558296601</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3594142450885398</v>
+        <v>0.4045041577744266</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2483704874908909</v>
+        <v>-0.1356457057761746</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.727766512912281</v>
+        <v>2.795401381941111</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.239575817757331</v>
+        <v>-6.126851036042613</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3718880677366569</v>
+        <v>0.4169779804225442</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.0826761835221857</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.750834240011196</v>
+        <v>2.818469109040026</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.07378762179704</v>
+        <v>-5.961062840082322</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4312427340256799</v>
+        <v>0.4763326467115672</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.0826761835221857</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.743873627916103</v>
+        <v>2.811508496944933</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.040424415318271</v>
+        <v>-5.927699633603553</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4590503709983307</v>
+        <v>0.5041402836842179</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.0826761835221857</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.758335982297246</v>
+        <v>2.825970851326076</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.932165278195749</v>
+        <v>-5.819440496481032</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4968861463065344</v>
+        <v>0.5419760589924216</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.195400965236902</v>
+        <v>-0.0826761835221857</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.752868102756441</v>
+        <v>2.820502971785271</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.808874143378619</v>
+        <v>-5.696149361663901</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5437006942439635</v>
+        <v>0.5887906069298507</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.07210983041977154</v>
+        <v>0.0406149512949448</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.824340877657296</v>
+        <v>2.891975746686126</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.756177276247327</v>
+        <v>-5.643452494532609</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5724804193338051</v>
+        <v>0.6175703320196924</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.01941296328848036</v>
+        <v>0.09331181842623598</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.863659976173396</v>
+        <v>2.931294845202226</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.512411834263883</v>
+        <v>-5.399687052549165</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6657673044742336</v>
+        <v>0.7108572171601208</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.01941296328848036</v>
+        <v>0.09331181842623598</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.859440684520447</v>
+        <v>2.927075553549277</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.422636161887411</v>
+        <v>-5.309911380172693</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7038018873448384</v>
+        <v>0.7488918000307256</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.04218648162582966</v>
+        <v>0.154911263340546</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.898524665389049</v>
+        <v>2.966159534417879</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.172785767938336</v>
+        <v>-5.060060986223618</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7964841199081705</v>
+        <v>0.8415740325940577</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.04218648162582966</v>
+        <v>0.154911263340546</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.891266740372751</v>
+        <v>2.958901609401581</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.996893675470904</v>
+        <v>-4.884168893756186</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8704400804157921</v>
+        <v>0.9155299931016794</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.04218648162582966</v>
+        <v>0.154911263340546</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.8948658638934</v>
+        <v>2.962500732922229</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.825447212448441</v>
+        <v>-4.712722430733723</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9523461716793311</v>
+        <v>0.9974360843652184</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2136329446482928</v>
+        <v>0.3263577263630091</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.011061247761432</v>
+        <v>3.078696116790261</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.74542492533932</v>
+        <v>-4.632700143624602</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9833755641392765</v>
+        <v>1.028465476825164</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2936552317574138</v>
+        <v>0.4063800134721301</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.058095097643201</v>
+        <v>3.125729966672031</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.681789183105385</v>
+        <v>-4.569064401390667</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.013524662087168</v>
+        <v>1.058614574773055</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3572909739913483</v>
+        <v>0.4700157557060646</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.100971344037879</v>
+        <v>3.168606213066709</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.58809186488899</v>
+        <v>-4.475367083174272</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.032197848157521</v>
+        <v>1.077287760843408</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3572909739913483</v>
+        <v>0.4700157557060646</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.082165602821675</v>
+        <v>3.149800471850504</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.598594487954279</v>
+        <v>-4.485869706239561</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.029739875556283</v>
+        <v>1.07482978824217</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3467883509260594</v>
+        <v>0.4595131326407758</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.077607105607379</v>
+        <v>3.145241974636209</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.486108227285404</v>
+        <v>-4.373383445570687</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.078663693658653</v>
+        <v>1.12375360634454</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3467883509260594</v>
+        <v>0.4595131326407758</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.081536419442199</v>
+        <v>3.149171288471029</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.468394540407539</v>
+        <v>-4.355669758692821</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.086427752327139</v>
+        <v>1.131517665013027</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3499696798229762</v>
+        <v>0.4626944615376926</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.084123800697689</v>
+        <v>3.151758669726519</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.344920269094521</v>
+        <v>-4.232195487379803</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.13281553207234</v>
+        <v>1.177905444758227</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3499696798229762</v>
+        <v>0.4626944615376926</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.081121871917682</v>
+        <v>3.148756740946512</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.12489947105751</v>
+        <v>-4.143666626641847</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.222402888297758</v>
+        <v>1.214896026064024</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4911895248909565</v>
+        <v>0.5220884576801976</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.167432815969085</v>
+        <v>3.185972175642629</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.992031781994232</v>
+        <v>-4.01079893757857</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.291444146724893</v>
+        <v>1.283937284491158</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4911895248909565</v>
+        <v>0.5220884576801976</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.183326998770908</v>
+        <v>3.201866358444453</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.871858698629733</v>
+        <v>-3.890625854214071</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.340659224510995</v>
+        <v>1.333152362277259</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6113626082554554</v>
+        <v>0.6422615410446966</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.256576693229909</v>
+        <v>3.275116052903454</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.736605337299756</v>
+        <v>-3.755372492884094</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.404848671604425</v>
+        <v>1.39734180937069</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7466159695854325</v>
+        <v>0.7775149023746737</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.347816812589335</v>
+        <v>3.36635617226288</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.796480164657448</v>
+        <v>-3.815247320241786</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.366936232062774</v>
+        <v>1.359429369829039</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6867411422277404</v>
+        <v>0.7176400750169816</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.297929407576146</v>
+        <v>3.316468767249691</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.676659933746611</v>
+        <v>-3.695427089330949</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.430153493661318</v>
+        <v>1.422646631427583</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6867411422277404</v>
+        <v>0.7176400750169816</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.313218576810355</v>
+        <v>3.331757936483899</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.679129640208417</v>
+        <v>-3.697896795792755</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.336809810399037</v>
+        <v>1.329302948165302</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6842714357659343</v>
+        <v>0.7151703685551754</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.219380952255712</v>
+        <v>3.237920311929257</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.747499826532427</v>
+        <v>-3.766266982116765</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.228723597354734</v>
+        <v>1.221216735120999</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.7244460675913903</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.144208233162743</v>
+        <v>3.162747592836287</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.859372106158578</v>
+        <v>-3.878139261742915</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.174411394136165</v>
+        <v>1.16690453190243</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.7244460675913903</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.134644941794634</v>
+        <v>3.153184301468179</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.84339744067231</v>
+        <v>-3.862164596256648</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.1473757852547</v>
+        <v>1.139868923020965</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.7244460675913903</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.101219466718661</v>
+        <v>3.119758826392206</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.66792318087984</v>
+        <v>-3.686690336464178</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.222132721163475</v>
+        <v>1.21462585892974</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.7244460675913903</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.105786698710449</v>
+        <v>3.124326058383994</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.659998806294926</v>
+        <v>-3.678765961879264</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.201044499758648</v>
+        <v>1.193537637524913</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6935471348021492</v>
+        <v>0.7244460675913903</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.081528727471656</v>
+        <v>3.100068087145201</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.653720603725077</v>
+        <v>-3.672487759309415</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.132094094188037</v>
+        <v>1.124587231954302</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6998253373719983</v>
+        <v>0.7307242701612393</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.013833962415015</v>
+        <v>3.03237332208856</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.593867984521354</v>
+        <v>-3.612635140105692</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.166207528301659</v>
+        <v>1.158700666067924</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6998253373719983</v>
+        <v>0.7307242701612393</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.024006348847148</v>
+        <v>3.042545708520692</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.507624521494977</v>
+        <v>-3.526391677079315</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.19565118408607</v>
+        <v>1.188144321852335</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6998253373719983</v>
+        <v>0.7307242701612393</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.018952619421008</v>
+        <v>3.037491979094553</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.552931340893957</v>
+        <v>-3.571698496478295</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.169304231771004</v>
+        <v>1.161797369537269</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6590151743627675</v>
+        <v>0.6899141071520085</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.986242297059995</v>
+        <v>3.00478165673354</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.581964445596258</v>
+        <v>-3.600731601180596</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.158242862923185</v>
+        <v>1.15073600068945</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6590151743627675</v>
+        <v>0.6899141071520085</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.986794170093097</v>
+        <v>3.005333529766641</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.489153964145399</v>
+        <v>-3.507921119729737</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.124639747394894</v>
+        <v>1.117132885161159</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7518256558136268</v>
+        <v>0.7827245886028679</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.971753150854978</v>
+        <v>2.990292510528523</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.533543433474827</v>
+        <v>-3.552310589059164</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.108757435587724</v>
+        <v>1.101250573353989</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7074361864841991</v>
+        <v>0.7383351192734402</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.946992945181922</v>
+        <v>2.965532304855467</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.513039739589329</v>
+        <v>-3.531806895173667</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.112034621653646</v>
+        <v>1.104527759419911</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7279398803696965</v>
+        <v>0.7588388131589375</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.954370870024944</v>
+        <v>2.972910229698488</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.552963834171901</v>
+        <v>-3.571730989756239</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.101556279651284</v>
+        <v>1.094049417417549</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7279398803696965</v>
+        <v>0.7588388131589375</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.959862165855611</v>
+        <v>2.978401525529156</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.580744232073255</v>
+        <v>-3.599511387657592</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.101941322259282</v>
+        <v>1.094434460025547</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7001594824683435</v>
+        <v>0.7310584152575845</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.954691128883338</v>
+        <v>2.973230488556883</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.699124904803393</v>
+        <v>-3.717892060387731</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8929447731678799</v>
+        <v>0.8854379109341448</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6329416303173673</v>
+        <v>0.6638405631066083</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.752716137593405</v>
+        <v>2.77125549726695</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.807738983246724</v>
+        <v>-3.826506138831062</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9696488025097532</v>
+        <v>0.9621419402760178</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6329416303173673</v>
+        <v>0.6638405631066083</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.872865798312611</v>
+        <v>2.891405157986156</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.772329944998581</v>
+        <v>-3.791097100582919</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9983254439113332</v>
+        <v>0.9908185816775981</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6329416303173673</v>
+        <v>0.6638405631066083</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.887378824414934</v>
+        <v>2.905918184088479</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.780791113654042</v>
+        <v>-3.79955826923838</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9923604177915175</v>
+        <v>0.9848535555577822</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6244804616619062</v>
+        <v>0.6553793944511472</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.879721564564026</v>
+        <v>2.898260924237571</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.603674783618876</v>
+        <v>-3.622441939203214</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.059935978650886</v>
+        <v>1.052429116417151</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6244804616619062</v>
+        <v>0.6553793944511472</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.876450593409329</v>
+        <v>2.894989953082873</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.648767028452422</v>
+        <v>-3.66753418403676</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.042582472479381</v>
+        <v>1.035075610245646</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5625844184925164</v>
+        <v>0.5934833512817574</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.839996359269608</v>
+        <v>2.858535718943152</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.469391607213654</v>
+        <v>-3.488158762797992</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.108119616281303</v>
+        <v>1.100612754047567</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7193611766632351</v>
+        <v>0.7502601094524761</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.927849389478454</v>
+        <v>2.946388749151998</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.514405820734261</v>
+        <v>-3.533172976318598</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.07092138620465</v>
+        <v>1.063414523970915</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6890122813486305</v>
+        <v>0.7199112141378715</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.890447507621281</v>
+        <v>2.908986867294825</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.542570212848694</v>
+        <v>-3.800177486591034</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.065347191697822</v>
+        <v>0.9623042822008863</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6271880390725921</v>
+        <v>0.525548176094923</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.859044524594603</v>
+        <v>2.798060606808002</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.643767994285867</v>
+        <v>-3.901375268028207</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.024072001019455</v>
+        <v>0.9210290915225186</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.558779225527273</v>
+        <v>0.4571393625496038</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.817203158363913</v>
+        <v>2.756219240577312</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.637257027671554</v>
+        <v>-3.894864301413894</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.024276349219496</v>
+        <v>0.9212334397225603</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.558779225527273</v>
+        <v>0.4571393625496038</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.81480311991823</v>
+        <v>2.753819202131628</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.618218899964257</v>
+        <v>-3.875826173706597</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.02841631951066</v>
+        <v>0.9253734100137241</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.5005956141960785</v>
+        <v>0.3989557512184093</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.776417672327758</v>
+        <v>2.715433754541157</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.670734702239077</v>
+        <v>-3.928341975981417</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.126704400234922</v>
+        <v>1.023661490737986</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.5005956141960785</v>
+        <v>0.3989557512184093</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.895712073961949</v>
+        <v>2.834728156175347</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.674143013673656</v>
+        <v>-3.931750287415996</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.126174404647224</v>
+        <v>1.023131495150288</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5331121832054558</v>
+        <v>0.4314723202277866</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.916055344353708</v>
+        <v>2.855071426567107</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.654786877779809</v>
+        <v>-3.912394151522149</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.139925389401689</v>
+        <v>1.036882479904753</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5331121832054558</v>
+        <v>0.4314723202277866</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.922063874750634</v>
+        <v>2.861079956964033</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.507043907544807</v>
+        <v>-3.764651181287147</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.096972798772889</v>
+        <v>0.9939298892759532</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.700919540440339</v>
+        <v>0.5992796774626699</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.920698510368764</v>
+        <v>2.859714592582162</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.590865128819505</v>
+        <v>-3.848472402561845</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.066237931794491</v>
+        <v>0.9631950222975549</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.700919540440339</v>
+        <v>0.5992796774626699</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.923492131900245</v>
+        <v>2.862508214113643</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.584712422766721</v>
+        <v>-3.842319696509061</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.069361362607263</v>
+        <v>0.966318453110327</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.7070722464931233</v>
+        <v>0.6054323835154541</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.927846103923573</v>
+        <v>2.866862186136972</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.601521720917222</v>
+        <v>-3.859128994659562</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.061718120087173</v>
+        <v>0.9586752105902367</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.6902629483426217</v>
+        <v>0.5886230853649526</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.916841001773383</v>
+        <v>2.855857083986781</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.5392237221411</v>
+        <v>-3.796830995883441</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.152972873394442</v>
+        <v>1.049929963897506</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7355572126170637</v>
+        <v>0.6339173496393946</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.010353114134869</v>
+        <v>2.949369196348268</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.337433524475943</v>
+        <v>-3.595040798218283</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.035980954174633</v>
+        <v>0.9329380446776967</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.9335754047862181</v>
+        <v>0.831935541808549</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.931456031150489</v>
+        <v>2.870472113363888</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.388320237162137</v>
+        <v>-3.645927510904477</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.08591650142233</v>
+        <v>0.9828735919253939</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8826886921000237</v>
+        <v>0.7810488291223545</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.971214235860947</v>
+        <v>2.910230318074346</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.30170949451233</v>
+        <v>-3.55931676825467</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.135188534598297</v>
+        <v>1.032145625101361</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9613144233051819</v>
+        <v>0.8596745603275128</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.033017410700086</v>
+        <v>2.972033492913484</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.361918792517614</v>
+        <v>-3.619526066259954</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.109640796220854</v>
+        <v>1.006597886723918</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.9011051252998974</v>
+        <v>0.7994652623222283</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.995427812721587</v>
+        <v>2.934443894934986</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.312732143833263</v>
+        <v>-3.570339417575603</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.127807073734524</v>
+        <v>1.024764164237588</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.9011051252998974</v>
+        <v>0.7994652623222283</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.993919430761515</v>
+        <v>2.932935512974914</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.268359012194694</v>
+        <v>-3.525966285937034</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.145419193825387</v>
+        <v>1.042376284328451</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.945478256938466</v>
+        <v>0.8438383939607969</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.020406177180093</v>
+        <v>2.959422259393491</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.290839363053579</v>
+        <v>-3.548446636795919</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.130820847620424</v>
+        <v>1.027777938123488</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.945478256938466</v>
+        <v>0.8438383939607969</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.014799971318683</v>
+        <v>2.953816053532082</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.243183632492523</v>
+        <v>-3.500790906234863</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.156264896872651</v>
+        <v>1.053221987375715</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.9931339874995215</v>
+        <v>0.8914941245218525</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.049775166683121</v>
+        <v>2.98879124889652</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.142665473993769</v>
+        <v>-3.400272747736109</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.201364533646877</v>
+        <v>1.098321624149941</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.093652145998276</v>
+        <v>0.9920122830206071</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.114978435157099</v>
+        <v>3.053994517370497</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.126760144561416</v>
+        <v>-3.384367418303756</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.194481337895691</v>
+        <v>1.091438428398755</v>
       </c>
       <c r="F1980" t="n">
-        <v>1.014539485289037</v>
+        <v>0.9128996223113681</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.054265511207428</v>
+        <v>2.993281593420826</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.081921742953018</v>
+        <v>-3.339529016695358</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.216514401149678</v>
+        <v>1.113471491652742</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.019082918233907</v>
+        <v>0.9174430552562376</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.061089273584978</v>
+        <v>3.000105355798377</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.101420199195026</v>
+        <v>-3.359027472937366</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.212875958283953</v>
+        <v>1.109833048787017</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9709982769540024</v>
+        <v>0.8693584139763333</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.036399428448113</v>
+        <v>2.975415510661512</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.057217362109126</v>
+        <v>-3.314824635851466</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.236436695646151</v>
+        <v>1.133393786149214</v>
       </c>
       <c r="F1983" t="n">
-        <v>1.015201114039903</v>
+        <v>0.9135612510622337</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.068800733227491</v>
+        <v>3.007816815440889</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.064777027946173</v>
+        <v>-3.322384301688513</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.231822829780579</v>
+        <v>1.128779920283643</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.070004518049722</v>
+        <v>0.968364655072053</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.10009277610263</v>
+        <v>3.039108858316029</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.906485610406901</v>
+        <v>-3.164092884149241</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.346387161979328</v>
+        <v>1.243344252482392</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.070004518049722</v>
+        <v>0.968364655072053</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.151340541285669</v>
+        <v>3.090356623499068</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.698843606772424</v>
+        <v>-2.956450880514764</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.427884668027372</v>
+        <v>1.324841758530436</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.277646521684198</v>
+        <v>1.176006658706529</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.274366448060608</v>
+        <v>3.213382530274007</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.647811514049896</v>
+        <v>-2.905418787792236</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.443245733354653</v>
+        <v>1.340202823857717</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.328678614406726</v>
+        <v>1.227038751429057</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.299933931932395</v>
+        <v>3.238950014145794</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.58258733292269</v>
+        <v>-2.840194606665031</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.48652280989824</v>
+        <v>1.383479900401304</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.393902795533932</v>
+        <v>1.292262932556263</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.356255844701423</v>
+        <v>3.295271926914822</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.545160312851557</v>
+        <v>-2.802767586593897</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.497454590225974</v>
+        <v>1.394411680729038</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.399154333563114</v>
+        <v>1.297514470585444</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.355367739818213</v>
+        <v>3.294383822031612</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.543802327878011</v>
+        <v>-2.801409601620351</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.499254576546632</v>
+        <v>1.396211667049696</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.473492459100932</v>
+        <v>1.371852596123263</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.401227407472144</v>
+        <v>3.340243489685543</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.515389064778128</v>
+        <v>-2.772996338520468</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.671177652807797</v>
+        <v>1.568134743310861</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.414516896354504</v>
+        <v>1.312877033376834</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.526399840845498</v>
+        <v>3.465415923058896</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.440606803753115</v>
+        <v>-2.698214077495455</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.821203466435619</v>
+        <v>1.718160556938683</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.489299157379516</v>
+        <v>1.387659294401847</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.691382106678323</v>
+        <v>3.630398188891721</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.414522719489307</v>
+        <v>-2.672129993231647</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.823345076155001</v>
+        <v>1.720302166658065</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.489299157379516</v>
+        <v>1.387659294401847</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.683090082692182</v>
+        <v>3.62210616490558</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.326644806380187</v>
+        <v>-2.584252080122527</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.856689436982429</v>
+        <v>1.753646527485493</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.605224799802867</v>
+        <v>1.503584936825198</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.750838663729972</v>
+        <v>3.68985474594337</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.317752344986904</v>
+        <v>-2.575359618729244</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.877800827266533</v>
+        <v>1.774757917769597</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.605224799802867</v>
+        <v>1.503584936825198</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.768393069456763</v>
+        <v>3.707409151670161</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.486228461956781</v>
+        <v>-2.743835735699121</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.802265427883166</v>
+        <v>1.69922251838623</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.577276964086286</v>
+        <v>1.475637101108617</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.743479415431398</v>
+        <v>3.682495497644797</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.039972269327341</v>
+        <v>-2.297579543069681</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.962037602122804</v>
+        <v>1.858994692625868</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.482558294416654</v>
+        <v>1.380918431438984</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.667917910817481</v>
+        <v>3.606933993030879</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.017251165644189</v>
+        <v>-2.274858439386529</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.961790066092969</v>
+        <v>1.858747156596033</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.482558294416654</v>
+        <v>1.380918431438984</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.658581933314386</v>
+        <v>3.597598015527784</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.146452978938231</v>
+        <v>-2.404060252680571</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.069015466626522</v>
+        <v>1.965972557129585</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.353356481122612</v>
+        <v>1.251716618144942</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.739966971189129</v>
+        <v>3.678983053402527</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.172327377412257</v>
+        <v>-2.429934651154597</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.095743529730558</v>
+        <v>1.992700620233622</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.398268089834353</v>
+        <v>1.296628226856683</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.80399175890982</v>
+        <v>3.743007841123219</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.165272687197084</v>
+        <v>-2.422879960939424</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.095240761806172</v>
+        <v>1.992197852309237</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.405322780049526</v>
+        <v>1.303682917071857</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.80489992902847</v>
+        <v>3.743916011241868</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.138321462870596</v>
+        <v>-2.395928736612936</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.116027405181509</v>
+        <v>2.012984495684573</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.420203126077246</v>
+        <v>1.318563263099576</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.823834290289843</v>
+        <v>3.762850372503241</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.159865690701383</v>
+        <v>-2.417472964443723</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.291512846194154</v>
+        <v>2.188469936697218</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.420203126077246</v>
+        <v>1.318563263099576</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.007937422434803</v>
+        <v>3.946953504648201</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.182273808506255</v>
+        <v>-2.439881082248595</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.274666293975198</v>
+        <v>2.171623384478262</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.420203126077246</v>
+        <v>1.318563263099576</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.000054117337796</v>
+        <v>3.939070199551194</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.210498044083855</v>
+        <v>-2.468105317826195</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.265430599293795</v>
+        <v>2.162387689796859</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.438179878528554</v>
+        <v>1.336540015550885</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.012894168358218</v>
+        <v>3.951910250571617</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.219938969972385</v>
+        <v>-2.477546243714725</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.317907946660231</v>
+        <v>2.214865037163295</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.560606996071946</v>
+        <v>1.458967133094276</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.1426041566061</v>
+        <v>4.081620238819498</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.308815601140859</v>
+        <v>-2.566422874883199</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.285248388738142</v>
+        <v>2.182205479241206</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.471730364903472</v>
+        <v>1.370090501925803</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.092169272450317</v>
+        <v>4.031185354663715</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.385145578741765</v>
+        <v>-2.642752852484105</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.252828210591555</v>
+        <v>2.149785301094619</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.471730364903472</v>
+        <v>1.370090501925803</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.090281085344092</v>
+        <v>4.02929716755749</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.478809523419306</v>
+        <v>-2.736416797161646</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.210182862323401</v>
+        <v>2.107139952826465</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.378066420225931</v>
+        <v>1.276426557248261</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.02890294814043</v>
+        <v>3.967919030353828</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.640377948946561</v>
+        <v>-2.897985222688901</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.143989502322651</v>
+        <v>2.040946592825715</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.251283496428051</v>
+        <v>1.149643633450382</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.951267204071854</v>
+        <v>3.890283286285253</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.748678610816681</v>
+        <v>-3.006285884559021</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.113742644440522</v>
+        <v>2.010699734943586</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.251283496428051</v>
+        <v>1.149643633450382</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.964340610937773</v>
+        <v>3.903356693151171</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.766482582537425</v>
+        <v>-3.024089856279765</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.098626252535164</v>
+        <v>1.995583343038228</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.18074887352285</v>
+        <v>1.079109010545181</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.914025033977592</v>
+        <v>3.85304111619099</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.794383369646898</v>
+        <v>-3.051990643389238</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.085989978818377</v>
+        <v>1.982947069321441</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.146151949379915</v>
+        <v>1.044512086402246</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.891790920618833</v>
+        <v>3.830807002832232</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.916909472349792</v>
+        <v>-3.174516746092132</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.033743981714418</v>
+        <v>1.930701072217482</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.023625846677021</v>
+        <v>0.921985983699352</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.815039702974296</v>
+        <v>3.754055785187694</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.147423968535381</v>
+        <v>-3.405031242277721</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.008244142830686</v>
+        <v>1.90520123333375</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7931113504914327</v>
+        <v>0.6914714875137633</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.743436964853446</v>
+        <v>3.682453047066845</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.496169053759824</v>
+        <v>-3.753776327502164</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.009057827742756</v>
+        <v>1.90601491824582</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6843633965725349</v>
+        <v>0.5827235335948655</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.818499911503955</v>
+        <v>3.757515993717353</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237096</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.650155471535965</v>
+        <v>-3.907762745278305</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.01644352977794</v>
+        <v>1.913400620281003</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6843633965725349</v>
+        <v>0.5827235335948655</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.887480180649594</v>
+        <v>3.826496262862993</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423389</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.854754906398973</v>
+        <v>-4.112362180141313</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.920654957952857</v>
+        <v>1.817612048455921</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6843633965725349</v>
+        <v>0.5827235335948655</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.873531382769715</v>
+        <v>3.812547464983114</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.107230060406698</v>
+        <v>-4.364837334149038</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.831535385405181</v>
+        <v>1.728492475908245</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6843633965725349</v>
+        <v>0.5827235335948655</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.885401871825129</v>
+        <v>3.824417954038528</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.40012581688611</v>
+        <v>-4.65773309062845</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.71558761733236</v>
+        <v>1.612544707835424</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6843633965725349</v>
+        <v>0.5827235335948655</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.886612406344073</v>
+        <v>3.825628488557471</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.586789945020918</v>
+        <v>-4.844397218763258</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.645043708305758</v>
+        <v>1.542000798808822</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.657624425747975</v>
+        <v>0.5559845627703056</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.874690766076658</v>
+        <v>3.813706848290057</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916199</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.73281063193488</v>
+        <v>-4.99041790567722</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.581713286276363</v>
+        <v>1.478670376779427</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.6485413339541179</v>
+        <v>0.5469014709764486</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.864318763736534</v>
+        <v>3.803334845949932</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.824524641044466</v>
+        <v>-5.082131914786805</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.707231739331573</v>
+        <v>1.604188829834637</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.6485413339541179</v>
+        <v>0.5469014709764486</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.026522820435578</v>
+        <v>3.965538902648976</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.856176300104435</v>
+        <v>-5.113783573846774</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.689417713671399</v>
+        <v>1.586374804174463</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6433728767096778</v>
+        <v>0.5417330137320084</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.018268384052728</v>
+        <v>3.957284466266127</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868142</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.938111118373318</v>
+        <v>-5.195718392115658</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.666873203932337</v>
+        <v>1.563830294435401</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6334381311225976</v>
+        <v>0.5317982681449283</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.022536954268971</v>
+        <v>3.961553036482369</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.040087240621726</v>
+        <v>-5.297694514364065</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.635008393488876</v>
+        <v>1.531965483991941</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.53146200887419</v>
+        <v>0.4298221458965207</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.970276919375829</v>
+        <v>3.909293001589227</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.930080957144504</v>
+        <v>-5.187688230886843</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.67116379412394</v>
+        <v>1.568120884627004</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.5546665807914652</v>
+        <v>0.4530267178137959</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.976352549770369</v>
+        <v>3.915368631983768</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.787021381403578</v>
+        <v>-5.044628655145917</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.732637635142285</v>
+        <v>1.629594725645349</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.5626800073814445</v>
+        <v>0.4610401444037752</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.985410616446331</v>
+        <v>3.92442669865973</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.485574655931741</v>
+        <v>-4.74318192967408</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.860477208213556</v>
+        <v>1.75743429871662</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.8641267328532818</v>
+        <v>0.7624868698756124</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.17353953461197</v>
+        <v>4.112555616825368</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.510164900166925</v>
+        <v>-4.767772173909264</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.851612288272193</v>
+        <v>1.748569378775257</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.8641267328532818</v>
+        <v>0.7624868698756124</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.17451071236468</v>
+        <v>4.113526794578078</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.459126524160404</v>
+        <v>-4.716733797902743</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.872870543054557</v>
+        <v>1.769827633557621</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.8641267328532818</v>
+        <v>0.7624868698756124</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.175353616744435</v>
+        <v>4.114369698957834</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.417987229293773</v>
+        <v>-4.675594503036113</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.908364359875355</v>
+        <v>1.805321450378419</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.9052660277199126</v>
+        <v>0.8036261647422432</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.21907529253856</v>
+        <v>4.158091374751958</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.321352317275133</v>
+        <v>-4.578959591017473</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.763202320806745</v>
+        <v>1.660159411309809</v>
       </c>
       <c r="F2033" t="n">
-        <v>1.001900939738553</v>
+        <v>0.9002610767608832</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.093240235873678</v>
+        <v>4.032256318087077</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.451933051805976</v>
+        <v>-4.709540325548315</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.714472071068372</v>
+        <v>1.611429161571436</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.87132020520771</v>
+        <v>0.7696803422300407</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.018393839229137</v>
+        <v>3.957409921442535</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.287436717615014</v>
+        <v>-4.545043991357353</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.764697423820839</v>
+        <v>1.661654514323904</v>
       </c>
       <c r="F2035" t="n">
-        <v>1.035816539398672</v>
+        <v>0.9341766764210025</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.101518458819797</v>
+        <v>4.040534541033195</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.210338116073141</v>
+        <v>-4.467945389815481</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.794724574874018</v>
+        <v>1.691681665377083</v>
       </c>
       <c r="F2036" t="n">
-        <v>1.035816539398672</v>
+        <v>0.9341766764210025</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.100706169256227</v>
+        <v>4.039722251469625</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.220723310963031</v>
+        <v>-4.47833058470537</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.800439276043135</v>
+        <v>1.697396366546199</v>
       </c>
       <c r="F2037" t="n">
-        <v>1.025431344508783</v>
+        <v>0.9237914815311132</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.104343831447365</v>
+        <v>4.043359913660764</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.239311469685256</v>
+        <v>-4.496918743427595</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.86384101833067</v>
+        <v>1.760798108833734</v>
       </c>
       <c r="F2038" t="n">
-        <v>1.006843185786557</v>
+        <v>0.9052033228088878</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.164027941990455</v>
+        <v>4.103044024203854</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.855120535496556</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.239610016381292</v>
+        <v>-4.497217290123631</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.860590610470554</v>
+        <v>1.757547700973618</v>
       </c>
       <c r="F2039" t="n">
-        <v>1.006544639090521</v>
+        <v>0.9049047761128519</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.160717824791132</v>
+        <v>4.099733907004531</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.138786882690864</v>
+        <v>-4.396394156433203</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.905450758886117</v>
+        <v>1.802407849389181</v>
       </c>
       <c r="F2040" t="n">
-        <v>1.019008854574875</v>
+        <v>0.9173689915972058</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.172727249021135</v>
+        <v>4.111743331234534</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-3.948005521938457</v>
+        <v>-4.205612795680796</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.981892556665623</v>
+        <v>1.878849647168687</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.209790215327283</v>
+        <v>1.108150352349613</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.287325318951123</v>
+        <v>4.226341401164522</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.841042164089035</v>
+        <v>-4.098649437831375</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.004514745542989</v>
+        <v>1.901471836046052</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.268254823287084</v>
+        <v>1.166614960309415</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.302240929464601</v>
+        <v>4.241257011677999</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.785711576187273</v>
+        <v>-4.043318849929612</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.061613917315752</v>
+        <v>1.958571007818816</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.323585411188846</v>
+        <v>1.221945548211177</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.370406218817717</v>
+        <v>4.309422301031115</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.77365744927431</v>
+        <v>-4.031264723016649</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.060122135982374</v>
+        <v>1.957079226485439</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.335639538101809</v>
+        <v>1.23399967512414</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.371325262866932</v>
+        <v>4.31034134508033</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.814812568842531</v>
+        <v>-4.07241984258487</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.045540718339222</v>
+        <v>1.942497808842286</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.294484418533588</v>
+        <v>1.192844555555919</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.348512821310135</v>
+        <v>4.287528903523533</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.746764006151001</v>
+        <v>-4.00437127989334</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.085611169293716</v>
+        <v>1.98256825979678</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.362532981225118</v>
+        <v>1.260893118247449</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.402192984802936</v>
+        <v>4.341209067016334</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013426</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-3.978364399320502</v>
+        <v>-4.235971673062841</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.01317368219951</v>
+        <v>1.910130772702574</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.362532981225118</v>
+        <v>1.260893118247449</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.42239565497653</v>
+        <v>4.361411737189928</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498971</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.028415944849721</v>
+        <v>-4.28602321859206</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.976759300054705</v>
+        <v>1.873716390557769</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.362532981225118</v>
+        <v>1.260893118247449</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.406001891043412</v>
+        <v>4.345017973256811</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.6700487028001</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.203522777426166</v>
+        <v>-4.461130051168505</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.866968480617593</v>
+        <v>1.763925571120658</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.362532981225118</v>
+        <v>1.260893118247449</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.366253804636878</v>
+        <v>4.305269886850277</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660853</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.007422623995643</v>
+        <v>-4.265029897737982</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.952431160986742</v>
+        <v>1.849388251489807</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.558633134655641</v>
+        <v>1.456993271677971</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.490936515692132</v>
+        <v>4.429952597905531</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.73057047339509</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.854397231882359</v>
+        <v>-4.112004505624697</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.11281231740496</v>
+        <v>2.009769407908025</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.711658526768925</v>
+        <v>1.610018663791255</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.681922750533007</v>
+        <v>4.620938832746406</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74127833279115</v>
+        <v>3.741278332791151</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.882704545755629</v>
+        <v>-4.140311819497968</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.288955616763945</v>
+        <v>2.185912707267009</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.711658526768925</v>
+        <v>1.610018663791255</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.8693889754413</v>
+        <v>4.808405057654698</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620437</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.049297770869151</v>
+        <v>-4.30690504461149</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.191721278072619</v>
+        <v>2.088678368575683</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.545065301655402</v>
+        <v>1.443425438677733</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.738835991727269</v>
+        <v>4.677852073940667</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285648</v>
+        <v>3.70818251928565</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.026261977507585</v>
+        <v>-4.283869251249924</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.204611998078963</v>
+        <v>2.101569088582028</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.545065301655402</v>
+        <v>1.443425438677733</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.742512394388987</v>
+        <v>4.681528476602385</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.74058140139947</v>
+        <v>3.740581401399472</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-3.997015997051889</v>
+        <v>-4.254623270794228</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.213928445384737</v>
+        <v>2.110885535887801</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.545065301655402</v>
+        <v>1.443425438677733</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.740130449512482</v>
+        <v>4.67914653172588</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256371</v>
+        <v>3.699404642256373</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.10394154492974</v>
+        <v>-4.361548818672079</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.168451465391231</v>
+        <v>2.065408555894296</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.438139753777551</v>
+        <v>1.336499890799882</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.673268359943406</v>
+        <v>4.612284442156804</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701001</v>
+        <v>3.689942600701003</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.248960103436989</v>
+        <v>-4.506567377179327</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.111872844131566</v>
+        <v>2.008829934634631</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.293121195270303</v>
+        <v>1.191481332292633</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.587686026982292</v>
+        <v>4.526702109195689</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687014</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.367301869221706</v>
+        <v>-4.624909142964045</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.164467377075432</v>
+        <v>2.061424467578497</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.303807233833193</v>
+        <v>1.202167370855523</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.694028889377778</v>
+        <v>4.633044971591176</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.714879051790804</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.418712291542414</v>
+        <v>-4.676319565284753</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.141688905273088</v>
+        <v>2.038645995776152</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.303807233833193</v>
+        <v>1.202167370855523</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.691814586503718</v>
+        <v>4.630830668717116</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437331</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.498131742750166</v>
+        <v>-4.755739016492504</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.109824252864276</v>
+        <v>2.006781343367341</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.303807233833193</v>
+        <v>1.202167370855523</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.691717714578006</v>
+        <v>4.630733796791405</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298398</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.593594740667384</v>
+        <v>-4.851202014409722</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.071632947255432</v>
+        <v>1.968590037758497</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.303807233833193</v>
+        <v>1.202167370855523</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.69171160813605</v>
+        <v>4.630727690349448</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960218</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.529218829816669</v>
+        <v>-4.786826103559007</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.095479708158329</v>
+        <v>1.992436798661394</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.368183144683908</v>
+        <v>1.266543281706239</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.728433551209089</v>
+        <v>4.667449633422487</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353535</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.584587991948863</v>
+        <v>-4.842195265691201</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.079065861053178</v>
+        <v>1.976022951556243</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.368183144683908</v>
+        <v>1.266543281706239</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.734167368956816</v>
+        <v>4.673183451170214</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113278</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.63002577177969</v>
+        <v>-4.887633045522028</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.06042911246378</v>
+        <v>1.957386202966844</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.325338154005748</v>
+        <v>1.223698291028079</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.707998737892853</v>
+        <v>4.647014820106251</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113687</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.541818937632112</v>
+        <v>-4.79942621137445</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.11558623897313</v>
+        <v>2.012543329476194</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.325338154005748</v>
+        <v>1.223698291028079</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.727873130743172</v>
+        <v>4.66688921295657</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016441</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.435783942426802</v>
+        <v>-4.69339121616914</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.141700937579981</v>
+        <v>2.038658028083046</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.325338154005748</v>
+        <v>1.223698291028079</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.711573831267899</v>
+        <v>4.650589913481298</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307672</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.252572279293707</v>
+        <v>-4.510179553036045</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.217416552297265</v>
+        <v>2.114373642800329</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.325338154005748</v>
+        <v>1.223698291028079</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.714004780731945</v>
+        <v>4.653020862945343</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.180850832279856</v>
+        <v>-4.438458106022194</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.211896316950695</v>
+        <v>2.108853407453759</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.397059601019599</v>
+        <v>1.29541973804193</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.722828834788145</v>
+        <v>4.661844917001543</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394114</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.15847780667215</v>
+        <v>-4.416085080414488</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.167761273114949</v>
+        <v>2.064718363618014</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.4083153521325</v>
+        <v>1.306675489154831</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.676498031377058</v>
+        <v>4.615514113590455</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.191494102582895</v>
+        <v>-4.449101376325233</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.339752959636006</v>
+        <v>2.236710050139071</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.338877975465749</v>
+        <v>1.23723811248808</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.820033810262362</v>
+        <v>4.75904989247576</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883677</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.179966466933286</v>
+        <v>-4.437573740675624</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.336285239724099</v>
+        <v>2.233242330227164</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.397878633667111</v>
+        <v>1.296238770689442</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.847355431011428</v>
+        <v>4.786371513224826</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236297</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.277307968275655</v>
+        <v>-4.534915242017993</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.30101675170894</v>
+        <v>2.197973842212004</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.353458451501623</v>
+        <v>1.251818588523954</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.824371434233924</v>
+        <v>4.763387516447322</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427683</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.363163997615621</v>
+        <v>-4.62077127135796</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.267925422165791</v>
+        <v>2.164882512668856</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.311082382275488</v>
+        <v>1.209442519297819</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.800196874891081</v>
+        <v>4.739212957104479</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610383</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.372000795031741</v>
+        <v>-4.629608068774079</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.246809905019846</v>
+        <v>2.14376699552291</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.303640209634137</v>
+        <v>1.202000346656468</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.778150773126772</v>
+        <v>4.717166855340171</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667454</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.463383357597199</v>
+        <v>-4.720990631339538</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.220421391038712</v>
+        <v>2.117378481541776</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.267075324914793</v>
+        <v>1.165435461937123</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.766376353340215</v>
+        <v>4.705392435553613</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.67397837488919</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.451676639610193</v>
+        <v>-4.709283913352531</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.327232336057781</v>
+        <v>2.224189426560846</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.278782042901799</v>
+        <v>1.17714217992413</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.875528641956686</v>
+        <v>4.814544724170084</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409566</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.352013135526531</v>
+        <v>-4.609620409268869</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.370130076422651</v>
+        <v>2.267087166925716</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.341969126105486</v>
+        <v>1.240329263127816</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.916473230610302</v>
+        <v>4.855489312823702</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452573</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.362329233692883</v>
+        <v>-4.619936507435221</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.578908470434168</v>
+        <v>2.475865560937233</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.341969126105486</v>
+        <v>1.240329263127816</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.12937806388836</v>
+        <v>5.06839414610176</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762286</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.36223526567551</v>
+        <v>-4.619842539417848</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.578124724553207</v>
+        <v>2.475081815056272</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.342338987452804</v>
+        <v>1.240699124475134</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.128778647608842</v>
+        <v>5.067794729822239</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988017</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.369454089875354</v>
+        <v>-4.627061363617693</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.569469180817623</v>
+        <v>2.466426271320688</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.342338987452804</v>
+        <v>1.240699124475134</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.123010633553195</v>
+        <v>5.062026715766594</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740923</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.368505666757316</v>
+        <v>-4.626112940499654</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.569848550064838</v>
+        <v>2.466805640567903</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.342338987452804</v>
+        <v>1.240699124475134</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.123010633553195</v>
+        <v>5.062026715766594</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663627</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.525574125012939</v>
+        <v>-4.783181398755278</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.519748774743681</v>
+        <v>2.416705865246746</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.342338987452804</v>
+        <v>1.240699124475134</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.135738241534288</v>
+        <v>5.074754323747685</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424771</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.519581878224128</v>
+        <v>-4.777189151966467</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.524091671883594</v>
+        <v>2.421048762386658</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.342338987452804</v>
+        <v>1.240699124475134</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.137684239958675</v>
+        <v>5.076700322172073</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149219</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.43102391709336</v>
+        <v>-4.688631190835699</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.553168992353669</v>
+        <v>2.450126082856734</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.342338987452804</v>
+        <v>1.240699124475134</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.131338375976444</v>
+        <v>5.070354458189842</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383092</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.413264839590286</v>
+        <v>-4.670872113332625</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.559581300793894</v>
+        <v>2.456538391296959</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.342338987452804</v>
+        <v>1.240699124475134</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.130647053415439</v>
+        <v>5.069663135628838</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720999</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.313634688541218</v>
+        <v>-4.571241962283557</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.612215547122108</v>
+        <v>2.509172637625173</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.441969138501871</v>
+        <v>1.340329275524202</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.203207329953467</v>
+        <v>5.142223412166866</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455273</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.363034197230229</v>
+        <v>-4.620641470972568</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.78161000914523</v>
+        <v>2.678567099648295</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.452227971933616</v>
+        <v>1.350588108955947</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.39851689551124</v>
+        <v>5.337532977724639</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.749078058963134</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.156349723587853</v>
+        <v>-4.413956997330192</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.851472471705043</v>
+        <v>2.748429562208107</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.658912445575992</v>
+        <v>1.557272582598322</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.509716252799527</v>
+        <v>5.448732335012926</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162539</v>
+        <v>3.740284389162541</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.156156687804433</v>
+        <v>-4.448113892327719</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.853551199672516</v>
+        <v>2.736768317863202</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.659089346624647</v>
+        <v>1.47368881305751</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.511823907082825</v>
+        <v>5.400583586942544</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.981726001287928</v>
+        <v>3.6000377477571</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.892051269809499</v>
+        <v>4.464614027191413</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.156156687804433</v>
+        <v>-4.448113892327719</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.853551199672516</v>
+        <v>2.736768317863202</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.659089346624647</v>
+        <v>1.47368881305751</v>
       </c>
       <c r="G2090" t="n">
-        <v>4.885115066795866</v>
+        <v>4.457677824177781</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240917.xlsx
+++ b/tame_output/ON/bt/strategyON_20240917.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-72.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.1%</t>
+          <t>420.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-606.4%</t>
+          <t>-615.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-102.5%</t>
+          <t>-106.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>-55.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-342.6%</t>
+          <t>-327.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-85.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,31 +1423,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.226054034658109</v>
+        <v>-7.338778816372826</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2606819359262631</v>
+        <v>0.2155920232403763</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9476778951207698</v>
+        <v>-1.060402676835486</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.582853237030793</v>
+        <v>2.515218368001963</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.062654163718746</v>
+        <v>-7.175378945433463</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.325408705522765</v>
+        <v>0.2803187928368782</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7842780241814074</v>
+        <v>-0.8970028058961237</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.680259980815167</v>
+        <v>2.612625111786337</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.829172941489148</v>
+        <v>-6.941897723203865</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4267256232524566</v>
+        <v>0.3816357105665698</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5507968019518088</v>
+        <v>-0.6635215836665251</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.828273142990779</v>
+        <v>2.760638273961949</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.679506550481633</v>
+        <v>-6.79223133219635</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4836999693425037</v>
+        <v>0.4386100566566169</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4578933107092729</v>
+        <v>-0.5706180924239892</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.881123027423341</v>
+        <v>2.813488158394511</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.547231076850746</v>
+        <v>-6.659955858565463</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4378709448020128</v>
+        <v>0.392781032116126</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3256178370783862</v>
+        <v>-0.4383426187931025</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.861749097609028</v>
+        <v>2.794114228580198</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.375369861285844</v>
+        <v>-6.488094643000561</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5094304917156105</v>
+        <v>0.4643405790297237</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1537566215134833</v>
+        <v>-0.2664814032281997</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.967680887635606</v>
+        <v>2.900046018606776</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.290405194556524</v>
+        <v>-6.403129976271241</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5563226996309973</v>
+        <v>0.5112327869451101</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06879195478416378</v>
+        <v>-0.1815167364988801</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.031566028896857</v>
+        <v>2.963931159868027</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.395995184329628</v>
+        <v>-6.508719966044346</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3861107741225367</v>
+        <v>0.3410208614366494</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1743819445572681</v>
+        <v>-0.2871067262719845</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.840236105433775</v>
+        <v>2.772601236404946</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.327760599704201</v>
+        <v>-6.440485381418918</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.461948949849794</v>
+        <v>0.4168590371639072</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1559666216847321</v>
+        <v>-0.2686914033994485</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.899829641034383</v>
+        <v>2.832194772005554</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.179820558296601</v>
+        <v>-6.292545340011319</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4045041577744266</v>
+        <v>0.3594142450885398</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1356457057761746</v>
+        <v>-0.2483704874908909</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.795401381941111</v>
+        <v>2.727766512912281</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.126851036042613</v>
+        <v>-6.239575817757331</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4169779804225442</v>
+        <v>0.3718880677366569</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.0826761835221857</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.818469109040026</v>
+        <v>2.750834240011196</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.961062840082322</v>
+        <v>-6.07378762179704</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4763326467115672</v>
+        <v>0.4312427340256799</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.0826761835221857</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.811508496944933</v>
+        <v>2.743873627916103</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.927699633603553</v>
+        <v>-6.040424415318271</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5041402836842179</v>
+        <v>0.4590503709983307</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.0826761835221857</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.825970851326076</v>
+        <v>2.758335982297246</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.819440496481032</v>
+        <v>-5.932165278195749</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5419760589924216</v>
+        <v>0.4968861463065344</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.0826761835221857</v>
+        <v>-0.195400965236902</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.820502971785271</v>
+        <v>2.752868102756441</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.696149361663901</v>
+        <v>-5.808874143378619</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5887906069298507</v>
+        <v>0.5437006942439635</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.0406149512949448</v>
+        <v>-0.07210983041977154</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.891975746686126</v>
+        <v>2.824340877657296</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.643452494532609</v>
+        <v>-5.756177276247327</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6175703320196924</v>
+        <v>0.5724804193338051</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.09331181842623598</v>
+        <v>-0.01941296328848036</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.931294845202226</v>
+        <v>2.863659976173396</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.399687052549165</v>
+        <v>-5.512411834263883</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7108572171601208</v>
+        <v>0.6657673044742336</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.09331181842623598</v>
+        <v>-0.01941296328848036</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.927075553549277</v>
+        <v>2.859440684520447</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.309911380172693</v>
+        <v>-5.422636161887411</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7488918000307256</v>
+        <v>0.7038018873448384</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.154911263340546</v>
+        <v>0.04218648162582966</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.966159534417879</v>
+        <v>2.898524665389049</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.060060986223618</v>
+        <v>-5.172785767938336</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8415740325940577</v>
+        <v>0.7964841199081705</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.154911263340546</v>
+        <v>0.04218648162582966</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.958901609401581</v>
+        <v>2.891266740372751</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.884168893756186</v>
+        <v>-4.996893675470904</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9155299931016794</v>
+        <v>0.8704400804157921</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.154911263340546</v>
+        <v>0.04218648162582966</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.962500732922229</v>
+        <v>2.8948658638934</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.712722430733723</v>
+        <v>-4.825447212448441</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9974360843652184</v>
+        <v>0.9523461716793311</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3263577263630091</v>
+        <v>0.2136329446482928</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.078696116790261</v>
+        <v>3.011061247761432</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.632700143624602</v>
+        <v>-4.74542492533932</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.028465476825164</v>
+        <v>0.9833755641392765</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.4063800134721301</v>
+        <v>0.2936552317574138</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.125729966672031</v>
+        <v>3.058095097643201</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.569064401390667</v>
+        <v>-4.681789183105385</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.058614574773055</v>
+        <v>1.013524662087168</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4700157557060646</v>
+        <v>0.3572909739913483</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.168606213066709</v>
+        <v>3.100971344037879</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.475367083174272</v>
+        <v>-4.58809186488899</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.077287760843408</v>
+        <v>1.032197848157521</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4700157557060646</v>
+        <v>0.3572909739913483</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.149800471850504</v>
+        <v>3.082165602821675</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.485869706239561</v>
+        <v>-4.598594487954279</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.07482978824217</v>
+        <v>1.029739875556283</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4595131326407758</v>
+        <v>0.3467883509260594</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.145241974636209</v>
+        <v>3.077607105607379</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.373383445570687</v>
+        <v>-4.486108227285404</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.12375360634454</v>
+        <v>1.078663693658653</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4595131326407758</v>
+        <v>0.3467883509260594</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.149171288471029</v>
+        <v>3.081536419442199</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.355669758692821</v>
+        <v>-4.468394540407539</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.131517665013027</v>
+        <v>1.086427752327139</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4626944615376926</v>
+        <v>0.3499696798229762</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.151758669726519</v>
+        <v>3.084123800697689</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.232195487379803</v>
+        <v>-4.344920269094521</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.177905444758227</v>
+        <v>1.13281553207234</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4626944615376926</v>
+        <v>0.3499696798229762</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.148756740946512</v>
+        <v>3.081121871917682</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.143666626641847</v>
+        <v>-4.2309956657824</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.214896026064024</v>
+        <v>1.179964410407803</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5220884576801976</v>
+        <v>0.4307728428842427</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.185972175642629</v>
+        <v>3.131182806765056</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.01079893757857</v>
+        <v>-4.098127976719122</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.283937284491158</v>
+        <v>1.249005668834937</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5220884576801976</v>
+        <v>0.4307728428842427</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.201866358444453</v>
+        <v>3.14707698956688</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.890625854214071</v>
+        <v>-3.977954893354624</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.333152362277259</v>
+        <v>1.298220746621038</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6422615410446966</v>
+        <v>0.5509459262487416</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.275116052903454</v>
+        <v>3.220326684025881</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.755372492884094</v>
+        <v>-3.842701532024646</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.39734180937069</v>
+        <v>1.362410193714469</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7775149023746737</v>
+        <v>0.6861992875787187</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.36635617226288</v>
+        <v>3.311566803385307</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.815247320241786</v>
+        <v>-3.902576359382339</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.359429369829039</v>
+        <v>1.324497754172818</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7176400750169816</v>
+        <v>0.6263244602210266</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.316468767249691</v>
+        <v>3.261679398372118</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.695427089330949</v>
+        <v>-3.782756128471501</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.422646631427583</v>
+        <v>1.387715015771361</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7176400750169816</v>
+        <v>0.6263244602210266</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.331757936483899</v>
+        <v>3.276968567606326</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.697896795792755</v>
+        <v>-3.785225834933307</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.329302948165302</v>
+        <v>1.294371332509081</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7151703685551754</v>
+        <v>0.6238547537592205</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.237920311929257</v>
+        <v>3.183130943051684</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.766266982116765</v>
+        <v>-3.853596021257317</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.221216735120999</v>
+        <v>1.186285119464778</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7244460675913903</v>
+        <v>0.6331304527954354</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.162747592836287</v>
+        <v>3.107958223958715</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.878139261742915</v>
+        <v>-3.965468300883468</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.16690453190243</v>
+        <v>1.131972916246209</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7244460675913903</v>
+        <v>0.6331304527954354</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.153184301468179</v>
+        <v>3.098394932590605</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.862164596256648</v>
+        <v>-3.9494936353972</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.139868923020965</v>
+        <v>1.104937307364743</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7244460675913903</v>
+        <v>0.6331304527954354</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.119758826392206</v>
+        <v>3.064969457514633</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.686690336464178</v>
+        <v>-3.774019375604731</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.21462585892974</v>
+        <v>1.179694243273519</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7244460675913903</v>
+        <v>0.6331304527954354</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.124326058383994</v>
+        <v>3.069536689506421</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.678765961879264</v>
+        <v>-3.766095001019817</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.193537637524913</v>
+        <v>1.158606021868692</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7244460675913903</v>
+        <v>0.6331304527954354</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.100068087145201</v>
+        <v>3.045278718267628</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.672487759309415</v>
+        <v>-3.759816798449968</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.124587231954302</v>
+        <v>1.089655616298081</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7307242701612393</v>
+        <v>0.6394086553652845</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.03237332208856</v>
+        <v>2.977583953210987</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.612635140105692</v>
+        <v>-3.699964179246245</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.158700666067924</v>
+        <v>1.123769050411703</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7307242701612393</v>
+        <v>0.6394086553652845</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.042545708520692</v>
+        <v>2.987756339643119</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.526391677079315</v>
+        <v>-3.613720716219867</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.188144321852335</v>
+        <v>1.153212706196114</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7307242701612393</v>
+        <v>0.6394086553652845</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.037491979094553</v>
+        <v>2.98270261021698</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.571698496478295</v>
+        <v>-3.659027535618847</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.161797369537269</v>
+        <v>1.126865753881048</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6899141071520085</v>
+        <v>0.5985984923560537</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.00478165673354</v>
+        <v>2.949992287855967</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.600731601180596</v>
+        <v>-3.688060640321149</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.15073600068945</v>
+        <v>1.115804385033229</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6899141071520085</v>
+        <v>0.5985984923560537</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.005333529766641</v>
+        <v>2.950544160889069</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.507921119729737</v>
+        <v>-3.595250158870289</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.117132885161159</v>
+        <v>1.082201269504938</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7827245886028679</v>
+        <v>0.691408973806913</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.990292510528523</v>
+        <v>2.93550314165095</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.552310589059164</v>
+        <v>-3.639639628199717</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.101250573353989</v>
+        <v>1.066318957697768</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7383351192734402</v>
+        <v>0.6470195044774854</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.965532304855467</v>
+        <v>2.910742935977894</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.531806895173667</v>
+        <v>-3.61913593431422</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.104527759419911</v>
+        <v>1.06959614376369</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7588388131589375</v>
+        <v>0.6675231983629827</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.972910229698488</v>
+        <v>2.918120860820915</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.571730989756239</v>
+        <v>-3.659060028896792</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.094049417417549</v>
+        <v>1.059117801761328</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7588388131589375</v>
+        <v>0.6675231983629827</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.978401525529156</v>
+        <v>2.923612156651583</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.599511387657592</v>
+        <v>-3.686840426798145</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.094434460025547</v>
+        <v>1.059502844369326</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7310584152575845</v>
+        <v>0.6397428004616297</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.973230488556883</v>
+        <v>2.91844111967931</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.717892060387731</v>
+        <v>-3.805221099528283</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8854379109341448</v>
+        <v>0.8505062952779237</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6638405631066083</v>
+        <v>0.5725249483106535</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.77125549726695</v>
+        <v>2.716466128389377</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.826506138831062</v>
+        <v>-3.913835177971615</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9621419402760178</v>
+        <v>0.9272103246197969</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6638405631066083</v>
+        <v>0.5725249483106535</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.891405157986156</v>
+        <v>2.836615789108583</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.791097100582919</v>
+        <v>-3.878426139723472</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9908185816775981</v>
+        <v>0.9558869660213771</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6638405631066083</v>
+        <v>0.5725249483106535</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.905918184088479</v>
+        <v>2.851128815210906</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.79955826923838</v>
+        <v>-3.886887308378933</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9848535555577822</v>
+        <v>0.9499219399015613</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6553793944511472</v>
+        <v>0.5640637796551924</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.898260924237571</v>
+        <v>2.843471555359998</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.622441939203214</v>
+        <v>-3.709770978343767</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.052429116417151</v>
+        <v>1.01749750076093</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6553793944511472</v>
+        <v>0.5640637796551924</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.894989953082873</v>
+        <v>2.8402005842053</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.66753418403676</v>
+        <v>-3.754863223177312</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.035075610245646</v>
+        <v>1.000143994589425</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5934833512817574</v>
+        <v>0.5021677364858026</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.858535718943152</v>
+        <v>2.803746350065579</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.488158762797992</v>
+        <v>-3.575487801938545</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.100612754047567</v>
+        <v>1.065681138391346</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7502601094524761</v>
+        <v>0.6589444946565213</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.946388749151998</v>
+        <v>2.891599380274425</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.533172976318598</v>
+        <v>-3.620502015459151</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.063414523970915</v>
+        <v>1.028482908314694</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7199112141378715</v>
+        <v>0.6285955993419167</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.908986867294825</v>
+        <v>2.854197498417252</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.800177486591034</v>
+        <v>-3.887506525731586</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9623042822008863</v>
+        <v>0.9273726665446651</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.525548176094923</v>
+        <v>0.4342325612989681</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.798060606808002</v>
+        <v>2.743271237930429</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.901375268028207</v>
+        <v>-3.988704307168759</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9210290915225186</v>
+        <v>0.8860974758662974</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4571393625496038</v>
+        <v>0.3658237477536489</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.756219240577312</v>
+        <v>2.701429871699739</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.894864301413894</v>
+        <v>-3.982193340554447</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9212334397225603</v>
+        <v>0.8863018240663392</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4571393625496038</v>
+        <v>0.3658237477536489</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.753819202131628</v>
+        <v>2.699029833254055</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.875826173706597</v>
+        <v>-3.963155212847149</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9253734100137241</v>
+        <v>0.8904417943575031</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3989557512184093</v>
+        <v>0.3076401364224544</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.715433754541157</v>
+        <v>2.660644385663584</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.928341975981417</v>
+        <v>-4.01567101512197</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.023661490737986</v>
+        <v>0.9887298750817652</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3989557512184093</v>
+        <v>0.3076401364224544</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.834728156175347</v>
+        <v>2.779938787297774</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.931750287415996</v>
+        <v>-4.019079326556549</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.023131495150288</v>
+        <v>0.988199879494067</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4314723202277866</v>
+        <v>0.3401567054318317</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.855071426567107</v>
+        <v>2.800282057689534</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.912394151522149</v>
+        <v>-3.999723190662702</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.036882479904753</v>
+        <v>1.001950864248532</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4314723202277866</v>
+        <v>0.3401567054318317</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.861079956964033</v>
+        <v>2.80629058808646</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.764651181287147</v>
+        <v>-3.8519802204277</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9939298892759532</v>
+        <v>0.958998273619732</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5992796774626699</v>
+        <v>0.5079640626667149</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.859714592582162</v>
+        <v>2.804925223704589</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.848472402561845</v>
+        <v>-3.935801441702398</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9631950222975549</v>
+        <v>0.9282634066413338</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5992796774626699</v>
+        <v>0.5079640626667149</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.862508214113643</v>
+        <v>2.80771884523607</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.842319696509061</v>
+        <v>-3.929648735649614</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.966318453110327</v>
+        <v>0.9313868374541059</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6054323835154541</v>
+        <v>0.5141167687194992</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.866862186136972</v>
+        <v>2.812072817259399</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.859128994659562</v>
+        <v>-3.946458033800115</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9586752105902367</v>
+        <v>0.9237435949340156</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5886230853649526</v>
+        <v>0.4973074705689975</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.855857083986781</v>
+        <v>2.801067715109208</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.796830995883441</v>
+        <v>-3.884160035023994</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.049929963897506</v>
+        <v>1.014998348241285</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6339173496393946</v>
+        <v>0.5426017348434395</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.949369196348268</v>
+        <v>2.894579827470694</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.595040798218283</v>
+        <v>-3.682369837358836</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9329380446776967</v>
+        <v>0.8980064290214753</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.831935541808549</v>
+        <v>0.7406199270125939</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.870472113363888</v>
+        <v>2.815682744486314</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.645927510904477</v>
+        <v>-3.73325655004503</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9828735919253939</v>
+        <v>0.9479419762691728</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7810488291223545</v>
+        <v>0.6897332143263994</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.910230318074346</v>
+        <v>2.855440949196773</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.55931676825467</v>
+        <v>-3.646645807395223</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.032145625101361</v>
+        <v>0.9972140094451394</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8596745603275128</v>
+        <v>0.7683589455315577</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.972033492913484</v>
+        <v>2.917244124035911</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.619526066259954</v>
+        <v>-3.706855105400507</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.006597886723918</v>
+        <v>0.9716662710676971</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7994652623222283</v>
+        <v>0.7081496475262732</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.934443894934986</v>
+        <v>2.879654526057412</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.570339417575603</v>
+        <v>-3.657668456716156</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.024764164237588</v>
+        <v>0.9898325485813664</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7994652623222283</v>
+        <v>0.7081496475262732</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.932935512974914</v>
+        <v>2.878146144097341</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.525966285937034</v>
+        <v>-3.613295325077587</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.042376284328451</v>
+        <v>1.00744466867223</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8438383939607969</v>
+        <v>0.7525227791648418</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.959422259393491</v>
+        <v>2.904632890515918</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.548446636795919</v>
+        <v>-3.635775675936472</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.027777938123488</v>
+        <v>0.9928463224672666</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8438383939607969</v>
+        <v>0.7525227791648418</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.953816053532082</v>
+        <v>2.899026684654509</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.500790906234863</v>
+        <v>-3.588119945375417</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.053221987375715</v>
+        <v>1.018290371719493</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8914941245218525</v>
+        <v>0.8001785097258974</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.98879124889652</v>
+        <v>2.934001880018947</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.400272747736109</v>
+        <v>-3.487601786876662</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.098321624149941</v>
+        <v>1.06339000849372</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9920122830206071</v>
+        <v>0.900696668224652</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.053994517370497</v>
+        <v>2.999205148492925</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.384367418303756</v>
+        <v>-3.47169645744431</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.091438428398755</v>
+        <v>1.056506812742533</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9128996223113681</v>
+        <v>0.8215840075154131</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.993281593420826</v>
+        <v>2.938492224543253</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.339529016695358</v>
+        <v>-3.426858055835912</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.113471491652742</v>
+        <v>1.078539875996521</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9174430552562376</v>
+        <v>0.8261274404602825</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.000105355798377</v>
+        <v>2.945315986920804</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.359027472937366</v>
+        <v>-3.44635651207792</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.109833048787017</v>
+        <v>1.074901433130796</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8693584139763333</v>
+        <v>0.7780427991803782</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.975415510661512</v>
+        <v>2.920626141783939</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.314824635851466</v>
+        <v>-3.402153674992019</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.133393786149214</v>
+        <v>1.098462170492993</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9135612510622337</v>
+        <v>0.8222456362662787</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.007816815440889</v>
+        <v>2.953027446563316</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.322384301688513</v>
+        <v>-3.409713340829066</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.128779920283643</v>
+        <v>1.093848304627422</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.968364655072053</v>
+        <v>0.877049040276098</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.039108858316029</v>
+        <v>2.984319489438455</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.164092884149241</v>
+        <v>-3.251421923289794</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.243344252482392</v>
+        <v>1.208412636826171</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.968364655072053</v>
+        <v>0.877049040276098</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.090356623499068</v>
+        <v>3.035567254621495</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.956450880514764</v>
+        <v>-3.043779919655318</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.324841758530436</v>
+        <v>1.289910142874214</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.176006658706529</v>
+        <v>1.084691043910574</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.213382530274007</v>
+        <v>3.158593161396434</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.905418787792236</v>
+        <v>-2.99274782693279</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.340202823857717</v>
+        <v>1.305271208201495</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.227038751429057</v>
+        <v>1.135723136633102</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.238950014145794</v>
+        <v>3.184160645268221</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.840194606665031</v>
+        <v>-2.927523645805584</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.383479900401304</v>
+        <v>1.348548284745082</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.292262932556263</v>
+        <v>1.200947317760308</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.295271926914822</v>
+        <v>3.240482558037249</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.802767586593897</v>
+        <v>-2.89009662573445</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.394411680729038</v>
+        <v>1.359480065072816</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.297514470585444</v>
+        <v>1.20619885578949</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.294383822031612</v>
+        <v>3.239594453154039</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.801409601620351</v>
+        <v>-2.888738640760905</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.396211667049696</v>
+        <v>1.361280051393475</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.371852596123263</v>
+        <v>1.280536981327308</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.340243489685543</v>
+        <v>3.28545412080797</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.772996338520468</v>
+        <v>-2.860325377661021</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.568134743310861</v>
+        <v>1.533203127654639</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.312877033376834</v>
+        <v>1.221561418580879</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.465415923058896</v>
+        <v>3.410626554181324</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.698214077495455</v>
+        <v>-2.785543116636009</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.718160556938683</v>
+        <v>1.683228941282461</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.387659294401847</v>
+        <v>1.296343679605892</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.630398188891721</v>
+        <v>3.575608820014148</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.672129993231647</v>
+        <v>-2.759459032372201</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.720302166658065</v>
+        <v>1.685370551001844</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.387659294401847</v>
+        <v>1.296343679605892</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.62210616490558</v>
+        <v>3.567316796028007</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.584252080122527</v>
+        <v>-2.67158111926308</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.753646527485493</v>
+        <v>1.718714911829271</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.503584936825198</v>
+        <v>1.412269322029243</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.68985474594337</v>
+        <v>3.635065377065797</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.575359618729244</v>
+        <v>-2.662688657869797</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.774757917769597</v>
+        <v>1.739826302113376</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.503584936825198</v>
+        <v>1.412269322029243</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.707409151670161</v>
+        <v>3.652619782792589</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.743835735699121</v>
+        <v>-2.831164774839675</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.69922251838623</v>
+        <v>1.664290902730009</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.475637101108617</v>
+        <v>1.384321486312662</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.682495497644797</v>
+        <v>3.627706128767224</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.297579543069681</v>
+        <v>-2.384908582210235</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.858994692625868</v>
+        <v>1.824063076969646</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.380918431438984</v>
+        <v>1.28960281664303</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.606933993030879</v>
+        <v>3.552144624153306</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.274858439386529</v>
+        <v>-2.362187478527082</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.858747156596033</v>
+        <v>1.823815540939812</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.380918431438984</v>
+        <v>1.28960281664303</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.597598015527784</v>
+        <v>3.542808646650211</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.404060252680571</v>
+        <v>-2.491389291821125</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.965972557129585</v>
+        <v>1.931040941473364</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.251716618144942</v>
+        <v>1.160401003348987</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.678983053402527</v>
+        <v>3.624193684524954</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.429934651154597</v>
+        <v>-2.517263690295151</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.992700620233622</v>
+        <v>1.957769004577401</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.296628226856683</v>
+        <v>1.205312612060728</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.743007841123219</v>
+        <v>3.688218472245646</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.422879960939424</v>
+        <v>-2.510209000079977</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.992197852309237</v>
+        <v>1.957266236653015</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.303682917071857</v>
+        <v>1.212367302275902</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.743916011241868</v>
+        <v>3.689126642364295</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.395928736612936</v>
+        <v>-2.483257775753489</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.012984495684573</v>
+        <v>1.978052880028351</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.318563263099576</v>
+        <v>1.227247648303621</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.762850372503241</v>
+        <v>3.708061003625668</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.417472964443723</v>
+        <v>-2.504802003584276</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.188469936697218</v>
+        <v>2.153538321040997</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.318563263099576</v>
+        <v>1.227247648303621</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.946953504648201</v>
+        <v>3.892164135770628</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.439881082248595</v>
+        <v>-2.527210121389148</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.171623384478262</v>
+        <v>2.136691768822041</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.318563263099576</v>
+        <v>1.227247648303621</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.939070199551194</v>
+        <v>3.884280830673621</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.468105317826195</v>
+        <v>-2.555434356966749</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.162387689796859</v>
+        <v>2.127456074140638</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.336540015550885</v>
+        <v>1.24522440075493</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.951910250571617</v>
+        <v>3.897120881694044</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.477546243714725</v>
+        <v>-2.564875282855279</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.214865037163295</v>
+        <v>2.179933421507073</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.458967133094276</v>
+        <v>1.367651518298322</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.081620238819498</v>
+        <v>4.026830869941926</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.566422874883199</v>
+        <v>-2.653751914023752</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.182205479241206</v>
+        <v>2.147273863584985</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.370090501925803</v>
+        <v>1.278774887129848</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.031185354663715</v>
+        <v>3.976395985786143</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.642752852484105</v>
+        <v>-2.730081891624658</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.149785301094619</v>
+        <v>2.114853685438398</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.370090501925803</v>
+        <v>1.278774887129848</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.02929716755749</v>
+        <v>3.974507798679918</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.736416797161646</v>
+        <v>-2.8237458363022</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.107139952826465</v>
+        <v>2.072208337170244</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.276426557248261</v>
+        <v>1.185110942452306</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.967919030353828</v>
+        <v>3.913129661476255</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.897985222688901</v>
+        <v>-2.985314261829455</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.040946592825715</v>
+        <v>2.006014977169493</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.149643633450382</v>
+        <v>1.058328018654427</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.890283286285253</v>
+        <v>3.83549391740768</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.006285884559021</v>
+        <v>-3.093614923699574</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.010699734943586</v>
+        <v>1.975768119287364</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.149643633450382</v>
+        <v>1.058328018654427</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.903356693151171</v>
+        <v>3.848567324273598</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.024089856279765</v>
+        <v>-3.111418895420318</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.995583343038228</v>
+        <v>1.960651727382007</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.079109010545181</v>
+        <v>0.9877933957492258</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.85304111619099</v>
+        <v>3.798251747313418</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.051990643389238</v>
+        <v>-3.139319682529791</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.982947069321441</v>
+        <v>1.948015453665219</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.044512086402246</v>
+        <v>0.953196471606291</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.830807002832232</v>
+        <v>3.776017633954659</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.174516746092132</v>
+        <v>-3.261845785232685</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.930701072217482</v>
+        <v>1.895769456561261</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.921985983699352</v>
+        <v>0.8306703689033971</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.754055785187694</v>
+        <v>3.699266416310121</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.405031242277721</v>
+        <v>-3.492360281418274</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.90520123333375</v>
+        <v>1.870269617677529</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6914714875137633</v>
+        <v>0.6001558727178083</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.682453047066845</v>
+        <v>3.627663678189272</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.753776327502164</v>
+        <v>-3.841105366642718</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.90601491824582</v>
+        <v>1.871083302589598</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5827235335948655</v>
+        <v>0.4914079187989105</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.757515993717353</v>
+        <v>3.70272662483978</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237096</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.907762745278305</v>
+        <v>-3.995091784418858</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.913400620281003</v>
+        <v>1.878469004624782</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5827235335948655</v>
+        <v>0.4914079187989105</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.826496262862993</v>
+        <v>3.77170689398542</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423389</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.112362180141313</v>
+        <v>-4.199691219281867</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.817612048455921</v>
+        <v>1.782680432799699</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5827235335948655</v>
+        <v>0.4914079187989105</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.812547464983114</v>
+        <v>3.757758096105541</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.364837334149038</v>
+        <v>-4.452166373289591</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.728492475908245</v>
+        <v>1.693560860252024</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5827235335948655</v>
+        <v>0.4914079187989105</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.824417954038528</v>
+        <v>3.769628585160955</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.65773309062845</v>
+        <v>-4.745062129769003</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.612544707835424</v>
+        <v>1.577613092179202</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5827235335948655</v>
+        <v>0.4914079187989105</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.825628488557471</v>
+        <v>3.770839119679898</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.844397218763258</v>
+        <v>-4.931726257903811</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.542000798808822</v>
+        <v>1.507069183152601</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5559845627703056</v>
+        <v>0.4646689479743507</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.813706848290057</v>
+        <v>3.758917479412484</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.99041790567722</v>
+        <v>-5.077746944817774</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.478670376779427</v>
+        <v>1.443738761123205</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5469014709764486</v>
+        <v>0.4555858561804937</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.803334845949932</v>
+        <v>3.748545477072359</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.082131914786805</v>
+        <v>-5.169460953927359</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.604188829834637</v>
+        <v>1.569257214178415</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5469014709764486</v>
+        <v>0.4555858561804937</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.965538902648976</v>
+        <v>3.910749533771403</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.113783573846774</v>
+        <v>-5.201112612987329</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.586374804174463</v>
+        <v>1.551443188518241</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5417330137320084</v>
+        <v>0.4504173989360535</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.957284466266127</v>
+        <v>3.902495097388553</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868144</v>
+        <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.195718392115658</v>
+        <v>-5.283047431256212</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.563830294435401</v>
+        <v>1.528898678779179</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5317982681449283</v>
+        <v>0.4404826533489733</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.961553036482369</v>
+        <v>3.906763667604797</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.297694514364065</v>
+        <v>-5.385023553504619</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.531965483991941</v>
+        <v>1.497033868335719</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.4298221458965207</v>
+        <v>0.3385065311005657</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.909293001589227</v>
+        <v>3.854503632711654</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231806</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.187688230886843</v>
+        <v>-5.275017270027398</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.568120884627004</v>
+        <v>1.533189268970783</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4530267178137959</v>
+        <v>0.3617111030178409</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.915368631983768</v>
+        <v>3.860579263106195</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.044628655145917</v>
+        <v>-5.131957694286472</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.629594725645349</v>
+        <v>1.594663109989128</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4610401444037752</v>
+        <v>0.3697245296078202</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.92442669865973</v>
+        <v>3.869637329782157</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.74318192967408</v>
+        <v>-4.830510968814634</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.75743429871662</v>
+        <v>1.722502683060399</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7624868698756124</v>
+        <v>0.6711712550796575</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.112555616825368</v>
+        <v>4.057766247947795</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.767772173909264</v>
+        <v>-4.855101213049818</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.748569378775257</v>
+        <v>1.713637763119036</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7624868698756124</v>
+        <v>0.6711712550796575</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.113526794578078</v>
+        <v>4.058737425700506</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.716733797902743</v>
+        <v>-4.804062837043298</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.769827633557621</v>
+        <v>1.734896017901399</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7624868698756124</v>
+        <v>0.6711712550796575</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.114369698957834</v>
+        <v>4.059580330080261</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.675594503036113</v>
+        <v>-4.762923542176667</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.805321450378419</v>
+        <v>1.770389834722197</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8036261647422432</v>
+        <v>0.7123105499462883</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.158091374751958</v>
+        <v>4.103302005874385</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.578959591017473</v>
+        <v>-4.666288630158027</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.660159411309809</v>
+        <v>1.625227795653588</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.9002610767608832</v>
+        <v>0.8089454619649282</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.032256318087077</v>
+        <v>3.977466949209504</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.709540325548315</v>
+        <v>-4.796869364688869</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.611429161571436</v>
+        <v>1.576497545915215</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7696803422300407</v>
+        <v>0.6783647274340857</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.957409921442535</v>
+        <v>3.902620552564962</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.545043991357353</v>
+        <v>-4.632373030497908</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.661654514323904</v>
+        <v>1.626722898667682</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9341766764210025</v>
+        <v>0.8428610616250476</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.040534541033195</v>
+        <v>3.985745172155622</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.467945389815481</v>
+        <v>-4.555274428956035</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.691681665377083</v>
+        <v>1.656750049720861</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9341766764210025</v>
+        <v>0.8428610616250476</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.039722251469625</v>
+        <v>3.984932882592052</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.47833058470537</v>
+        <v>-4.565659623845924</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.697396366546199</v>
+        <v>1.662464750889977</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9237914815311132</v>
+        <v>0.8324758667351583</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.043359913660764</v>
+        <v>3.98857054478319</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.496918743427595</v>
+        <v>-4.584247782568149</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.760798108833734</v>
+        <v>1.725866493177513</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9052033228088878</v>
+        <v>0.813887708012933</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.103044024203854</v>
+        <v>4.04825465532628</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496556</v>
+        <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.497217290123631</v>
+        <v>-4.584546329264185</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.757547700973618</v>
+        <v>1.722616085317397</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9049047761128519</v>
+        <v>0.8135891613168971</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.099733907004531</v>
+        <v>4.044944538126957</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108856</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.396394156433203</v>
+        <v>-4.483723195573758</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.802407849389181</v>
+        <v>1.767476233732959</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9173689915972058</v>
+        <v>0.8260533768012509</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.111743331234534</v>
+        <v>4.056953962356961</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.205612795680796</v>
+        <v>-4.292941834821351</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.878849647168687</v>
+        <v>1.843918031512465</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.108150352349613</v>
+        <v>1.016834737553658</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.226341401164522</v>
+        <v>4.171552032286949</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.098649437831375</v>
+        <v>-4.185978476971929</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.901471836046052</v>
+        <v>1.86654022038983</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.166614960309415</v>
+        <v>1.07529934551346</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.241257011677999</v>
+        <v>4.186467642800427</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.043318849929612</v>
+        <v>-4.130647889070167</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.958571007818816</v>
+        <v>1.923639392162594</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.221945548211177</v>
+        <v>1.130629933415222</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.309422301031115</v>
+        <v>4.254632932153542</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.031264723016649</v>
+        <v>-4.118593762157204</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.957079226485439</v>
+        <v>1.922147610829217</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.23399967512414</v>
+        <v>1.142684060328185</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.31034134508033</v>
+        <v>4.255551976202757</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.07241984258487</v>
+        <v>-4.159748881725425</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.942497808842286</v>
+        <v>1.907566193186064</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.192844555555919</v>
+        <v>1.101528940759964</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.287528903523533</v>
+        <v>4.232739534645961</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.00437127989334</v>
+        <v>-4.091700319033895</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.98256825979678</v>
+        <v>1.947636644140559</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.260893118247449</v>
+        <v>1.169577503451494</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.341209067016334</v>
+        <v>4.286419698138761</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013426</v>
+        <v>3.645256780013424</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.235971673062841</v>
+        <v>-4.323300712203396</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.910130772702574</v>
+        <v>1.875199157046353</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.260893118247449</v>
+        <v>1.169577503451494</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.361411737189928</v>
+        <v>4.306622368312356</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498971</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.28602321859206</v>
+        <v>-4.373352257732614</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.873716390557769</v>
+        <v>1.838784774901547</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.260893118247449</v>
+        <v>1.169577503451494</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.345017973256811</v>
+        <v>4.290228604379237</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.6700487028001</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.461130051168505</v>
+        <v>-4.548459090309059</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.763925571120658</v>
+        <v>1.728993955464436</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.260893118247449</v>
+        <v>1.169577503451494</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.305269886850277</v>
+        <v>4.250480517972704</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660853</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.265029897737982</v>
+        <v>-4.352358936878536</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.849388251489807</v>
+        <v>1.814456635833585</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.456993271677971</v>
+        <v>1.365677656882017</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.429952597905531</v>
+        <v>4.375163229027958</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73057047339509</v>
+        <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.112004505624697</v>
+        <v>-4.199333544765252</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.009769407908025</v>
+        <v>1.974837792251803</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.610018663791255</v>
+        <v>1.518703048995301</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.620938832746406</v>
+        <v>4.566149463868832</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791151</v>
+        <v>3.74127833279115</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.140311819497968</v>
+        <v>-4.227640858638522</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.185912707267009</v>
+        <v>2.150981091610788</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.610018663791255</v>
+        <v>1.518703048995301</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.808405057654698</v>
+        <v>4.753615688777125</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620437</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.30690504461149</v>
+        <v>-4.394234083752044</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.088678368575683</v>
+        <v>2.053746752919461</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.443425438677733</v>
+        <v>1.352109823881778</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.677852073940667</v>
+        <v>4.623062705063094</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.70818251928565</v>
+        <v>3.708182519285648</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.283869251249924</v>
+        <v>-4.371198290390478</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.101569088582028</v>
+        <v>2.066637472925806</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.443425438677733</v>
+        <v>1.352109823881778</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.681528476602385</v>
+        <v>4.626739107724812</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399472</v>
+        <v>3.74058140139947</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.254623270794228</v>
+        <v>-4.341952309934782</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.110885535887801</v>
+        <v>2.07595392023158</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.443425438677733</v>
+        <v>1.352109823881778</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.67914653172588</v>
+        <v>4.624357162848307</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256373</v>
+        <v>3.699404642256371</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.361548818672079</v>
+        <v>-4.448877857812633</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.065408555894296</v>
+        <v>2.030476940238074</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.336499890799882</v>
+        <v>1.245184276003927</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.612284442156804</v>
+        <v>4.557495073279232</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701003</v>
+        <v>3.689942600701001</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.506567377179327</v>
+        <v>-4.593896416319882</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.008829934634631</v>
+        <v>1.973898318978409</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.191481332292633</v>
+        <v>1.100165717496678</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.526702109195689</v>
+        <v>4.471912740318117</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687014</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.624909142964045</v>
+        <v>-4.712238182104599</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.061424467578497</v>
+        <v>2.026492851922275</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.202167370855523</v>
+        <v>1.110851756059569</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.633044971591176</v>
+        <v>4.578255602713604</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790804</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.676319565284753</v>
+        <v>-4.763648604425307</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.038645995776152</v>
+        <v>2.003714380119931</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.202167370855523</v>
+        <v>1.110851756059569</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.630830668717116</v>
+        <v>4.576041299839543</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437331</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.755739016492504</v>
+        <v>-4.843068055633059</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.006781343367341</v>
+        <v>1.971849727711119</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.202167370855523</v>
+        <v>1.110851756059569</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.630733796791405</v>
+        <v>4.575944427913832</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298398</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.851202014409722</v>
+        <v>-4.938531053550276</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.968590037758497</v>
+        <v>1.933658422102275</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.202167370855523</v>
+        <v>1.110851756059569</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.630727690349448</v>
+        <v>4.575938321471875</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.786826103559007</v>
+        <v>-4.874155142699562</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.992436798661394</v>
+        <v>1.957505183005172</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.266543281706239</v>
+        <v>1.175227666910284</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.667449633422487</v>
+        <v>4.612660264544915</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353535</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.842195265691201</v>
+        <v>-4.929524304831755</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.976022951556243</v>
+        <v>1.941091335900021</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.266543281706239</v>
+        <v>1.175227666910284</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.673183451170214</v>
+        <v>4.618394082292641</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113278</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.887633045522028</v>
+        <v>-4.974962084662582</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.957386202966844</v>
+        <v>1.922454587310622</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.223698291028079</v>
+        <v>1.132382676232124</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.647014820106251</v>
+        <v>4.592225451228678</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113687</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.79942621137445</v>
+        <v>-4.886755250515004</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.012543329476194</v>
+        <v>1.977611713819972</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.223698291028079</v>
+        <v>1.132382676232124</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.66688921295657</v>
+        <v>4.612099844078997</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016441</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.69339121616914</v>
+        <v>-4.780720255309695</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.038658028083046</v>
+        <v>2.003726412426824</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.223698291028079</v>
+        <v>1.132382676232124</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.650589913481298</v>
+        <v>4.595800544603724</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307672</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.510179553036045</v>
+        <v>-4.5975085921766</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.114373642800329</v>
+        <v>2.079442027144108</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.223698291028079</v>
+        <v>1.132382676232124</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.653020862945343</v>
+        <v>4.59823149406777</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.438458106022194</v>
+        <v>-4.525787145162749</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.108853407453759</v>
+        <v>2.073921791797538</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.29541973804193</v>
+        <v>1.204104123245975</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.661844917001543</v>
+        <v>4.60705554812397</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394114</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.416085080414488</v>
+        <v>-4.503414119555043</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.064718363618014</v>
+        <v>2.029786747961792</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.306675489154831</v>
+        <v>1.215359874358876</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.615514113590455</v>
+        <v>4.560724744712883</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.449101376325233</v>
+        <v>-4.536430415465787</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.236710050139071</v>
+        <v>2.201778434482849</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.23723811248808</v>
+        <v>1.145922497692125</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.75904989247576</v>
+        <v>4.704260523598187</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883677</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.437573740675624</v>
+        <v>-4.524902779816179</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.233242330227164</v>
+        <v>2.198310714570941</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.296238770689442</v>
+        <v>1.204923155893487</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.786371513224826</v>
+        <v>4.731582144347254</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236297</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.534915242017993</v>
+        <v>-4.622244281158547</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.197973842212004</v>
+        <v>2.163042226555783</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.251818588523954</v>
+        <v>1.160502973727999</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.763387516447322</v>
+        <v>4.708598147569749</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427683</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.62077127135796</v>
+        <v>-4.708100310498514</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.164882512668856</v>
+        <v>2.129950897012634</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.209442519297819</v>
+        <v>1.118126904501864</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.739212957104479</v>
+        <v>4.684423588226906</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610383</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.629608068774079</v>
+        <v>-4.716937107914633</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.14376699552291</v>
+        <v>2.108835379866688</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.202000346656468</v>
+        <v>1.110684731860513</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.717166855340171</v>
+        <v>4.662377486462598</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667454</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.720990631339538</v>
+        <v>-4.808319670480092</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.117378481541776</v>
+        <v>2.082446865885554</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.165435461937123</v>
+        <v>1.074119847141168</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.705392435553613</v>
+        <v>4.65060306667604</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.67397837488919</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.709283913352531</v>
+        <v>-4.796612952493086</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.224189426560846</v>
+        <v>2.189257810904624</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.17714217992413</v>
+        <v>1.085826565128175</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.814544724170084</v>
+        <v>4.759755355292511</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409566</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.609620409268869</v>
+        <v>-4.696949448409423</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.267087166925716</v>
+        <v>2.232155551269494</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.240329263127816</v>
+        <v>1.149013648331861</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.855489312823702</v>
+        <v>4.800699943946128</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452573</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.619936507435221</v>
+        <v>-4.707265546575775</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.475865560937233</v>
+        <v>2.440933945281011</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.240329263127816</v>
+        <v>1.149013648331861</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.06839414610176</v>
+        <v>5.013604777224186</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762286</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.619842539417848</v>
+        <v>-4.707171578558403</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.475081815056272</v>
+        <v>2.44015019940005</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.240699124475134</v>
+        <v>1.149383509679179</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.067794729822239</v>
+        <v>5.013005360944667</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988017</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.627061363617693</v>
+        <v>-4.714390402758247</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.466426271320688</v>
+        <v>2.431494655664466</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.240699124475134</v>
+        <v>1.149383509679179</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.062026715766594</v>
+        <v>5.007237346889021</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740923</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.626112940499654</v>
+        <v>-4.713441979640209</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.466805640567903</v>
+        <v>2.431874024911681</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.240699124475134</v>
+        <v>1.149383509679179</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.062026715766594</v>
+        <v>5.007237346889021</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663627</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.783181398755278</v>
+        <v>-4.870510437895833</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.416705865246746</v>
+        <v>2.381774249590523</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.240699124475134</v>
+        <v>1.149383509679179</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.074754323747685</v>
+        <v>5.019964954870113</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424771</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.777189151966467</v>
+        <v>-4.864518191107021</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.421048762386658</v>
+        <v>2.386117146730436</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.240699124475134</v>
+        <v>1.149383509679179</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.076700322172073</v>
+        <v>5.0219109532945</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149219</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.688631190835699</v>
+        <v>-4.775960229976254</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.450126082856734</v>
+        <v>2.415194467200512</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.240699124475134</v>
+        <v>1.149383509679179</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.070354458189842</v>
+        <v>5.015565089312269</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383092</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.670872113332625</v>
+        <v>-4.75820115247318</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.456538391296959</v>
+        <v>2.421606775640737</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.240699124475134</v>
+        <v>1.149383509679179</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.069663135628838</v>
+        <v>5.014873766751265</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720999</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.571241962283557</v>
+        <v>-4.658571001424112</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.509172637625173</v>
+        <v>2.474241021968951</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.340329275524202</v>
+        <v>1.249013660728247</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.142223412166866</v>
+        <v>5.087434043289292</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455273</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.620641470972568</v>
+        <v>-4.707970510113123</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.678567099648295</v>
+        <v>2.643635483992073</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.350588108955947</v>
+        <v>1.259272494159992</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.337532977724639</v>
+        <v>5.282743608847065</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963134</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.413956997330192</v>
+        <v>-4.501286036470747</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.748429562208107</v>
+        <v>2.713497946551886</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.557272582598322</v>
+        <v>1.465956967802367</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.448732335012926</v>
+        <v>5.393942966135353</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162541</v>
+        <v>3.74028438916254</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.448113892327719</v>
+        <v>-4.535442931468273</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.736768317863202</v>
+        <v>2.70183670220698</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.47368881305751</v>
+        <v>1.382373198261555</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.400583586942544</v>
+        <v>5.34579421806497</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,19 +49615,19 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.6000377477571</v>
+        <v>3.600037747757098</v>
       </c>
       <c r="C2090" t="n">
         <v>4.464614027191413</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.448113892327719</v>
+        <v>-4.535442931468273</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.736768317863202</v>
+        <v>2.70183670220698</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.47368881305751</v>
+        <v>1.382373198261555</v>
       </c>
       <c r="G2090" t="n">
         <v>4.457677824177781</v>

--- a/tame_output/ON/bt/strategyON_20240917.xlsx
+++ b/tame_output/ON/bt/strategyON_20240917.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100.1%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>134.8%</t>
+          <t>161.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-71.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.0%</t>
+          <t>421.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-615.1%</t>
+          <t>-605.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-106.0%</t>
+          <t>-102.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-55.2%</t>
+          <t>-56.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-327.1%</t>
+          <t>-326.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-85.8%</t>
+          <t>-83.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,17 +1456,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>26.9%</t>
         </is>
       </c>
     </row>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319539</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316244</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284876</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636281</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.81322282095762</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.74392550571442</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161971</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321628</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916199</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830324</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868142</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231803</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74127833279115</v>
+        <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285648</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.74058140139947</v>
+        <v>3.740581401399468</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256371</v>
+        <v>3.699404642256369</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701001</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.712238182104599</v>
+        <v>-4.62055242878886</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.026492851922275</v>
+        <v>2.06316715324857</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.110851756059569</v>
+        <v>1.135118257116184</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.578255602713604</v>
+        <v>4.592815503347573</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.714879051790801</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.763648604425307</v>
+        <v>-4.671962851109568</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.003714380119931</v>
+        <v>2.040388681446226</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.110851756059569</v>
+        <v>1.135118257116184</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.576041299839543</v>
+        <v>4.590601200473512</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.843068055633059</v>
+        <v>-4.75138230231732</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.971849727711119</v>
+        <v>2.008524029037415</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.110851756059569</v>
+        <v>1.135118257116184</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.575944427913832</v>
+        <v>4.590504328547802</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.938531053550276</v>
+        <v>-4.846845300234538</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.933658422102275</v>
+        <v>1.97033272342857</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.110851756059569</v>
+        <v>1.135118257116184</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.575938321471875</v>
+        <v>4.590498222105844</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.874155142699562</v>
+        <v>-4.782469389383823</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.957505183005172</v>
+        <v>1.994179484331467</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.175227666910284</v>
+        <v>1.199494167966899</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.612660264544915</v>
+        <v>4.627220165178884</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.929524304831755</v>
+        <v>-4.837838551516016</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.941091335900021</v>
+        <v>1.977765637226316</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.175227666910284</v>
+        <v>1.199494167966899</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.618394082292641</v>
+        <v>4.632953982926611</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.974962084662582</v>
+        <v>-4.883276331346844</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.922454587310622</v>
+        <v>1.959128888636918</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.132382676232124</v>
+        <v>1.156649177288739</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.592225451228678</v>
+        <v>4.606785351862647</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.886755250515004</v>
+        <v>-4.795069497199266</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.977611713819972</v>
+        <v>2.014286015146268</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.132382676232124</v>
+        <v>1.156649177288739</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.612099844078997</v>
+        <v>4.626659744712966</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.780720255309695</v>
+        <v>-4.689034501993956</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.003726412426824</v>
+        <v>2.04040071375312</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.132382676232124</v>
+        <v>1.156649177288739</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.595800544603724</v>
+        <v>4.610360445237694</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.5975085921766</v>
+        <v>-4.505822838860861</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.079442027144108</v>
+        <v>2.116116328470403</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.132382676232124</v>
+        <v>1.156649177288739</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.59823149406777</v>
+        <v>4.612791394701739</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.525787145162749</v>
+        <v>-4.43410139184701</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.073921791797538</v>
+        <v>2.110596093123833</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.204104123245975</v>
+        <v>1.22837062430259</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.60705554812397</v>
+        <v>4.62161544875794</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.72378970539411</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.503414119555043</v>
+        <v>-4.411728366239304</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.029786747961792</v>
+        <v>2.066461049288087</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.215359874358876</v>
+        <v>1.239626375415491</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.560724744712883</v>
+        <v>4.575284645346852</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456727</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.536430415465787</v>
+        <v>-4.444744662150049</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.201778434482849</v>
+        <v>2.238452735809145</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.145922497692125</v>
+        <v>1.17018899874874</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.704260523598187</v>
+        <v>4.718820424232156</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.524902779816179</v>
+        <v>-4.43321702650044</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.198310714570941</v>
+        <v>2.234985015897237</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.204923155893487</v>
+        <v>1.229189656950102</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.731582144347254</v>
+        <v>4.746142044981223</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236293</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.622244281158547</v>
+        <v>-4.530558527842809</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.163042226555783</v>
+        <v>2.199716527882078</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.160502973727999</v>
+        <v>1.184769474784614</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.708598147569749</v>
+        <v>4.723158048203718</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427679</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.708100310498514</v>
+        <v>-4.616414557182775</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.129950897012634</v>
+        <v>2.16662519833893</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.118126904501864</v>
+        <v>1.142393405558479</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.684423588226906</v>
+        <v>4.698983488860875</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.716937107914633</v>
+        <v>-4.625251354598895</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.108835379866688</v>
+        <v>2.145509681192983</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.110684731860513</v>
+        <v>1.134951232917128</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.662377486462598</v>
+        <v>4.676937387096567</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667451</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.808319670480092</v>
+        <v>-4.716633917164353</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.082446865885554</v>
+        <v>2.11912116721185</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.074119847141168</v>
+        <v>1.098386348197784</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.65060306667604</v>
+        <v>4.665162967310009</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889186</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.796612952493086</v>
+        <v>-4.704927199177347</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.189257810904624</v>
+        <v>2.225932112230919</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.085826565128175</v>
+        <v>1.11009306618479</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.759755355292511</v>
+        <v>4.774315255926481</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409562</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.696949448409423</v>
+        <v>-4.605263695093685</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.232155551269494</v>
+        <v>2.268829852595789</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.149013648331861</v>
+        <v>1.173280149388477</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.800699943946128</v>
+        <v>4.815259844580098</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.707265546575775</v>
+        <v>-4.615579793260037</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.440933945281011</v>
+        <v>2.477608246607307</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.149013648331861</v>
+        <v>1.173280149388477</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.013604777224186</v>
+        <v>5.028164677858156</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.707171578558403</v>
+        <v>-4.615485825242664</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.44015019940005</v>
+        <v>2.476824500726345</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.149383509679179</v>
+        <v>1.173650010735795</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.013005360944667</v>
+        <v>5.027565261578636</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.714390402758247</v>
+        <v>-4.622704649442508</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.431494655664466</v>
+        <v>2.468168956990762</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.149383509679179</v>
+        <v>1.173650010735795</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.007237346889021</v>
+        <v>5.02179724752299</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.713441979640209</v>
+        <v>-4.62175622632447</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.431874024911681</v>
+        <v>2.468548326237977</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.149383509679179</v>
+        <v>1.173650010735795</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.007237346889021</v>
+        <v>5.02179724752299</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.870510437895833</v>
+        <v>-4.778824684580094</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.381774249590523</v>
+        <v>2.418448550916819</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.149383509679179</v>
+        <v>1.173650010735795</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.019964954870113</v>
+        <v>5.034524855504082</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.864518191107021</v>
+        <v>-4.772832437791283</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.386117146730436</v>
+        <v>2.422791448056731</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.149383509679179</v>
+        <v>1.173650010735795</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.0219109532945</v>
+        <v>5.03647085392847</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.775960229976254</v>
+        <v>-4.684274476660515</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.415194467200512</v>
+        <v>2.451868768526808</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.149383509679179</v>
+        <v>1.173650010735795</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.015565089312269</v>
+        <v>5.030124989946239</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.75820115247318</v>
+        <v>-4.666515399157441</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.421606775640737</v>
+        <v>2.458281076967033</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.149383509679179</v>
+        <v>1.173650010735795</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.014873766751265</v>
+        <v>5.029433667385234</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.658571001424112</v>
+        <v>-4.566885248108373</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.474241021968951</v>
+        <v>2.510915323295246</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.249013660728247</v>
+        <v>1.273280161784862</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.087434043289292</v>
+        <v>5.101993943923262</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.707970510113123</v>
+        <v>-4.616284756797384</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.643635483992073</v>
+        <v>2.680309785318369</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.259272494159992</v>
+        <v>1.283538995216607</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.282743608847065</v>
+        <v>5.297303509481035</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.501286036470747</v>
+        <v>-4.409600283155008</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.713497946551886</v>
+        <v>2.750172247878181</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.465956967802367</v>
+        <v>1.490223468858983</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.393942966135353</v>
+        <v>5.408502866769322</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.74028438916254</v>
+        <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.535442931468273</v>
+        <v>-4.443757178152534</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.70183670220698</v>
+        <v>2.738511003533276</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.382373198261555</v>
+        <v>1.40663969931817</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.34579421806497</v>
+        <v>5.36035411869894</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.600037747757098</v>
+        <v>3.931224795638601</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.464614027191413</v>
+        <v>4.735684087539255</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.535442931468273</v>
+        <v>-4.443757178152534</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.70183670220698</v>
+        <v>2.738511003533276</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.382373198261555</v>
+        <v>1.40663969931817</v>
       </c>
       <c r="G2090" t="n">
-        <v>4.457677824177781</v>
+        <v>4.728747884525623</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240917.xlsx
+++ b/tame_output/ON/bt/strategyON_20240917.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>54.6%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-71.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.8%</t>
+          <t>422.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-605.9%</t>
+          <t>-593.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-102.4%</t>
+          <t>-75.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-56.0%</t>
+          <t>-58.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-326.2%</t>
+          <t>-328.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-83.3%</t>
+          <t>-77.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>126.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>115.7%</t>
         </is>
       </c>
     </row>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.2309956657824</v>
+        <v>-4.12489947105751</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.179964410407803</v>
+        <v>1.222402888297758</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4307728428842427</v>
+        <v>0.4911895248909565</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.131182806765056</v>
+        <v>3.167432815969085</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.098127976719122</v>
+        <v>-4.022799462431371</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.249005668834937</v>
+        <v>1.279137074550037</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4307728428842427</v>
+        <v>0.4911895248909565</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.14707698956688</v>
+        <v>3.183326998770908</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.977954893354624</v>
+        <v>-3.902626379066873</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.298220746621038</v>
+        <v>1.328352152336139</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5509459262487416</v>
+        <v>0.6113626082554554</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.220326684025881</v>
+        <v>3.256576693229909</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.842701532024646</v>
+        <v>-3.767373017736896</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.362410193714469</v>
+        <v>1.392541599429569</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6861992875787187</v>
+        <v>0.7466159695854325</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.311566803385307</v>
+        <v>3.347816812589335</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.902576359382339</v>
+        <v>-3.827247845094588</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.324497754172818</v>
+        <v>1.354629159887918</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6263244602210266</v>
+        <v>0.6867411422277404</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.261679398372118</v>
+        <v>3.297929407576146</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.782756128471501</v>
+        <v>-3.707427614183751</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.387715015771361</v>
+        <v>1.417846421486462</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6263244602210266</v>
+        <v>0.6867411422277404</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.276968567606326</v>
+        <v>3.313218576810355</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.785225834933307</v>
+        <v>-3.709897320645557</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.294371332509081</v>
+        <v>1.324502738224181</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6238547537592205</v>
+        <v>0.6842714357659343</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.183130943051684</v>
+        <v>3.219380952255712</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.853596021257317</v>
+        <v>-3.778267506969566</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.186285119464778</v>
+        <v>1.216416525179878</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6331304527954354</v>
+        <v>0.6935471348021492</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.107958223958715</v>
+        <v>3.144208233162743</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.965468300883468</v>
+        <v>-3.890139786595717</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.131972916246209</v>
+        <v>1.162104321961309</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6331304527954354</v>
+        <v>0.6935471348021492</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.098394932590605</v>
+        <v>3.134644941794634</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.9494936353972</v>
+        <v>-3.874165121109449</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.104937307364743</v>
+        <v>1.135068713079844</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6331304527954354</v>
+        <v>0.6935471348021492</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.064969457514633</v>
+        <v>3.101219466718661</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.774019375604731</v>
+        <v>-3.69869086131698</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.179694243273519</v>
+        <v>1.209825648988619</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6331304527954354</v>
+        <v>0.6935471348021492</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.069536689506421</v>
+        <v>3.105786698710449</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.766095001019817</v>
+        <v>-3.690766486732066</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.158606021868692</v>
+        <v>1.188737427583792</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6331304527954354</v>
+        <v>0.6935471348021492</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.045278718267628</v>
+        <v>3.081528727471656</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.759816798449968</v>
+        <v>-3.684488284162217</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.089655616298081</v>
+        <v>1.119787022013182</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6394086553652845</v>
+        <v>0.6998253373719983</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.977583953210987</v>
+        <v>3.013833962415015</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.699964179246245</v>
+        <v>-3.624635664958494</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.123769050411703</v>
+        <v>1.153900456126803</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6394086553652845</v>
+        <v>0.6998253373719983</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.987756339643119</v>
+        <v>3.024006348847148</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.613720716219867</v>
+        <v>-3.538392201932116</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.153212706196114</v>
+        <v>1.183344111911214</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6394086553652845</v>
+        <v>0.6998253373719983</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.98270261021698</v>
+        <v>3.018952619421008</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.659027535618847</v>
+        <v>-3.583699021331096</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.126865753881048</v>
+        <v>1.156997159596148</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5985984923560537</v>
+        <v>0.6590151743627675</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.949992287855967</v>
+        <v>2.986242297059995</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.688060640321149</v>
+        <v>-3.612732126033398</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.115804385033229</v>
+        <v>1.145935790748329</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5985984923560537</v>
+        <v>0.6590151743627675</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.950544160889069</v>
+        <v>2.986794170093097</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.595250158870289</v>
+        <v>-3.519921644582539</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.082201269504938</v>
+        <v>1.112332675220038</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.691408973806913</v>
+        <v>0.7518256558136268</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.93550314165095</v>
+        <v>2.971753150854978</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.639639628199717</v>
+        <v>-3.564311113911966</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.066318957697768</v>
+        <v>1.096450363412868</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6470195044774854</v>
+        <v>0.7074361864841991</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.910742935977894</v>
+        <v>2.946992945181922</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.61913593431422</v>
+        <v>-3.543807420026469</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.06959614376369</v>
+        <v>1.09972754947879</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6675231983629827</v>
+        <v>0.7279398803696965</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.918120860820915</v>
+        <v>2.954370870024944</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.659060028896792</v>
+        <v>-3.583731514609041</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.059117801761328</v>
+        <v>1.089249207476428</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6675231983629827</v>
+        <v>0.7279398803696965</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.923612156651583</v>
+        <v>2.959862165855611</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.686840426798145</v>
+        <v>-3.611511912510394</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.059502844369326</v>
+        <v>1.089634250084426</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6397428004616297</v>
+        <v>0.7001594824683435</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.91844111967931</v>
+        <v>2.954691128883338</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.805221099528283</v>
+        <v>-3.729892585240532</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8505062952779237</v>
+        <v>0.8806377009930242</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5725249483106535</v>
+        <v>0.6329416303173673</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.716466128389377</v>
+        <v>2.752716137593405</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.913835177971615</v>
+        <v>-3.838506663683864</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9272103246197969</v>
+        <v>0.9573417303348972</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5725249483106535</v>
+        <v>0.6329416303173673</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.836615789108583</v>
+        <v>2.872865798312611</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.878426139723472</v>
+        <v>-3.803097625435721</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9558869660213771</v>
+        <v>0.9860183717364774</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5725249483106535</v>
+        <v>0.6329416303173673</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.851128815210906</v>
+        <v>2.887378824414934</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.886887308378933</v>
+        <v>-3.811558794091182</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9499219399015613</v>
+        <v>0.9800533456166616</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5640637796551924</v>
+        <v>0.6244804616619062</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.843471555359998</v>
+        <v>2.879721564564026</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.709770978343767</v>
+        <v>-3.634442464056016</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.01749750076093</v>
+        <v>1.04762890647603</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5640637796551924</v>
+        <v>0.6244804616619062</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.8402005842053</v>
+        <v>2.876450593409329</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.754863223177312</v>
+        <v>-3.679534708889562</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.000143994589425</v>
+        <v>1.030275400304525</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5021677364858026</v>
+        <v>0.5625844184925164</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.803746350065579</v>
+        <v>2.839996359269608</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.575487801938545</v>
+        <v>-3.500159287650794</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.065681138391346</v>
+        <v>1.095812544106447</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6589444946565213</v>
+        <v>0.7193611766632351</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.891599380274425</v>
+        <v>2.927849389478454</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.620502015459151</v>
+        <v>-3.5451735011714</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.028482908314694</v>
+        <v>1.058614314029794</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6285955993419167</v>
+        <v>0.6890122813486305</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.854197498417252</v>
+        <v>2.890447507621281</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.887506525731586</v>
+        <v>-3.812178011443836</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9273726665446651</v>
+        <v>0.9575040722597654</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4342325612989681</v>
+        <v>0.4946492433056819</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.743271237930429</v>
+        <v>2.779521247134457</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.988704307168759</v>
+        <v>-3.913375792881008</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8860974758662974</v>
+        <v>0.9162288815813979</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3658237477536489</v>
+        <v>0.4262404297603627</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.701429871699739</v>
+        <v>2.737679880903767</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.982193340554447</v>
+        <v>-3.906864826266696</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8863018240663392</v>
+        <v>0.9164332297814397</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3658237477536489</v>
+        <v>0.4262404297603627</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.699029833254055</v>
+        <v>2.735279842458084</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.963155212847149</v>
+        <v>-3.887826698559398</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8904417943575031</v>
+        <v>0.9205732000726035</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3076401364224544</v>
+        <v>0.3680568184291682</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.660644385663584</v>
+        <v>2.696894394867612</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.01567101512197</v>
+        <v>-3.940342500834218</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9887298750817652</v>
+        <v>1.018861280796866</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3076401364224544</v>
+        <v>0.3680568184291682</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.779938787297774</v>
+        <v>2.816188796501802</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.019079326556549</v>
+        <v>-3.943750812268798</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.988199879494067</v>
+        <v>1.018331285209167</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3401567054318317</v>
+        <v>0.4005733874385456</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.800282057689534</v>
+        <v>2.836532066893562</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.999723190662702</v>
+        <v>-3.924394676374951</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.001950864248532</v>
+        <v>1.032082269963632</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3401567054318317</v>
+        <v>0.4005733874385456</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.80629058808646</v>
+        <v>2.842540597290488</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.8519802204277</v>
+        <v>-3.776651706139949</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.958998273619732</v>
+        <v>0.9891296793348325</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5079640626667149</v>
+        <v>0.5683807446734288</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.804925223704589</v>
+        <v>2.841175232908618</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.935801441702398</v>
+        <v>-3.860472927414647</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9282634066413338</v>
+        <v>0.9583948123564343</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5079640626667149</v>
+        <v>0.5683807446734288</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.80771884523607</v>
+        <v>2.843968854440099</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.929648735649614</v>
+        <v>-3.854320221361863</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9313868374541059</v>
+        <v>0.9615182431692064</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5141167687194992</v>
+        <v>0.5745334507262131</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.812072817259399</v>
+        <v>2.848322826463427</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.946458033800115</v>
+        <v>-3.871129519512364</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9237435949340156</v>
+        <v>0.9538750006491161</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4973074705689975</v>
+        <v>0.5577241525757115</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.801067715109208</v>
+        <v>2.837317724313237</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.884160035023994</v>
+        <v>-3.808831520736242</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.014998348241285</v>
+        <v>1.045129753956386</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5426017348434395</v>
+        <v>0.6030184168501536</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.894579827470694</v>
+        <v>2.930829836674723</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.682369837358836</v>
+        <v>-3.607041323071084</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8980064290214753</v>
+        <v>0.9281378347365759</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7406199270125939</v>
+        <v>0.801036609019308</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.815682744486314</v>
+        <v>2.851932753690343</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.73325655004503</v>
+        <v>-3.657928035757279</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9479419762691728</v>
+        <v>0.9780733819842733</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6897332143263994</v>
+        <v>0.7501498963331135</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.855440949196773</v>
+        <v>2.891690958400801</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319539</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.646645807395223</v>
+        <v>-3.571317293107472</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9972140094451394</v>
+        <v>1.02734541516024</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7683589455315577</v>
+        <v>0.8287756275382717</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.917244124035911</v>
+        <v>2.95349413323994</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.706855105400507</v>
+        <v>-3.631526591112756</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9716662710676971</v>
+        <v>1.001797676782798</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7081496475262732</v>
+        <v>0.7685663295329872</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.879654526057412</v>
+        <v>2.915904535261441</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.657668456716156</v>
+        <v>-3.582339942428405</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9898325485813664</v>
+        <v>1.019963954296467</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7081496475262732</v>
+        <v>0.7685663295329872</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.878146144097341</v>
+        <v>2.914396153301369</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316244</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.613295325077587</v>
+        <v>-3.537966810789836</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.00744466867223</v>
+        <v>1.037576074387331</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7525227791648418</v>
+        <v>0.8129394611715558</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.904632890515918</v>
+        <v>2.940882899719947</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.635775675936472</v>
+        <v>-3.560447161648721</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9928463224672666</v>
+        <v>1.022977728182367</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7525227791648418</v>
+        <v>0.8129394611715558</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.899026684654509</v>
+        <v>2.935276693858537</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.588119945375417</v>
+        <v>-3.512791431087665</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.018290371719493</v>
+        <v>1.048421777434594</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8001785097258974</v>
+        <v>0.8605951917326115</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.934001880018947</v>
+        <v>2.970251889222975</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569612</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.487601786876662</v>
+        <v>-3.41227327258891</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.06339000849372</v>
+        <v>1.093521414208821</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.900696668224652</v>
+        <v>0.961113350231366</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.999205148492925</v>
+        <v>3.035455157696953</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.47169645744431</v>
+        <v>-3.396367943156558</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.056506812742533</v>
+        <v>1.086638218457634</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8215840075154131</v>
+        <v>0.8820006895221271</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.938492224543253</v>
+        <v>2.974742233747282</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.426858055835912</v>
+        <v>-3.35152954154816</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.078539875996521</v>
+        <v>1.108671281711622</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8261274404602825</v>
+        <v>0.8865441224669965</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.945315986920804</v>
+        <v>2.981565996124832</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.44635651207792</v>
+        <v>-3.371027997790168</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.074901433130796</v>
+        <v>1.105032838845897</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7780427991803782</v>
+        <v>0.8384594811870922</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.920626141783939</v>
+        <v>2.956876150987967</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.402153674992019</v>
+        <v>-3.326825160704268</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.098462170492993</v>
+        <v>1.128593576208094</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8222456362662787</v>
+        <v>0.8826623182729927</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.953027446563316</v>
+        <v>2.989277455767345</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.409713340829066</v>
+        <v>-3.334384826541315</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.093848304627422</v>
+        <v>1.123979710342523</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.877049040276098</v>
+        <v>0.937465722282812</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.984319489438455</v>
+        <v>3.020569498642484</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284876</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.251421923289794</v>
+        <v>-3.176093409002042</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.208412636826171</v>
+        <v>1.238544042541271</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.877049040276098</v>
+        <v>0.937465722282812</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.035567254621495</v>
+        <v>3.071817263825523</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.043779919655318</v>
+        <v>-2.968451405367566</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.289910142874214</v>
+        <v>1.320041548589315</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.084691043910574</v>
+        <v>1.145107725917288</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.158593161396434</v>
+        <v>3.194843170600462</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.99274782693279</v>
+        <v>-2.917419312645038</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.305271208201495</v>
+        <v>1.335402613916596</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.135723136633102</v>
+        <v>1.196139818639816</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.184160645268221</v>
+        <v>3.220410654472249</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.927523645805584</v>
+        <v>-2.852195131517832</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.348548284745082</v>
+        <v>1.378679690460183</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.200947317760308</v>
+        <v>1.261363999767022</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.240482558037249</v>
+        <v>3.276732567241277</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.89009662573445</v>
+        <v>-2.814768111446698</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.359480065072816</v>
+        <v>1.389611470787917</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.20619885578949</v>
+        <v>1.266615537796203</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.239594453154039</v>
+        <v>3.275844462358067</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.888738640760905</v>
+        <v>-2.813410126473153</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.361280051393475</v>
+        <v>1.391411457108576</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.280536981327308</v>
+        <v>1.340953663334022</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.28545412080797</v>
+        <v>3.321704130011998</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636281</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.860325377661021</v>
+        <v>-2.784996863373269</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.533203127654639</v>
+        <v>1.56333453336974</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.221561418580879</v>
+        <v>1.281978100587593</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.410626554181324</v>
+        <v>3.446876563385352</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095762</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.785543116636009</v>
+        <v>-2.710214602348257</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.683228941282461</v>
+        <v>1.713360346997562</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.296343679605892</v>
+        <v>1.356760361612606</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.575608820014148</v>
+        <v>3.611858829218177</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.759459032372201</v>
+        <v>-2.684130518084449</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.685370551001844</v>
+        <v>1.715501956716944</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.296343679605892</v>
+        <v>1.356760361612606</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.567316796028007</v>
+        <v>3.603566805232036</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.67158111926308</v>
+        <v>-2.596252604975328</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.718714911829271</v>
+        <v>1.748846317544372</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.412269322029243</v>
+        <v>1.472686004035957</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.635065377065797</v>
+        <v>3.671315386269826</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.662688657869797</v>
+        <v>-2.587360143582045</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.739826302113376</v>
+        <v>1.769957707828477</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.412269322029243</v>
+        <v>1.472686004035957</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.652619782792589</v>
+        <v>3.688869791996617</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.831164774839675</v>
+        <v>-2.755836260551923</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.664290902730009</v>
+        <v>1.694422308445109</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.384321486312662</v>
+        <v>1.444738168319376</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.627706128767224</v>
+        <v>3.663956137971252</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.384908582210235</v>
+        <v>-2.309580067922483</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.824063076969646</v>
+        <v>1.854194482684747</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.28960281664303</v>
+        <v>1.350019498649743</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.552144624153306</v>
+        <v>3.588394633357335</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632632</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.362187478527082</v>
+        <v>-2.286858964239331</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.823815540939812</v>
+        <v>1.853946946654913</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.28960281664303</v>
+        <v>1.350019498649743</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.542808646650211</v>
+        <v>3.579058655854239</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.491389291821125</v>
+        <v>-2.416060777533373</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.931040941473364</v>
+        <v>1.961172347188465</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.160401003348987</v>
+        <v>1.220817685355701</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.624193684524954</v>
+        <v>3.660443693728983</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.517263690295151</v>
+        <v>-2.441935176007399</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.957769004577401</v>
+        <v>1.987900410292501</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.205312612060728</v>
+        <v>1.265729294067442</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.688218472245646</v>
+        <v>3.724468481449674</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799959</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.510209000079977</v>
+        <v>-2.434880485792225</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.957266236653015</v>
+        <v>1.987397642368116</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.212367302275902</v>
+        <v>1.272783984282616</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.689126642364295</v>
+        <v>3.725376651568324</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.483257775753489</v>
+        <v>-2.407929261465737</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.978052880028351</v>
+        <v>2.008184285743452</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.227247648303621</v>
+        <v>1.287664330310335</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.708061003625668</v>
+        <v>3.744311012829697</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.504802003584276</v>
+        <v>-2.429473489296524</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.153538321040997</v>
+        <v>2.183669726756097</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.227247648303621</v>
+        <v>1.287664330310335</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.892164135770628</v>
+        <v>3.928414144974656</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571442</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.527210121389148</v>
+        <v>-2.451881607101396</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.136691768822041</v>
+        <v>2.166823174537142</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.227247648303621</v>
+        <v>1.287664330310335</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.884280830673621</v>
+        <v>3.920530839877649</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.555434356966749</v>
+        <v>-2.480105842678997</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.127456074140638</v>
+        <v>2.157587479855739</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.24522440075493</v>
+        <v>1.305641082761644</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.897120881694044</v>
+        <v>3.933370890898072</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161971</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.564875282855279</v>
+        <v>-2.489546768567527</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.179933421507073</v>
+        <v>2.210064827222174</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.367651518298322</v>
+        <v>1.428068200305035</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.026830869941926</v>
+        <v>4.063080879145955</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321628</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.653751914023752</v>
+        <v>-2.578423399736001</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.147273863584985</v>
+        <v>2.177405269300086</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.278774887129848</v>
+        <v>1.339191569136561</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.976395985786143</v>
+        <v>4.012645994990171</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.730081891624658</v>
+        <v>-2.654753377336907</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.114853685438398</v>
+        <v>2.144985091153498</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.278774887129848</v>
+        <v>1.339191569136561</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.974507798679918</v>
+        <v>4.010757807883946</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.8237458363022</v>
+        <v>-2.748417322014448</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.072208337170244</v>
+        <v>2.102339742885344</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.185110942452306</v>
+        <v>1.24552762445902</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.913129661476255</v>
+        <v>3.949379670680283</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.985314261829455</v>
+        <v>-2.909985747541703</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.006014977169493</v>
+        <v>2.036146382884594</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.058328018654427</v>
+        <v>1.118744700661141</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.83549391740768</v>
+        <v>3.871743926611708</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.093614923699574</v>
+        <v>-3.018286409411822</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.975768119287364</v>
+        <v>2.005899525002465</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.058328018654427</v>
+        <v>1.118744700661141</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.848567324273598</v>
+        <v>3.884817333477627</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.111418895420318</v>
+        <v>-3.036090381132567</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.960651727382007</v>
+        <v>1.990783133097107</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9877933957492258</v>
+        <v>1.04821007775594</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.798251747313418</v>
+        <v>3.834501756517446</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.139319682529791</v>
+        <v>-3.06399116824204</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.948015453665219</v>
+        <v>1.97814685938032</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.953196471606291</v>
+        <v>1.013613153613005</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.776017633954659</v>
+        <v>3.812267643158687</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.261845785232685</v>
+        <v>-3.186517270944933</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.895769456561261</v>
+        <v>1.925900862276361</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8306703689033971</v>
+        <v>0.891087050910111</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.699266416310121</v>
+        <v>3.73551642551415</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.492360281418274</v>
+        <v>-3.417031767130522</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.870269617677529</v>
+        <v>1.90040102339263</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6001558727178083</v>
+        <v>0.6605725547245223</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.627663678189272</v>
+        <v>3.6639136873933</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.841105366642718</v>
+        <v>-3.765776852354966</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.871083302589598</v>
+        <v>1.901214708304699</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4914079187989105</v>
+        <v>0.5518246008056245</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.70272662483978</v>
+        <v>3.738976634043809</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.995091784418858</v>
+        <v>-3.919763270131106</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.878469004624782</v>
+        <v>1.908600410339883</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4914079187989105</v>
+        <v>0.5518246008056245</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.77170689398542</v>
+        <v>3.807956903189448</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.199691219281867</v>
+        <v>-4.124362704994115</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.782680432799699</v>
+        <v>1.8128118385148</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4914079187989105</v>
+        <v>0.5518246008056245</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.757758096105541</v>
+        <v>3.794008105309569</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.452166373289591</v>
+        <v>-4.37683785900184</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.693560860252024</v>
+        <v>1.723692265967124</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4914079187989105</v>
+        <v>0.5518246008056245</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.769628585160955</v>
+        <v>3.805878594364983</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.745062129769003</v>
+        <v>-4.669733615481252</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.577613092179202</v>
+        <v>1.607744497894303</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4914079187989105</v>
+        <v>0.5518246008056245</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.770839119679898</v>
+        <v>3.807089128883927</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.931726257903811</v>
+        <v>-4.85639774361606</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.507069183152601</v>
+        <v>1.537200588867701</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4646689479743507</v>
+        <v>0.5250856299810646</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.758917479412484</v>
+        <v>3.795167488616512</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.077746944817774</v>
+        <v>-5.002418430530022</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.443738761123205</v>
+        <v>1.473870166838306</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4555858561804937</v>
+        <v>0.5160025381872075</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.748545477072359</v>
+        <v>3.784795486276388</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830324</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.169460953927359</v>
+        <v>-5.094132439639607</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.569257214178415</v>
+        <v>1.599388619893516</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4555858561804937</v>
+        <v>0.5160025381872075</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.910749533771403</v>
+        <v>3.946999542975432</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.201112612987329</v>
+        <v>-5.125784098699576</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.551443188518241</v>
+        <v>1.581574594233343</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4504173989360535</v>
+        <v>0.5108340809427674</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.902495097388553</v>
+        <v>3.938745106592582</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.283047431256212</v>
+        <v>-5.207718916968459</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.528898678779179</v>
+        <v>1.55903008449428</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4404826533489733</v>
+        <v>0.5008993353556872</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.906763667604797</v>
+        <v>3.943013676808825</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.385023553504619</v>
+        <v>-5.309695039216867</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.497033868335719</v>
+        <v>1.52716527405082</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3385065311005657</v>
+        <v>0.3989232131072796</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.854503632711654</v>
+        <v>3.890753641915683</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231803</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.275017270027398</v>
+        <v>-5.199688755739645</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.533189268970783</v>
+        <v>1.563320674685884</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3617111030178409</v>
+        <v>0.4221277850245548</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.860579263106195</v>
+        <v>3.896829272310223</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.131957694286472</v>
+        <v>-5.056629179998719</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.594663109989128</v>
+        <v>1.624794515704229</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3697245296078202</v>
+        <v>0.4301412116145341</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.869637329782157</v>
+        <v>3.905887338986185</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.830510968814634</v>
+        <v>-4.755182454526881</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.722502683060399</v>
+        <v>1.7526340887755</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6711712550796575</v>
+        <v>0.7315879370863714</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.057766247947795</v>
+        <v>4.094016257151823</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.855101213049818</v>
+        <v>-4.779772698762065</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.713637763119036</v>
+        <v>1.743769168834137</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6711712550796575</v>
+        <v>0.7315879370863714</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.058737425700506</v>
+        <v>4.094987434904534</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.804062837043298</v>
+        <v>-4.728734322755545</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.734896017901399</v>
+        <v>1.7650274236165</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6711712550796575</v>
+        <v>0.7315879370863714</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.059580330080261</v>
+        <v>4.09583033928429</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.762923542176667</v>
+        <v>-4.687595027888914</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.770389834722197</v>
+        <v>1.800521240437298</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7123105499462883</v>
+        <v>0.7727272319530022</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.103302005874385</v>
+        <v>4.139552015078413</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.666288630158027</v>
+        <v>-4.590960115870274</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.625227795653588</v>
+        <v>1.655359201368689</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8089454619649282</v>
+        <v>0.8693621439716421</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.977466949209504</v>
+        <v>4.013716958413532</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077636</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.796869364688869</v>
+        <v>-4.721540850401117</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.576497545915215</v>
+        <v>1.606628951630316</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6783647274340857</v>
+        <v>0.7387814094407996</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.902620552564962</v>
+        <v>3.93887056176899</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.632373030497908</v>
+        <v>-4.557044516210155</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.626722898667682</v>
+        <v>1.656854304382783</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8428610616250476</v>
+        <v>0.9032777436317615</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.985745172155622</v>
+        <v>4.02199518135965</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.555274428956035</v>
+        <v>-4.479945914668282</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.656750049720861</v>
+        <v>1.686881455435962</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8428610616250476</v>
+        <v>0.9032777436317615</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.984932882592052</v>
+        <v>4.02118289179608</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.565659623845924</v>
+        <v>-4.490331109558172</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.662464750889977</v>
+        <v>1.692596156605079</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8324758667351583</v>
+        <v>0.8928925487418722</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.98857054478319</v>
+        <v>4.024820553987219</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.584247782568149</v>
+        <v>-4.508919268280397</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.725866493177513</v>
+        <v>1.755997898892614</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.813887708012933</v>
+        <v>0.8743043900196468</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.04825465532628</v>
+        <v>4.084504664530309</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.584546329264185</v>
+        <v>-4.509217814976433</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.722616085317397</v>
+        <v>1.752747491032498</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8135891613168971</v>
+        <v>0.8740058433236109</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.044944538126957</v>
+        <v>4.081194547330986</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.483723195573758</v>
+        <v>-4.408394681286005</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.767476233732959</v>
+        <v>1.79760763944806</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8260533768012509</v>
+        <v>0.8864700588079647</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.056953962356961</v>
+        <v>4.093203971560989</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.292941834821351</v>
+        <v>-4.217613320533598</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.843918031512465</v>
+        <v>1.874049437227566</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.016834737553658</v>
+        <v>1.077251419560372</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.171552032286949</v>
+        <v>4.207802041490977</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.185978476971929</v>
+        <v>-4.110649962684176</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.86654022038983</v>
+        <v>1.896671626104932</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.07529934551346</v>
+        <v>1.135716027520174</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.186467642800427</v>
+        <v>4.222717652004454</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.130647889070167</v>
+        <v>-4.055319374782414</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.923639392162594</v>
+        <v>1.953770797877695</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.130629933415222</v>
+        <v>1.191046615421936</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.254632932153542</v>
+        <v>4.29088294135757</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.118593762157204</v>
+        <v>-4.043265247869451</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.922147610829217</v>
+        <v>1.952279016544318</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.142684060328185</v>
+        <v>1.203100742334898</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.255551976202757</v>
+        <v>4.291801985406786</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.159748881725425</v>
+        <v>-4.084420367437672</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.907566193186064</v>
+        <v>1.937697598901165</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.101528940759964</v>
+        <v>1.161945622766678</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.232739534645961</v>
+        <v>4.268989543849989</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.091700319033895</v>
+        <v>-4.016371804746142</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.947636644140559</v>
+        <v>1.97776804985566</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.169577503451494</v>
+        <v>1.229994185458207</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.286419698138761</v>
+        <v>4.322669707342789</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013424</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.323300712203396</v>
+        <v>-4.247972197915643</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.875199157046353</v>
+        <v>1.905330562761454</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.169577503451494</v>
+        <v>1.229994185458207</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.306622368312356</v>
+        <v>4.342872377516383</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.373352257732614</v>
+        <v>-4.298023743444862</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.838784774901547</v>
+        <v>1.868916180616648</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.169577503451494</v>
+        <v>1.229994185458207</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.290228604379237</v>
+        <v>4.326478613583266</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.548459090309059</v>
+        <v>-4.473130576021306</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.728993955464436</v>
+        <v>1.759125361179537</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.169577503451494</v>
+        <v>1.229994185458207</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.250480517972704</v>
+        <v>4.286730527176732</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.352358936878536</v>
+        <v>-4.277030422590784</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.814456635833585</v>
+        <v>1.844588041548686</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.365677656882017</v>
+        <v>1.42609433888873</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.375163229027958</v>
+        <v>4.411413238231986</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.199333544765252</v>
+        <v>-4.124005030477499</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.974837792251803</v>
+        <v>2.004969197966904</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.518703048995301</v>
+        <v>1.579119731002014</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.566149463868832</v>
+        <v>4.602399473072861</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791148</v>
+        <v>3.74127833279115</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.227640858638522</v>
+        <v>-4.152312344350769</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.150981091610788</v>
+        <v>2.181112497325889</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.518703048995301</v>
+        <v>1.579119731002014</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.753615688777125</v>
+        <v>4.789865697981154</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.394234083752044</v>
+        <v>-4.318905569464292</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.053746752919461</v>
+        <v>2.083878158634563</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.352109823881778</v>
+        <v>1.412526505888492</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.623062705063094</v>
+        <v>4.659312714267123</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.708182519285648</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.371198290390478</v>
+        <v>-4.295869776102726</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.066637472925806</v>
+        <v>2.096768878640907</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.352109823881778</v>
+        <v>1.412526505888492</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.626739107724812</v>
+        <v>4.66298911692884</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399468</v>
+        <v>3.74058140139947</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.341952309934782</v>
+        <v>-4.266623795647029</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.07595392023158</v>
+        <v>2.106085325946681</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.352109823881778</v>
+        <v>1.412526505888492</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.624357162848307</v>
+        <v>4.660607172052336</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256369</v>
+        <v>3.699404642256371</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.448877857812633</v>
+        <v>-4.37354934352488</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.030476940238074</v>
+        <v>2.060608345953175</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.245184276003927</v>
+        <v>1.305600958010641</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.557495073279232</v>
+        <v>4.59374508248326</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.689942600701001</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.593896416319882</v>
+        <v>-4.518567902032129</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.973898318978409</v>
+        <v>2.00402972469351</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.100165717496678</v>
+        <v>1.160582399503392</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.471912740318117</v>
+        <v>4.508162749522145</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.62055242878886</v>
+        <v>-4.526673210054996</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.06316715324857</v>
+        <v>2.100718840742116</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.135118257116184</v>
+        <v>1.198506347415544</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.592815503347573</v>
+        <v>4.630848357527189</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790801</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.671962851109568</v>
+        <v>-4.578083632375704</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.040388681446226</v>
+        <v>2.077940368939772</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.135118257116184</v>
+        <v>1.198506347415544</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.590601200473512</v>
+        <v>4.628634054653128</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.75138230231732</v>
+        <v>-4.657503083583456</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.008524029037415</v>
+        <v>2.04607571653096</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.135118257116184</v>
+        <v>1.198506347415544</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.590504328547802</v>
+        <v>4.628537182727418</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.846845300234538</v>
+        <v>-4.752966081500674</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.97033272342857</v>
+        <v>2.007884410922117</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.135118257116184</v>
+        <v>1.198506347415544</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.590498222105844</v>
+        <v>4.62853107628546</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.782469389383823</v>
+        <v>-4.688590170649959</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.994179484331467</v>
+        <v>2.031731171825013</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.199494167966899</v>
+        <v>1.262882258266259</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.627220165178884</v>
+        <v>4.6652530193585</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.837838551516016</v>
+        <v>-4.743959332782152</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.977765637226316</v>
+        <v>2.015317324719862</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.199494167966899</v>
+        <v>1.262882258266259</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.632953982926611</v>
+        <v>4.670986837106227</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.883276331346844</v>
+        <v>-4.78939711261298</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.959128888636918</v>
+        <v>1.996680576130464</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.156649177288739</v>
+        <v>1.2200372675881</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.606785351862647</v>
+        <v>4.644818206042263</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.795069497199266</v>
+        <v>-4.701190278465401</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.014286015146268</v>
+        <v>2.051837702639814</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.156649177288739</v>
+        <v>1.2200372675881</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.626659744712966</v>
+        <v>4.664692598892582</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.689034501993956</v>
+        <v>-4.595155283260092</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.04040071375312</v>
+        <v>2.077952401246665</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.156649177288739</v>
+        <v>1.2200372675881</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.610360445237694</v>
+        <v>4.64839329941731</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.505822838860861</v>
+        <v>-4.411943620126997</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.116116328470403</v>
+        <v>2.153668015963949</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.156649177288739</v>
+        <v>1.2200372675881</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.612791394701739</v>
+        <v>4.650824248881356</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.43410139184701</v>
+        <v>-4.340222173113146</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.110596093123833</v>
+        <v>2.148147780617379</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.22837062430259</v>
+        <v>1.29175871460195</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.62161544875794</v>
+        <v>4.659648302937556</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72378970539411</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.411728366239304</v>
+        <v>-4.31784914750544</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.066461049288087</v>
+        <v>2.104012736781633</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.239626375415491</v>
+        <v>1.303014465714852</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.575284645346852</v>
+        <v>4.613317499526469</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456727</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.444744662150049</v>
+        <v>-4.350865443416184</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.238452735809145</v>
+        <v>2.27600442330269</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.17018899874874</v>
+        <v>1.2335770890481</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.718820424232156</v>
+        <v>4.756853278411772</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.43321702650044</v>
+        <v>-4.339337807766576</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.234985015897237</v>
+        <v>2.272536703390783</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.229189656950102</v>
+        <v>1.292577747249463</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.746142044981223</v>
+        <v>4.784174899160838</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236293</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.530558527842809</v>
+        <v>-4.436679309108944</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.199716527882078</v>
+        <v>2.237268215375624</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.184769474784614</v>
+        <v>1.248157565083974</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.723158048203718</v>
+        <v>4.761190902383334</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427679</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.616414557182775</v>
+        <v>-4.522535338448911</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.16662519833893</v>
+        <v>2.204176885832475</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.142393405558479</v>
+        <v>1.205781495857839</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.698983488860875</v>
+        <v>4.737016343040492</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.625251354598895</v>
+        <v>-4.531372135865031</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.145509681192983</v>
+        <v>2.18306136868653</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.134951232917128</v>
+        <v>1.198339323216489</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.676937387096567</v>
+        <v>4.714970241276183</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667451</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.716633917164353</v>
+        <v>-4.622754698430489</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.11912116721185</v>
+        <v>2.156672854705396</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.098386348197784</v>
+        <v>1.161774438497144</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.665162967310009</v>
+        <v>4.703195821489626</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889186</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.704927199177347</v>
+        <v>-4.611047980443483</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.225932112230919</v>
+        <v>2.263483799724465</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.11009306618479</v>
+        <v>1.17348115648415</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.774315255926481</v>
+        <v>4.812348110106097</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409562</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.605263695093685</v>
+        <v>-4.511384476359821</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.268829852595789</v>
+        <v>2.306381540089335</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.173280149388477</v>
+        <v>1.236668239687837</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.815259844580098</v>
+        <v>4.853292698759714</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.615579793260037</v>
+        <v>-4.521700574526172</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.477608246607307</v>
+        <v>2.515159934100852</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.173280149388477</v>
+        <v>1.236668239687837</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.028164677858156</v>
+        <v>5.066197532037772</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.615485825242664</v>
+        <v>-4.5216066065088</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.476824500726345</v>
+        <v>2.514376188219891</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.173650010735795</v>
+        <v>1.237038101035155</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.027565261578636</v>
+        <v>5.065598115758252</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988014</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.622704649442508</v>
+        <v>-4.528825430708644</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.468168956990762</v>
+        <v>2.505720644484307</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.173650010735795</v>
+        <v>1.237038101035155</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.02179724752299</v>
+        <v>5.059830101702606</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.62175622632447</v>
+        <v>-4.527877007590606</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.468548326237977</v>
+        <v>2.506100013731523</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.173650010735795</v>
+        <v>1.237038101035155</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.02179724752299</v>
+        <v>5.059830101702606</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.778824684580094</v>
+        <v>-4.68494546584623</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.418448550916819</v>
+        <v>2.456000238410365</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.173650010735795</v>
+        <v>1.237038101035155</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.034524855504082</v>
+        <v>5.072557709683698</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.772832437791283</v>
+        <v>-4.678953219057418</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.422791448056731</v>
+        <v>2.460343135550277</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.173650010735795</v>
+        <v>1.237038101035155</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.03647085392847</v>
+        <v>5.074503708108086</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.684274476660515</v>
+        <v>-4.590395257926651</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.451868768526808</v>
+        <v>2.489420456020353</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.173650010735795</v>
+        <v>1.237038101035155</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.030124989946239</v>
+        <v>5.068157844125855</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.666515399157441</v>
+        <v>-4.572636180423577</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.458281076967033</v>
+        <v>2.495832764460578</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.173650010735795</v>
+        <v>1.237038101035155</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.029433667385234</v>
+        <v>5.06746652156485</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.566885248108373</v>
+        <v>-4.473006029374509</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.510915323295246</v>
+        <v>2.548467010788793</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.273280161784862</v>
+        <v>1.336668252084222</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.101993943923262</v>
+        <v>5.140026798102878</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455269</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.616284756797384</v>
+        <v>-4.52240553806352</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.680309785318369</v>
+        <v>2.717861472811914</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.283538995216607</v>
+        <v>1.346927085515967</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.297303509481035</v>
+        <v>5.335336363660651</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.74907805896313</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.409600283155008</v>
+        <v>-4.315721064421144</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.750172247878181</v>
+        <v>2.787723935371726</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.490223468858983</v>
+        <v>1.553611559158343</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.408502866769322</v>
+        <v>5.446535720948939</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162539</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.443757178152534</v>
+        <v>-4.34987795941867</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.738511003533276</v>
+        <v>2.776062691026821</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.40663969931817</v>
+        <v>1.47002778961753</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.36035411869894</v>
+        <v>5.398386972878556</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.931224795638601</v>
+        <v>3.826643328191134</v>
       </c>
       <c r="C2090" t="n">
         <v>4.735684087539255</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.443757178152534</v>
+        <v>-4.319678161249579</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.738511003533276</v>
+        <v>3.007456398725675</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.40663969931817</v>
+        <v>1.47002778961753</v>
       </c>
       <c r="G2090" t="n">
-        <v>4.728747884525623</v>
+        <v>5.617700761309774</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240917.xlsx
+++ b/tame_output/ON/bt/strategyON_20240917.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>60.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>161.9%</t>
+          <t>159.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.3%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.0%</t>
+          <t>422.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-593.5%</t>
+          <t>-598.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-80.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-58.2%</t>
+          <t>-59.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-328.9%</t>
+          <t>-330.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-63.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>126.2%</t>
+          <t>128.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>116.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>115.7%</t>
+          <t>121.4%</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.022799462431371</v>
+        <v>-3.992031781994232</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.279137074550037</v>
+        <v>1.291444146724893</v>
       </c>
       <c r="F1930" t="n">
         <v>0.4911895248909565</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.902626379066873</v>
+        <v>-3.871858698629733</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.328352152336139</v>
+        <v>1.340659224510995</v>
       </c>
       <c r="F1931" t="n">
         <v>0.6113626082554554</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.767373017736896</v>
+        <v>-3.736605337299756</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.392541599429569</v>
+        <v>1.404848671604425</v>
       </c>
       <c r="F1932" t="n">
         <v>0.7466159695854325</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.827247845094588</v>
+        <v>-3.796480164657448</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.354629159887918</v>
+        <v>1.366936232062774</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6867411422277404</v>
@@ -46033,10 +46033,10 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.707427614183751</v>
+        <v>-3.676659933746611</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.417846421486462</v>
+        <v>1.430153493661318</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6867411422277404</v>
@@ -46056,10 +46056,10 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.709897320645557</v>
+        <v>-3.679129640208417</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.324502738224181</v>
+        <v>1.336809810399037</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6842714357659343</v>
@@ -46079,10 +46079,10 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.778267506969566</v>
+        <v>-3.747499826532427</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.216416525179878</v>
+        <v>1.228723597354734</v>
       </c>
       <c r="F1936" t="n">
         <v>0.6935471348021492</v>
@@ -46102,10 +46102,10 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.890139786595717</v>
+        <v>-3.859372106158578</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.162104321961309</v>
+        <v>1.174411394136165</v>
       </c>
       <c r="F1937" t="n">
         <v>0.6935471348021492</v>
@@ -46125,10 +46125,10 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.874165121109449</v>
+        <v>-3.84339744067231</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.135068713079844</v>
+        <v>1.1473757852547</v>
       </c>
       <c r="F1938" t="n">
         <v>0.6935471348021492</v>
@@ -46148,10 +46148,10 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.69869086131698</v>
+        <v>-3.66792318087984</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.209825648988619</v>
+        <v>1.222132721163475</v>
       </c>
       <c r="F1939" t="n">
         <v>0.6935471348021492</v>
@@ -46171,10 +46171,10 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.690766486732066</v>
+        <v>-3.659998806294926</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.188737427583792</v>
+        <v>1.201044499758648</v>
       </c>
       <c r="F1940" t="n">
         <v>0.6935471348021492</v>
@@ -46194,10 +46194,10 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.684488284162217</v>
+        <v>-3.653720603725077</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.119787022013182</v>
+        <v>1.132094094188037</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6998253373719983</v>
@@ -46217,10 +46217,10 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.624635664958494</v>
+        <v>-3.593867984521354</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.153900456126803</v>
+        <v>1.166207528301659</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6998253373719983</v>
@@ -46240,10 +46240,10 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.538392201932116</v>
+        <v>-3.507624521494977</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.183344111911214</v>
+        <v>1.19565118408607</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6998253373719983</v>
@@ -46263,10 +46263,10 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.583699021331096</v>
+        <v>-3.552931340893957</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.156997159596148</v>
+        <v>1.169304231771004</v>
       </c>
       <c r="F1944" t="n">
         <v>0.6590151743627675</v>
@@ -46286,10 +46286,10 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.612732126033398</v>
+        <v>-3.581964445596258</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.145935790748329</v>
+        <v>1.158242862923185</v>
       </c>
       <c r="F1945" t="n">
         <v>0.6590151743627675</v>
@@ -46309,10 +46309,10 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.519921644582539</v>
+        <v>-3.489153964145399</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.112332675220038</v>
+        <v>1.124639747394894</v>
       </c>
       <c r="F1946" t="n">
         <v>0.7518256558136268</v>
@@ -46332,10 +46332,10 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.564311113911966</v>
+        <v>-3.533543433474827</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.096450363412868</v>
+        <v>1.108757435587724</v>
       </c>
       <c r="F1947" t="n">
         <v>0.7074361864841991</v>
@@ -46355,10 +46355,10 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.543807420026469</v>
+        <v>-3.513039739589329</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.09972754947879</v>
+        <v>1.112034621653646</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7279398803696965</v>
@@ -46378,10 +46378,10 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.583731514609041</v>
+        <v>-3.552963834171901</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.089249207476428</v>
+        <v>1.101556279651284</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7279398803696965</v>
@@ -46401,10 +46401,10 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.611511912510394</v>
+        <v>-3.580744232073255</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.089634250084426</v>
+        <v>1.101941322259282</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7001594824683435</v>
@@ -46424,10 +46424,10 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.729892585240532</v>
+        <v>-3.699124904803393</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8806377009930242</v>
+        <v>0.8929447731678799</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6329416303173673</v>
@@ -46447,10 +46447,10 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.838506663683864</v>
+        <v>-3.807738983246724</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9573417303348972</v>
+        <v>0.9696488025097532</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6329416303173673</v>
@@ -46470,10 +46470,10 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.803097625435721</v>
+        <v>-3.772329944998581</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9860183717364774</v>
+        <v>0.9983254439113332</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6329416303173673</v>
@@ -46493,10 +46493,10 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.811558794091182</v>
+        <v>-3.780791113654042</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9800533456166616</v>
+        <v>0.9923604177915175</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6244804616619062</v>
@@ -46516,10 +46516,10 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.634442464056016</v>
+        <v>-3.603674783618876</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.04762890647603</v>
+        <v>1.059935978650886</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6244804616619062</v>
@@ -46539,10 +46539,10 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.679534708889562</v>
+        <v>-3.648767028452422</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.030275400304525</v>
+        <v>1.042582472479381</v>
       </c>
       <c r="F1956" t="n">
         <v>0.5625844184925164</v>
@@ -46562,10 +46562,10 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.500159287650794</v>
+        <v>-3.469391607213654</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.095812544106447</v>
+        <v>1.108119616281303</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7193611766632351</v>
@@ -46585,10 +46585,10 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.5451735011714</v>
+        <v>-3.514405820734261</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.058614314029794</v>
+        <v>1.07092138620465</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6890122813486305</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.812178011443836</v>
+        <v>-3.781410331006696</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9575040722597654</v>
+        <v>0.9698111444346214</v>
       </c>
       <c r="F1959" t="n">
         <v>0.4946492433056819</v>
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.913375792881008</v>
+        <v>-3.847022139142605</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9162288815813979</v>
+        <v>0.9427703430767591</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4262404297603627</v>
+        <v>0.5151795272790612</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.737679880903767</v>
+        <v>2.791043339414986</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.906864826266696</v>
+        <v>-3.840511172528292</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9164332297814397</v>
+        <v>0.9429746912768009</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4262404297603627</v>
+        <v>0.5151795272790612</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.735279842458084</v>
+        <v>2.788643300969303</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.887826698559398</v>
+        <v>-3.821473044820995</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9205732000726035</v>
+        <v>0.9471146615679649</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3680568184291682</v>
+        <v>0.4569959159478667</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.696894394867612</v>
+        <v>2.750257853378831</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.940342500834218</v>
+        <v>-3.873988847095815</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.018861280796866</v>
+        <v>1.045402742292227</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3680568184291682</v>
+        <v>0.4569959159478667</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.816188796501802</v>
+        <v>2.869552255013021</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.943750812268798</v>
+        <v>-3.877397158530395</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.018331285209167</v>
+        <v>1.044872746704529</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4005733874385456</v>
+        <v>0.4895124849572441</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.836532066893562</v>
+        <v>2.889895525404782</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.924394676374951</v>
+        <v>-3.858041022636548</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.032082269963632</v>
+        <v>1.058623731458993</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4005733874385456</v>
+        <v>0.4895124849572441</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.842540597290488</v>
+        <v>2.895904055801708</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.776651706139949</v>
+        <v>-3.710298052401546</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9891296793348325</v>
+        <v>1.015671140830194</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5683807446734288</v>
+        <v>0.6573198421921272</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.841175232908618</v>
+        <v>2.894538691419837</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.860472927414647</v>
+        <v>-3.794119273676244</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9583948123564343</v>
+        <v>0.9849362738517957</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5683807446734288</v>
+        <v>0.6573198421921272</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.843968854440099</v>
+        <v>2.897332312951318</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.854320221361863</v>
+        <v>-3.787966567623459</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9615182431692064</v>
+        <v>0.9880597046645678</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5745334507262131</v>
+        <v>0.6634725482449115</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.848322826463427</v>
+        <v>2.901686284974647</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.871129519512364</v>
+        <v>-3.804775865773961</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9538750006491161</v>
+        <v>0.9804164621444773</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5577241525757115</v>
+        <v>0.6466632500944098</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.837317724313237</v>
+        <v>2.890681182824456</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.808831520736242</v>
+        <v>-3.742477866997839</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.045129753956386</v>
+        <v>1.071671215451747</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6030184168501536</v>
+        <v>0.6919575143688519</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.930829836674723</v>
+        <v>2.984193295185942</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.607041323071084</v>
+        <v>-3.540687669332681</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9281378347365759</v>
+        <v>0.9546792962319373</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.801036609019308</v>
+        <v>0.8899757065380063</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.851932753690343</v>
+        <v>2.905296212201562</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.657928035757279</v>
+        <v>-3.591574382018876</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9780733819842733</v>
+        <v>1.004614843479635</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7501498963331135</v>
+        <v>0.8390889938518118</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.891690958400801</v>
+        <v>2.94505441691202</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.571317293107472</v>
+        <v>-3.504963639369068</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.02734541516024</v>
+        <v>1.053886876655601</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8287756275382717</v>
+        <v>0.91771472505697</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.95349413323994</v>
+        <v>3.006857591751159</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.631526591112756</v>
+        <v>-3.478596084399864</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.001797676782798</v>
+        <v>1.062969879467955</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7685663295329872</v>
+        <v>0.944082280026175</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.915904535261441</v>
+        <v>3.021214105557354</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.582339942428405</v>
+        <v>-3.429409435715512</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.019963954296467</v>
+        <v>1.081136156981624</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7685663295329872</v>
+        <v>0.944082280026175</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.914396153301369</v>
+        <v>3.019705723597282</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.537966810789836</v>
+        <v>-3.385036304076944</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.037576074387331</v>
+        <v>1.098748277072487</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8129394611715558</v>
+        <v>0.9884554116647437</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.940882899719947</v>
+        <v>3.04619247001586</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.560447161648721</v>
+        <v>-3.407516654935828</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.022977728182367</v>
+        <v>1.084149930867524</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8129394611715558</v>
+        <v>0.9884554116647437</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.935276693858537</v>
+        <v>3.04058626415445</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.512791431087665</v>
+        <v>-3.359860924374773</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.048421777434594</v>
+        <v>1.109593980119751</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8605951917326115</v>
+        <v>1.036111142225799</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.970251889222975</v>
+        <v>3.075561459518888</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.41227327258891</v>
+        <v>-3.259342765876018</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.093521414208821</v>
+        <v>1.154693616893978</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.961113350231366</v>
+        <v>1.136629300724554</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.035455157696953</v>
+        <v>3.140764727992865</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.396367943156558</v>
+        <v>-3.243437436443665</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.086638218457634</v>
+        <v>1.147810421142791</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8820006895221271</v>
+        <v>1.057516640015315</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.974742233747282</v>
+        <v>3.080051804043194</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.35152954154816</v>
+        <v>-3.198599034835267</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.108671281711622</v>
+        <v>1.169843484396779</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8865441224669965</v>
+        <v>1.062060072960184</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.981565996124832</v>
+        <v>3.086875566420745</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.371027997790168</v>
+        <v>-3.218097491077275</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.105032838845897</v>
+        <v>1.166205041531053</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8384594811870922</v>
+        <v>1.01397543168028</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.956876150987967</v>
+        <v>3.06218572128388</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.326825160704268</v>
+        <v>-3.173894653991375</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.128593576208094</v>
+        <v>1.189765778893251</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8826623182729927</v>
+        <v>1.05817826876618</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.989277455767345</v>
+        <v>3.094587026063258</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.334384826541315</v>
+        <v>-3.181454319828422</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.123979710342523</v>
+        <v>1.18515191302768</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.937465722282812</v>
+        <v>1.112981672776</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.020569498642484</v>
+        <v>3.125879068938397</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.176093409002042</v>
+        <v>-3.02316290228915</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.238544042541271</v>
+        <v>1.299716245226428</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.937465722282812</v>
+        <v>1.112981672776</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.071817263825523</v>
+        <v>3.177126834121436</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.968451405367566</v>
+        <v>-2.815520898654674</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.320041548589315</v>
+        <v>1.381213751274472</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.145107725917288</v>
+        <v>1.320623676410476</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.194843170600462</v>
+        <v>3.300152740896375</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.917419312645038</v>
+        <v>-2.764488805932146</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.335402613916596</v>
+        <v>1.396574816601753</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.196139818639816</v>
+        <v>1.371655769133004</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.220410654472249</v>
+        <v>3.325720224768162</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.852195131517832</v>
+        <v>-2.69926462480494</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.378679690460183</v>
+        <v>1.43985189314534</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.261363999767022</v>
+        <v>1.43687995026021</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.276732567241277</v>
+        <v>3.38204213753719</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.814768111446698</v>
+        <v>-2.661837604733806</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.389611470787917</v>
+        <v>1.450783673473074</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.266615537796203</v>
+        <v>1.442131488289391</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.275844462358067</v>
+        <v>3.38115403265398</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.813410126473153</v>
+        <v>-2.66047961976026</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.391411457108576</v>
+        <v>1.452583659793733</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.340953663334022</v>
+        <v>1.51646961382721</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.321704130011998</v>
+        <v>3.427013700307911</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.784996863373269</v>
+        <v>-2.632066356660377</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.56333453336974</v>
+        <v>1.624506736054897</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.281978100587593</v>
+        <v>1.457494051080781</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.446876563385352</v>
+        <v>3.552186133681265</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.710214602348257</v>
+        <v>-2.557284095635364</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.713360346997562</v>
+        <v>1.774532549682719</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.356760361612606</v>
+        <v>1.532276312105794</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.611858829218177</v>
+        <v>3.717168399514089</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.684130518084449</v>
+        <v>-2.531200011371556</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.715501956716944</v>
+        <v>1.776674159402101</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.356760361612606</v>
+        <v>1.532276312105794</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.603566805232036</v>
+        <v>3.708876375527948</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.596252604975328</v>
+        <v>-2.443322098262436</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.748846317544372</v>
+        <v>1.810018520229529</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.472686004035957</v>
+        <v>1.648201954529145</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.671315386269826</v>
+        <v>3.776624956565739</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.587360143582045</v>
+        <v>-2.434429636869153</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.769957707828477</v>
+        <v>1.831129910513634</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.472686004035957</v>
+        <v>1.648201954529145</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.688869791996617</v>
+        <v>3.79417936229253</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.755836260551923</v>
+        <v>-2.602905753839031</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.694422308445109</v>
+        <v>1.755594511130266</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.444738168319376</v>
+        <v>1.620254118812564</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.663956137971252</v>
+        <v>3.769265708267165</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.309580067922483</v>
+        <v>-2.156649561209591</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.854194482684747</v>
+        <v>1.915366685369904</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.350019498649743</v>
+        <v>1.525535449142931</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.588394633357335</v>
+        <v>3.693704203653247</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.286858964239331</v>
+        <v>-2.133928457526438</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.853946946654913</v>
+        <v>1.91511914934007</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.350019498649743</v>
+        <v>1.525535449142931</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.579058655854239</v>
+        <v>3.684368226150152</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.416060777533373</v>
+        <v>-2.263130270820481</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.961172347188465</v>
+        <v>2.022344549873622</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.220817685355701</v>
+        <v>1.396333635848889</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.660443693728983</v>
+        <v>3.765753264024896</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.441935176007399</v>
+        <v>-2.289004669294506</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.987900410292501</v>
+        <v>2.049072612977658</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.265729294067442</v>
+        <v>1.44124524456063</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.724468481449674</v>
+        <v>3.829778051745587</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.434880485792225</v>
+        <v>-2.281949979079333</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.987397642368116</v>
+        <v>2.048569845053273</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.272783984282616</v>
+        <v>1.448299934775804</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.725376651568324</v>
+        <v>3.830686221864236</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.407929261465737</v>
+        <v>-2.254998754752845</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.008184285743452</v>
+        <v>2.06935648842861</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.287664330310335</v>
+        <v>1.463180280803523</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.744311012829697</v>
+        <v>3.849620583125609</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.429473489296524</v>
+        <v>-2.276542982583632</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.183669726756097</v>
+        <v>2.244841929441254</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.287664330310335</v>
+        <v>1.463180280803523</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.928414144974656</v>
+        <v>4.033723715270569</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.451881607101396</v>
+        <v>-2.298951100388504</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.166823174537142</v>
+        <v>2.227995377222299</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.287664330310335</v>
+        <v>1.463180280803523</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.920530839877649</v>
+        <v>4.025840410173562</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.480105842678997</v>
+        <v>-2.327175335966104</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.157587479855739</v>
+        <v>2.218759682540896</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.305641082761644</v>
+        <v>1.481157033254832</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.933370890898072</v>
+        <v>4.038680461193985</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.489546768567527</v>
+        <v>-2.336616261854634</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.210064827222174</v>
+        <v>2.271237029907331</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.428068200305035</v>
+        <v>1.603584150798223</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.063080879145955</v>
+        <v>4.168390449441867</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.578423399736001</v>
+        <v>-2.425492893023108</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.177405269300086</v>
+        <v>2.238577471985242</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.339191569136561</v>
+        <v>1.514707519629749</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.012645994990171</v>
+        <v>4.117955565286083</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.654753377336907</v>
+        <v>-2.501822870624014</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.144985091153498</v>
+        <v>2.206157293838655</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.339191569136561</v>
+        <v>1.514707519629749</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.010757807883946</v>
+        <v>4.116067378179858</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.748417322014448</v>
+        <v>-2.595486815301555</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.102339742885344</v>
+        <v>2.163511945570501</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.24552762445902</v>
+        <v>1.421043574952208</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.949379670680283</v>
+        <v>4.054689240976196</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.909985747541703</v>
+        <v>-2.75705524082881</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.036146382884594</v>
+        <v>2.097318585569751</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.118744700661141</v>
+        <v>1.294260651154329</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.871743926611708</v>
+        <v>3.977053496907621</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.018286409411822</v>
+        <v>-2.86535590269893</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.005899525002465</v>
+        <v>2.067071727687622</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.118744700661141</v>
+        <v>1.294260651154329</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.884817333477627</v>
+        <v>3.99012690377354</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.036090381132567</v>
+        <v>-2.883159874419674</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.990783133097107</v>
+        <v>2.051955335782265</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.04821007775594</v>
+        <v>1.223726028249128</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.834501756517446</v>
+        <v>3.939811326813359</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.06399116824204</v>
+        <v>-2.911060661529147</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.97814685938032</v>
+        <v>2.039319062065477</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.013613153613005</v>
+        <v>1.189129104106193</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.812267643158687</v>
+        <v>3.9175772134546</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.186517270944933</v>
+        <v>-3.033586764232041</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.925900862276361</v>
+        <v>1.987073064961518</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.891087050910111</v>
+        <v>1.066603001403299</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.73551642551415</v>
+        <v>3.840825995810063</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.417031767130522</v>
+        <v>-3.26410126041763</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.90040102339263</v>
+        <v>1.961573226077786</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.6605725547245223</v>
+        <v>0.8360885052177103</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.6639136873933</v>
+        <v>3.769223257689213</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.765776852354966</v>
+        <v>-3.612846345642073</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.901214708304699</v>
+        <v>1.962386910989856</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5518246008056245</v>
+        <v>0.7273405512988125</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.738976634043809</v>
+        <v>3.844286204339721</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.919763270131106</v>
+        <v>-3.766832763418214</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.908600410339883</v>
+        <v>1.969772613025039</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5518246008056245</v>
+        <v>0.7273405512988125</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.807956903189448</v>
+        <v>3.913266473485361</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.124362704994115</v>
+        <v>-3.971432198281223</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.8128118385148</v>
+        <v>1.873984041199957</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5518246008056245</v>
+        <v>0.7273405512988125</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.794008105309569</v>
+        <v>3.899317675605482</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.37683785900184</v>
+        <v>-4.223907352288947</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.723692265967124</v>
+        <v>1.784864468652281</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5518246008056245</v>
+        <v>0.7273405512988125</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.805878594364983</v>
+        <v>3.911188164660896</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.669733615481252</v>
+        <v>-4.516803108768359</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.607744497894303</v>
+        <v>1.66891670057946</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5518246008056245</v>
+        <v>0.7273405512988125</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.807089128883927</v>
+        <v>3.91239869917984</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.85639774361606</v>
+        <v>-4.703467236903167</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.537200588867701</v>
+        <v>1.598372791552858</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5250856299810646</v>
+        <v>0.7006015804742526</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.795167488616512</v>
+        <v>3.900477058912425</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.002418430530022</v>
+        <v>-4.849487923817129</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.473870166838306</v>
+        <v>1.535042369523463</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5160025381872075</v>
+        <v>0.6915184886803956</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.784795486276388</v>
+        <v>3.8901050565723</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.094132439639607</v>
+        <v>-4.941201932926715</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.599388619893516</v>
+        <v>1.660560822578673</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5160025381872075</v>
+        <v>0.6915184886803956</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.946999542975432</v>
+        <v>4.052309113271344</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.125784098699576</v>
+        <v>-4.972853591986684</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.581574594233343</v>
+        <v>1.642746796918499</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5108340809427674</v>
+        <v>0.6863500314359554</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.938745106592582</v>
+        <v>4.044054676888495</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.207718916968459</v>
+        <v>-5.054788410255568</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.55903008449428</v>
+        <v>1.620202287179437</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5008993353556872</v>
+        <v>0.6764152858488752</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.943013676808825</v>
+        <v>4.048323247104737</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.309695039216867</v>
+        <v>-5.156764532503975</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.52716527405082</v>
+        <v>1.588337476735977</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3989232131072796</v>
+        <v>0.5744391636004677</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.890753641915683</v>
+        <v>3.996063212211595</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.199688755739645</v>
+        <v>-5.046758249026754</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.563320674685884</v>
+        <v>1.624492877371041</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4221277850245548</v>
+        <v>0.5976437355177429</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.896829272310223</v>
+        <v>4.002138842606136</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.056629179998719</v>
+        <v>-4.903698673285827</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.624794515704229</v>
+        <v>1.685966718389385</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4301412116145341</v>
+        <v>0.6056571621077221</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.905887338986185</v>
+        <v>4.011196909282098</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.755182454526881</v>
+        <v>-4.60225194781399</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.7526340887755</v>
+        <v>1.813806291460656</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7315879370863714</v>
+        <v>0.9071038875795594</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.094016257151823</v>
+        <v>4.199325827447736</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.779772698762065</v>
+        <v>-4.626842192049174</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.743769168834137</v>
+        <v>1.804941371519293</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7315879370863714</v>
+        <v>0.9071038875795594</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.094987434904534</v>
+        <v>4.200297005200447</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.728734322755545</v>
+        <v>-4.575803816042654</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.7650274236165</v>
+        <v>1.826199626301657</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7315879370863714</v>
+        <v>0.9071038875795594</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.09583033928429</v>
+        <v>4.201139909580203</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.687595027888914</v>
+        <v>-4.534664521176023</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.800521240437298</v>
+        <v>1.861693443122455</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.7727272319530022</v>
+        <v>0.9482431824461902</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.139552015078413</v>
+        <v>4.244861585374326</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.590960115870274</v>
+        <v>-4.438029609157383</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.655359201368689</v>
+        <v>1.716531404053845</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.8693621439716421</v>
+        <v>1.04487809446483</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.013716958413532</v>
+        <v>4.119026528709445</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.721540850401117</v>
+        <v>-4.568610343688225</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.606628951630316</v>
+        <v>1.667801154315472</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7387814094407996</v>
+        <v>0.9142973599339876</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.93887056176899</v>
+        <v>4.044180132064904</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.557044516210155</v>
+        <v>-4.404114009497263</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.656854304382783</v>
+        <v>1.71802650706794</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9032777436317615</v>
+        <v>1.07879369412495</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.02199518135965</v>
+        <v>4.127304751655563</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.479945914668282</v>
+        <v>-4.327015407955391</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.686881455435962</v>
+        <v>1.748053658121119</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9032777436317615</v>
+        <v>1.07879369412495</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.02118289179608</v>
+        <v>4.126492462091993</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.490331109558172</v>
+        <v>-4.33740060284528</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.692596156605079</v>
+        <v>1.753768359290235</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8928925487418722</v>
+        <v>1.06840849923506</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.024820553987219</v>
+        <v>4.130130124283132</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.508919268280397</v>
+        <v>-4.355988761567505</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.755997898892614</v>
+        <v>1.81717010157777</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8743043900196468</v>
+        <v>1.049820340512835</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.084504664530309</v>
+        <v>4.189814234826222</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.509217814976433</v>
+        <v>-4.356287308263541</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.752747491032498</v>
+        <v>1.813919693717654</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8740058433236109</v>
+        <v>1.049521793816799</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.081194547330986</v>
+        <v>4.186504117626899</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.408394681286005</v>
+        <v>-4.255464174573113</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.79760763944806</v>
+        <v>1.858779842133217</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8864700588079647</v>
+        <v>1.061986009301153</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.093203971560989</v>
+        <v>4.198513541856903</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.217613320533598</v>
+        <v>-4.064682813820706</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.874049437227566</v>
+        <v>1.935221639912723</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.077251419560372</v>
+        <v>1.25276737005356</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.207802041490977</v>
+        <v>4.31311161178689</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.110649962684176</v>
+        <v>-3.957719455971285</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.896671626104932</v>
+        <v>1.957843828790089</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.135716027520174</v>
+        <v>1.311231978013362</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.222717652004454</v>
+        <v>4.328027222300367</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.055319374782414</v>
+        <v>-3.902388868069523</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.953770797877695</v>
+        <v>2.014943000562852</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.191046615421936</v>
+        <v>1.366562565915124</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.29088294135757</v>
+        <v>4.396192511653483</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.043265247869451</v>
+        <v>-3.89033474115656</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.952279016544318</v>
+        <v>2.013451219229474</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.203100742334898</v>
+        <v>1.378616692828087</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.291801985406786</v>
+        <v>4.397111555702699</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.084420367437672</v>
+        <v>-3.931489860724781</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.937697598901165</v>
+        <v>1.998869801586322</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.161945622766678</v>
+        <v>1.337461573259866</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.268989543849989</v>
+        <v>4.374299114145902</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.016371804746142</v>
+        <v>-3.863441298033251</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.97776804985566</v>
+        <v>2.038940252540816</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.229994185458207</v>
+        <v>1.405510135951396</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.322669707342789</v>
+        <v>4.427979277638702</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.247972197915643</v>
+        <v>-4.095041691202752</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.905330562761454</v>
+        <v>1.96650276544661</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.229994185458207</v>
+        <v>1.405510135951396</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.342872377516383</v>
+        <v>4.448181947812296</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.298023743444862</v>
+        <v>-4.145093236731972</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.868916180616648</v>
+        <v>1.930088383301804</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.229994185458207</v>
+        <v>1.405510135951396</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.326478613583266</v>
+        <v>4.431788183879179</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.473130576021306</v>
+        <v>-4.320200069308417</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.759125361179537</v>
+        <v>1.820297563864693</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.229994185458207</v>
+        <v>1.405510135951396</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.286730527176732</v>
+        <v>4.392040097472645</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.277030422590784</v>
+        <v>-4.124099915877894</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.844588041548686</v>
+        <v>1.905760244233842</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.42609433888873</v>
+        <v>1.601610289381918</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.411413238231986</v>
+        <v>4.516722808527899</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.124005030477499</v>
+        <v>-3.97107452376461</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.004969197966904</v>
+        <v>2.06614140065206</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.579119731002014</v>
+        <v>1.754635681495202</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.602399473072861</v>
+        <v>4.707709043368774</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.152312344350769</v>
+        <v>-3.99938183763788</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.181112497325889</v>
+        <v>2.242284700011044</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.579119731002014</v>
+        <v>1.754635681495202</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.789865697981154</v>
+        <v>4.895175268277066</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.318905569464292</v>
+        <v>-4.165975062751402</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.083878158634563</v>
+        <v>2.145050361319718</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.412526505888492</v>
+        <v>1.58804245638168</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.659312714267123</v>
+        <v>4.764622284563035</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.295869776102726</v>
+        <v>-4.142939269389836</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.096768878640907</v>
+        <v>2.157941081326062</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.412526505888492</v>
+        <v>1.58804245638168</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.66298911692884</v>
+        <v>4.768298687224753</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.266623795647029</v>
+        <v>-4.113693288934139</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.106085325946681</v>
+        <v>2.167257528631836</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.412526505888492</v>
+        <v>1.58804245638168</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.660607172052336</v>
+        <v>4.765916742348248</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.37354934352488</v>
+        <v>-4.22061883681199</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.060608345953175</v>
+        <v>2.121780548638331</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.305600958010641</v>
+        <v>1.481116908503829</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.59374508248326</v>
+        <v>4.699054652779172</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.518567902032129</v>
+        <v>-4.365637395319239</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.00402972469351</v>
+        <v>2.065201927378666</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.160582399503392</v>
+        <v>1.33609834999658</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.508162749522145</v>
+        <v>4.613472319818058</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.526673210054996</v>
+        <v>-4.483979161103957</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.100718840742116</v>
+        <v>2.117796460322532</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.198506347415544</v>
+        <v>1.34678438855947</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.630848357527189</v>
+        <v>4.719815182213545</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.578083632375704</v>
+        <v>-4.535389583424664</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.077940368939772</v>
+        <v>2.095017988520188</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.198506347415544</v>
+        <v>1.34678438855947</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.628634054653128</v>
+        <v>4.717600879339484</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.657503083583456</v>
+        <v>-4.614809034632416</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.04607571653096</v>
+        <v>2.063153336111376</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.198506347415544</v>
+        <v>1.34678438855947</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.628537182727418</v>
+        <v>4.717504007413774</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.752966081500674</v>
+        <v>-4.710272032549634</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.007884410922117</v>
+        <v>2.024962030502532</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.198506347415544</v>
+        <v>1.34678438855947</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.62853107628546</v>
+        <v>4.717497900971816</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.688590170649959</v>
+        <v>-4.645896121698919</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.031731171825013</v>
+        <v>2.048808791405428</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.262882258266259</v>
+        <v>1.411160299410186</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.6652530193585</v>
+        <v>4.754219844044856</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.743959332782152</v>
+        <v>-4.701265283831113</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.015317324719862</v>
+        <v>2.032394944300278</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.262882258266259</v>
+        <v>1.411160299410186</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.670986837106227</v>
+        <v>4.759953661792583</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.78939711261298</v>
+        <v>-4.74670306366194</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.996680576130464</v>
+        <v>2.01375819571088</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.2200372675881</v>
+        <v>1.368315308732026</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.644818206042263</v>
+        <v>4.733785030728619</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.701190278465401</v>
+        <v>-4.658496229514362</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.051837702639814</v>
+        <v>2.06891532222023</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.2200372675881</v>
+        <v>1.368315308732026</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.664692598892582</v>
+        <v>4.753659423578938</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.595155283260092</v>
+        <v>-4.552461234309052</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.077952401246665</v>
+        <v>2.095030020827081</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.2200372675881</v>
+        <v>1.368315308732026</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.64839329941731</v>
+        <v>4.737360124103666</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.411943620126997</v>
+        <v>-4.369249571175957</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.153668015963949</v>
+        <v>2.170745635544365</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.2200372675881</v>
+        <v>1.368315308732026</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.650824248881356</v>
+        <v>4.739791073567711</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.340222173113146</v>
+        <v>-4.297528124162106</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.148147780617379</v>
+        <v>2.165225400197795</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.29175871460195</v>
+        <v>1.440036755745877</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.659648302937556</v>
+        <v>4.748615127623911</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.31784914750544</v>
+        <v>-4.2751550985544</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.104012736781633</v>
+        <v>2.121090356362049</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.303014465714852</v>
+        <v>1.451292506858778</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.613317499526469</v>
+        <v>4.702284324212824</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.350865443416184</v>
+        <v>-4.308171394465145</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.27600442330269</v>
+        <v>2.293082042883106</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.2335770890481</v>
+        <v>1.381855130192027</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.756853278411772</v>
+        <v>4.845820103098128</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.339337807766576</v>
+        <v>-4.296643758815536</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.272536703390783</v>
+        <v>2.289614322971198</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.292577747249463</v>
+        <v>1.440855788393389</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.784174899160838</v>
+        <v>4.873141723847195</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.436679309108944</v>
+        <v>-4.393985260157905</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.237268215375624</v>
+        <v>2.25434583495604</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.248157565083974</v>
+        <v>1.396435606227901</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.761190902383334</v>
+        <v>4.85015772706969</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.522535338448911</v>
+        <v>-4.479841289497871</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.204176885832475</v>
+        <v>2.221254505412891</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.205781495857839</v>
+        <v>1.354059537001766</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.737016343040492</v>
+        <v>4.825983167726847</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.531372135865031</v>
+        <v>-4.488678086913991</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.18306136868653</v>
+        <v>2.200138988266946</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.198339323216489</v>
+        <v>1.346617364360415</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.714970241276183</v>
+        <v>4.803937065962539</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.622754698430489</v>
+        <v>-4.580060649479449</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.156672854705396</v>
+        <v>2.173750474285812</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.161774438497144</v>
+        <v>1.31005247964107</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.703195821489626</v>
+        <v>4.792162646175981</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.611047980443483</v>
+        <v>-4.568353931492443</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.263483799724465</v>
+        <v>2.280561419304881</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.17348115648415</v>
+        <v>1.321759197628077</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.812348110106097</v>
+        <v>4.901314934792453</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.511384476359821</v>
+        <v>-4.468690427408781</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.306381540089335</v>
+        <v>2.323459159669751</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.236668239687837</v>
+        <v>1.384946280831763</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.853292698759714</v>
+        <v>4.94225952344607</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.521700574526172</v>
+        <v>-4.479006525575133</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.515159934100852</v>
+        <v>2.532237553681268</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.236668239687837</v>
+        <v>1.384946280831763</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.066197532037772</v>
+        <v>5.155164356724128</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.5216066065088</v>
+        <v>-4.47891255755776</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.514376188219891</v>
+        <v>2.531453807800307</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.237038101035155</v>
+        <v>1.385316142179081</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.065598115758252</v>
+        <v>5.154564940444608</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.528825430708644</v>
+        <v>-4.486131381757605</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.505720644484307</v>
+        <v>2.522798264064723</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.237038101035155</v>
+        <v>1.385316142179081</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.059830101702606</v>
+        <v>5.148796926388962</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.527877007590606</v>
+        <v>-4.485182958639566</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.506100013731523</v>
+        <v>2.523177633311938</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.237038101035155</v>
+        <v>1.385316142179081</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.059830101702606</v>
+        <v>5.148796926388962</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.68494546584623</v>
+        <v>-4.64225141689519</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.456000238410365</v>
+        <v>2.473077857990781</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.237038101035155</v>
+        <v>1.385316142179081</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.072557709683698</v>
+        <v>5.161524534370054</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.678953219057418</v>
+        <v>-4.636259170106379</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.460343135550277</v>
+        <v>2.477420755130693</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.237038101035155</v>
+        <v>1.385316142179081</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.074503708108086</v>
+        <v>5.163470532794442</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.590395257926651</v>
+        <v>-4.547701208975611</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.489420456020353</v>
+        <v>2.506498075600769</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.237038101035155</v>
+        <v>1.385316142179081</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.068157844125855</v>
+        <v>5.157124668812211</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.572636180423577</v>
+        <v>-4.529942131472537</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.495832764460578</v>
+        <v>2.512910384040994</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.237038101035155</v>
+        <v>1.385316142179081</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.06746652156485</v>
+        <v>5.156433346251206</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.473006029374509</v>
+        <v>-4.430311980423469</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.548467010788793</v>
+        <v>2.565544630369208</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.336668252084222</v>
+        <v>1.484946293228149</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.140026798102878</v>
+        <v>5.228993622789234</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.52240553806352</v>
+        <v>-4.47971148911248</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.717861472811914</v>
+        <v>2.73493909239233</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.346927085515967</v>
+        <v>1.495205126659894</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.335336363660651</v>
+        <v>5.424303188347007</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.315721064421144</v>
+        <v>-4.273027015470104</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.787723935371726</v>
+        <v>2.804801554952142</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.553611559158343</v>
+        <v>1.701889600302269</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.446535720948939</v>
+        <v>5.535502545635294</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.740284389162543</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.34987795941867</v>
+        <v>-4.30718391046763</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.776062691026821</v>
+        <v>2.793140310607237</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.47002778961753</v>
+        <v>1.618305830761457</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.398386972878556</v>
+        <v>5.487353797564912</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.826643328191134</v>
+        <v>3.884583734667195</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.735684087539255</v>
+        <v>4.711161981642519</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.319678161249579</v>
+        <v>-4.371725417903987</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.007456398725675</v>
+        <v>2.962115390167177</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.47002778961753</v>
+        <v>1.605794761668367</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.617700761309774</v>
+        <v>5.674638838643539</v>
       </c>
     </row>
   </sheetData>
